--- a/example6-rppa/results/pca/pca_norm_WT_7d_MC_CO_over_CO_CO.xlsx
+++ b/example6-rppa/results/pca/pca_norm_WT_7d_MC_CO_over_CO_CO.xlsx
@@ -1013,22 +1013,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.0208760018062579</v>
+        <v>-0.00657774885519052</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0337581227193334</v>
+        <v>0.00370605445645347</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00993849099034437</v>
+        <v>0.0167261147420646</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0104687272453228</v>
+        <v>0.0165410753830493</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00228108650218073</v>
+        <v>-0.0146614305786302</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.159798540011719</v>
+        <v>0.189876964358538</v>
       </c>
     </row>
     <row r="3">
@@ -1036,22 +1036,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0183623798439114</v>
+        <v>0.0111993878323746</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.00798492783346628</v>
+        <v>-0.00110459178225864</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0253810112585595</v>
+        <v>0.00448673832883429</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0317151457062741</v>
+        <v>-0.00568123485609609</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.018618837081751</v>
+        <v>0.0152030868174614</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.279329478605353</v>
+        <v>-0.285408702948272</v>
       </c>
     </row>
     <row r="4">
@@ -1059,22 +1059,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0378152670040101</v>
+        <v>0.131585263880326</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.00680598251254102</v>
+        <v>-0.104869148920813</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00618982363404213</v>
+        <v>0.160629356290015</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00759972778886281</v>
+        <v>-0.0366567736211506</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0131942563358099</v>
+        <v>-0.0343039671958202</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.150398646007047</v>
+        <v>-0.170984880667016</v>
       </c>
     </row>
     <row r="5">
@@ -1082,22 +1082,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0592089763780664</v>
+        <v>0.168274484071331</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0125389443928777</v>
+        <v>0.195583454198719</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0378737657638692</v>
+        <v>0.0707218961459099</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00231636351444557</v>
+        <v>-0.00758660196897218</v>
       </c>
       <c r="F5" t="n">
-        <v>0.113541394602017</v>
+        <v>-0.051728871657057</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0203998088284591</v>
+        <v>0.420886150127981</v>
       </c>
     </row>
     <row r="6">
@@ -1105,22 +1105,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0000348650802898668</v>
+        <v>-0.0530319953177806</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.00285396385120015</v>
+        <v>-0.0622055977641104</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00738257832077002</v>
+        <v>-0.000476919765206761</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0201250360373871</v>
+        <v>0.211306572359001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00880676158660602</v>
+        <v>-0.0714621275566927</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0835948080007354</v>
+        <v>0.147890056405921</v>
       </c>
     </row>
     <row r="7">
@@ -1128,22 +1128,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0207274587143088</v>
+        <v>0.0106465585381168</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.00862068204093552</v>
+        <v>-0.00130606909557878</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0112398320812323</v>
+        <v>-0.00359281451632229</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.00906222879016039</v>
+        <v>-0.00715238596678082</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0130596795873948</v>
+        <v>0.00720325759563435</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.132169048367387</v>
+        <v>-0.123550443651407</v>
       </c>
     </row>
     <row r="8">
@@ -1151,22 +1151,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0197998722809281</v>
+        <v>0.00710512249498674</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0347557282016192</v>
+        <v>-0.0108022135612484</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00774327797229524</v>
+        <v>-0.0109961184456208</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0432139030217731</v>
+        <v>-0.0145495605855044</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.023790748357529</v>
+        <v>0.0248156578540873</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.021594442971646</v>
+        <v>-0.0178564390827558</v>
       </c>
     </row>
     <row r="9">
@@ -1174,22 +1174,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00862712659422254</v>
+        <v>0.0103067710575789</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0129320741799678</v>
+        <v>0.0302081734917859</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0763050966577092</v>
+        <v>0.0183875408204871</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0129374353085661</v>
+        <v>-0.000380916119395531</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0499468720497478</v>
+        <v>0.000877796850332532</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0858828560181907</v>
+        <v>-0.0872177270176596</v>
       </c>
     </row>
     <row r="10">
@@ -1197,22 +1197,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0532438609161521</v>
+        <v>0.192350764521899</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0109356359487019</v>
+        <v>-0.127603367719778</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0315420247401537</v>
+        <v>-0.181268856916493</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00885968478520868</v>
+        <v>-0.162117858467681</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0410243519140937</v>
+        <v>-0.0329331346215974</v>
       </c>
       <c r="G10" t="n">
-        <v>0.137713154159151</v>
+        <v>0.0481904651096822</v>
       </c>
     </row>
     <row r="11">
@@ -1220,22 +1220,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.00914764024069908</v>
+        <v>-0.00679380366429692</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0355255107969785</v>
+        <v>0.0076332556508067</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0086978540472488</v>
+        <v>-0.00226289731981281</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0113794593134902</v>
+        <v>-0.0195515950824219</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0184709334730005</v>
+        <v>0.00826819945537845</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0876496372464789</v>
+        <v>-0.0821597908462685</v>
       </c>
     </row>
     <row r="12">
@@ -1243,22 +1243,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0609066509539654</v>
+        <v>0.224720825240488</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0123261948437374</v>
+        <v>-0.0182360097899855</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0436746074015156</v>
+        <v>-0.00134702010969072</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0725646823408849</v>
+        <v>0.057901203702853</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.028146334043713</v>
+        <v>0.113354869003016</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0402445858620036</v>
+        <v>0.0475618369468471</v>
       </c>
     </row>
     <row r="13">
@@ -1266,22 +1266,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0395780660138576</v>
+        <v>-0.131430572616782</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0313112969185558</v>
+        <v>0.0789153731648802</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0362263718454081</v>
+        <v>-0.00708083832705991</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0289605332070667</v>
+        <v>-0.255973960721631</v>
       </c>
       <c r="F13" t="n">
-        <v>0.026709470407761</v>
+        <v>-0.00147709840723312</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0470521767459831</v>
+        <v>0.066528227562322</v>
       </c>
     </row>
     <row r="14">
@@ -1289,22 +1289,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0232797218588173</v>
+        <v>-0.0146604487335742</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0320766177394105</v>
+        <v>-0.00460952228696862</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0155785364783304</v>
+        <v>-0.000428862423159943</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0222424653344163</v>
+        <v>-0.0104314461289598</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0013217030487767</v>
+        <v>0.0148035028228782</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.136115408043986</v>
+        <v>-0.12251153883591</v>
       </c>
     </row>
     <row r="15">
@@ -1312,22 +1312,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>0.00764539068208881</v>
+        <v>0.00166560067539766</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.036239283532378</v>
+        <v>-0.000578590961831163</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.00490988454399399</v>
+        <v>-0.00630168467867034</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.000374656178286835</v>
+        <v>-0.0212786983802691</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.00828614431847065</v>
+        <v>0.0117023164888762</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0428417039053138</v>
+        <v>-0.0396625501370886</v>
       </c>
     </row>
     <row r="16">
@@ -1335,22 +1335,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0982028263249054</v>
+        <v>0.174686601771993</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0535975863546412</v>
+        <v>-0.00238313585522848</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0596745667179995</v>
+        <v>-0.0101131460122575</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0145823009843295</v>
+        <v>0.043411700831149</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0354036828307205</v>
+        <v>0.0429631179974598</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00388346930171762</v>
+        <v>-0.0494794247611967</v>
       </c>
     </row>
     <row r="17">
@@ -1358,22 +1358,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>0.145908357188229</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0162812402875757</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0396840053748678</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.019614763744093</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.116561053744713</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0253885256442759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1381,22 +1381,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0995929344366299</v>
+        <v>0.0168086038974482</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0751329969170609</v>
+        <v>-0.140171566146239</v>
       </c>
       <c r="D18" t="n">
-        <v>0.308743659926286</v>
+        <v>-0.050601791275988</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0671344134746096</v>
+        <v>0.0388615117789122</v>
       </c>
       <c r="F18" t="n">
-        <v>0.124675440266002</v>
+        <v>0.0904145437744045</v>
       </c>
       <c r="G18" t="n">
-        <v>0.00755533716435296</v>
+        <v>-0.00283767160681313</v>
       </c>
     </row>
     <row r="19">
@@ -1404,22 +1404,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>0.036524947838877</v>
+        <v>0.262708074435779</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.00285002809802077</v>
+        <v>-0.0161473391690528</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0339224436996225</v>
+        <v>-0.00475526056614301</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.013609327855764</v>
+        <v>0.0593818613272467</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0190987732284178</v>
+        <v>0.121001343309183</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0478830706997344</v>
+        <v>-0.0541187765942675</v>
       </c>
     </row>
     <row r="20">
@@ -1427,22 +1427,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0337494518288142</v>
+        <v>0.0165542060272025</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0265716198820313</v>
+        <v>0.00189257863785026</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0233055413130218</v>
+        <v>-0.00786557601237592</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.00219278299858002</v>
+        <v>-0.0201701503241638</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0138300412100887</v>
+        <v>0.012162531077054</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00418798648651778</v>
+        <v>0.00456132567410455</v>
       </c>
     </row>
     <row r="21">
@@ -1450,22 +1450,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>0.00720700689038557</v>
+        <v>0.00247208750972928</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0301729783039426</v>
+        <v>-0.000546090418553896</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0094579626495031</v>
+        <v>-0.00293504209026304</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0009707693809969</v>
+        <v>-0.0192952135840445</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0130768440180301</v>
+        <v>0.00934863922762578</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.133495086647652</v>
+        <v>-0.125129822968629</v>
       </c>
     </row>
     <row r="22">
@@ -1473,22 +1473,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0398598507031057</v>
+        <v>0.166316092569204</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0137664129787803</v>
+        <v>0.190704917691835</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0169296301361152</v>
+        <v>0.0656883632840718</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0222986992410101</v>
+        <v>-0.00690976637103252</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0504720958214279</v>
+        <v>-0.0586154352370619</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0646872003396233</v>
+        <v>-0.05322373727689</v>
       </c>
     </row>
     <row r="23">
@@ -1496,22 +1496,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>0.000414851094351515</v>
+        <v>-0.000479640358444295</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0331654912253849</v>
+        <v>0.00331960050104943</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0170039734570512</v>
+        <v>0.000753191815285147</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0109490469346584</v>
+        <v>-0.0225312559631312</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.00801907206677721</v>
+        <v>0.00724854338846906</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.045163739656341</v>
+        <v>-0.0401363235062948</v>
       </c>
     </row>
     <row r="24">
@@ -1519,22 +1519,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0389159369831637</v>
+        <v>0.0176764865509219</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.013351823393849</v>
+        <v>0.00261294934177921</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.00622781482589078</v>
+        <v>-0.0166099879782999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.00387256554228681</v>
+        <v>-0.00859587932573367</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00812864990453763</v>
+        <v>0.00922549226456954</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00211344117200596</v>
+        <v>-0.00253888269392504</v>
       </c>
     </row>
     <row r="25">
@@ -1542,22 +1542,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0239802218276091</v>
+        <v>-0.0156424262657541</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0453063572476477</v>
+        <v>-0.00358958607139374</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0123250142051059</v>
+        <v>-0.0013478297324489</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0152532314111111</v>
+        <v>-0.0191750242720625</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.000585826288109109</v>
+        <v>0.016571508586764</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.137963025144238</v>
+        <v>-0.124417101897312</v>
       </c>
     </row>
     <row r="26">
@@ -1565,22 +1565,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0104560085710144</v>
+        <v>-0.0404191974073602</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0373063401192525</v>
+        <v>-0.108943680332563</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0213363194145413</v>
+        <v>-0.172942941867122</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0254974937121781</v>
+        <v>-0.203026281880101</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0171827832771937</v>
+        <v>-0.113540574948056</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0479909923683475</v>
+        <v>0.0656145500556664</v>
       </c>
     </row>
     <row r="27">
@@ -1588,22 +1588,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.00924291062807264</v>
+        <v>-0.00614142256134952</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0233385669182958</v>
+        <v>0.00207172148999273</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.00191504160818083</v>
+        <v>-0.000162693894510673</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0110434512906988</v>
+        <v>-0.00962188543080886</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0096518535602105</v>
+        <v>0.0110795992645127</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0438564238981407</v>
+        <v>0.0435868958889249</v>
       </c>
     </row>
     <row r="28">
@@ -1611,22 +1611,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>0.00850339413836153</v>
+        <v>0.0062081649500036</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.00396669904747828</v>
+        <v>0.00444921075175249</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0238791373813971</v>
+        <v>0.00477403688388701</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0254346071978451</v>
+        <v>-0.0109849330401714</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0137929423390177</v>
+        <v>-0.00602362579021961</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0487322294211356</v>
+        <v>0.0436505347843935</v>
       </c>
     </row>
     <row r="29">
@@ -1634,22 +1634,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0281924769209193</v>
+        <v>0.0844026942043349</v>
       </c>
       <c r="C29" t="n">
-        <v>0.015845054065128</v>
+        <v>0.110046761170866</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0519159227307621</v>
+        <v>0.22066251842626</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0224492191722621</v>
+        <v>-0.0861353848151989</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0611252599689017</v>
+        <v>-0.161066968643631</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0367382411729115</v>
+        <v>0.0222767541664046</v>
       </c>
     </row>
     <row r="30">
@@ -1657,22 +1657,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>0.00468248314322546</v>
+        <v>0.00352645636887335</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0175422248773149</v>
+        <v>0.00508829046071775</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0250541512129345</v>
+        <v>0.0042908088094301</v>
       </c>
       <c r="E30" t="n">
-        <v>0.031619990941571</v>
+        <v>-0.0192977873831874</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0151375353943257</v>
+        <v>-0.00421100877175312</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00276121267115479</v>
+        <v>0.00173126158796083</v>
       </c>
     </row>
     <row r="31">
@@ -1680,22 +1680,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0222663899264268</v>
+        <v>0.0116095009049641</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.00669882357446265</v>
+        <v>-0.000204917379695878</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0125356332633961</v>
+        <v>-0.00405643462840812</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0079173707148955</v>
+        <v>-0.00919970493856317</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0155161965228446</v>
+        <v>0.000865357515087276</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0436190372454803</v>
+        <v>-0.0411010956982273</v>
       </c>
     </row>
     <row r="32">
@@ -1703,22 +1703,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.0146848648857464</v>
+        <v>-0.00736447449969111</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0113317973403466</v>
+        <v>0.00271223771627867</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.00682291379482242</v>
+        <v>0.00615634362751514</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0218430940924219</v>
+        <v>-0.00172133298935798</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0114273423790247</v>
+        <v>0.0111180950600121</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.000345126388697046</v>
+        <v>0.00184562514700102</v>
       </c>
     </row>
     <row r="33">
@@ -1726,22 +1726,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.00443250415163518</v>
+        <v>-0.00622665725505998</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0232706194505161</v>
+        <v>-0.00240067287976043</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0222995637640038</v>
+        <v>-0.0114891906059392</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.00194300447017244</v>
+        <v>-0.00780150929275081</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0119213100050439</v>
+        <v>0.00672756519211591</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0421301182777997</v>
+        <v>0.0438135077160107</v>
       </c>
     </row>
     <row r="34">
@@ -1749,22 +1749,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>0.000170435153799856</v>
+        <v>-0.000266033478025134</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0130209987866863</v>
+        <v>0.00303092989074408</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.00899040473143104</v>
+        <v>0.000610477217549847</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0174178221485046</v>
+        <v>-0.00452835728868123</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00979635292545297</v>
+        <v>0.0112517038473228</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.043954894830194</v>
+        <v>-0.0414442773927009</v>
       </c>
     </row>
     <row r="35">
@@ -1772,22 +1772,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0338551019767733</v>
+        <v>0.0193584218415648</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0338355923931311</v>
+        <v>0.00557245946987646</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0528776817399225</v>
+        <v>0.00313567169633356</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0143236793268724</v>
+        <v>-0.0325539447962579</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0341889595902302</v>
+        <v>0.00957290139536295</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.044552539872446</v>
+        <v>-0.037821025097964</v>
       </c>
     </row>
     <row r="36">
@@ -1795,22 +1795,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.326304145235387</v>
+        <v>-0.0799081202259413</v>
       </c>
       <c r="C36" t="n">
-        <v>0.104880919309591</v>
+        <v>-0.0794117094458199</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.130637622772714</v>
+        <v>0.16174022883417</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.11437496648446</v>
+        <v>-0.0780376051562371</v>
       </c>
       <c r="F36" t="n">
-        <v>0.32899444797695</v>
+        <v>-0.115513477146699</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0151624129748573</v>
+        <v>0.00626332975952604</v>
       </c>
     </row>
     <row r="37">
@@ -1818,22 +1818,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.00924872981034794</v>
+        <v>-0.00359428982497921</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.00855410553257872</v>
+        <v>0.00932168887289476</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0211096445469344</v>
+        <v>0.00730198737937364</v>
       </c>
       <c r="E37" t="n">
-        <v>0.00831704403821472</v>
+        <v>-0.00657894917629883</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0152194947953313</v>
+        <v>0.00163322763332296</v>
       </c>
       <c r="G37" t="n">
-        <v>0.134467048287846</v>
+        <v>0.127635371361677</v>
       </c>
     </row>
     <row r="38">
@@ -1841,22 +1841,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0381805211349343</v>
+        <v>-0.0933719782251433</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0554768556997334</v>
+        <v>0.219548655278297</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0331089848954672</v>
+        <v>0.163547103909963</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00574079442324913</v>
+        <v>-0.174971561391915</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0358323622482244</v>
+        <v>0.143604963375859</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.045433338755999</v>
+        <v>0.0412665859007406</v>
       </c>
     </row>
     <row r="39">
@@ -1864,22 +1864,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0148530766365049</v>
+        <v>0.00666683838231932</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.0420164115408248</v>
+        <v>-0.000602153383255047</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0216105602907027</v>
+        <v>-0.00191906832049472</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0112340656777645</v>
+        <v>-0.0266446578306458</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.0213575034592113</v>
+        <v>0.0180517262563977</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0479861022806746</v>
+        <v>0.0460434166160068</v>
       </c>
     </row>
     <row r="40">
@@ -1887,22 +1887,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0054276980397218</v>
+        <v>0.00190205716873722</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.0347145673592191</v>
+        <v>-0.00175972444526776</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0145203839790536</v>
+        <v>0.000556094254019341</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.0368322885452774</v>
+        <v>-0.0162801484263586</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.0102502781410397</v>
+        <v>0.0240535033415824</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.089492803570622</v>
+        <v>-0.0825292995612421</v>
       </c>
     </row>
     <row r="41">
@@ -1933,22 +1933,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.0220032035925264</v>
+        <v>-0.145010268487172</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0045574019564066</v>
+        <v>-0.0563557205096884</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.057556660082655</v>
+        <v>0.096702507857404</v>
       </c>
       <c r="E42" t="n">
-        <v>0.012228405169911</v>
+        <v>0.191612001543392</v>
       </c>
       <c r="F42" t="n">
-        <v>0.080966939673849</v>
+        <v>0.153408761640394</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.111885955074824</v>
+        <v>0.0247687668866498</v>
       </c>
     </row>
     <row r="43">
@@ -1979,22 +1979,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.160250105715374</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.174929315701639</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.161356414643375</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.263456319685706</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0694714923255936</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0559022642785683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2002,22 +2002,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="n">
-        <v>0.0067602361102734</v>
+        <v>0.00483636875561595</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.00947763901270588</v>
+        <v>0.00684051401526164</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0254861775342521</v>
+        <v>0.00402224680173007</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0227776044731429</v>
+        <v>-0.012690733977421</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.00436639998047882</v>
+        <v>-0.00281358639257651</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.134007695500133</v>
+        <v>-0.12917089594127</v>
       </c>
     </row>
     <row r="46">
@@ -2025,22 +2025,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.00792532073603069</v>
+        <v>-0.0722743026583251</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0092910340171052</v>
+        <v>-0.0762042145823877</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0407272216285741</v>
+        <v>0.0209185249242056</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.00783224237859152</v>
+        <v>0.27794214996162</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.00528448060501928</v>
+        <v>-0.101954294480286</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0420789807821445</v>
+        <v>-0.0210286702380389</v>
       </c>
     </row>
     <row r="47">
@@ -2048,22 +2048,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.242415343724695</v>
+        <v>-0.0775046145761626</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0917594841653168</v>
+        <v>0.0716660839747811</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0566379319470165</v>
+        <v>-0.12192065350726</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.419241037994789</v>
+        <v>0.0215341434479072</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0325111339542581</v>
+        <v>0.0248389985203836</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.0266729523933783</v>
+        <v>-0.0122813089031575</v>
       </c>
     </row>
     <row r="48">
@@ -2071,22 +2071,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.18842868530257</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1977229714498</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.322152855130307</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.185995869036626</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.152195672531132</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0319956582748591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2094,22 +2094,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.0028812733339007</v>
+        <v>-0.0010220613893048</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.015386840453191</v>
+        <v>0.0055696178087581</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.0170065370072654</v>
+        <v>0.00364439715112544</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0181791186864575</v>
+        <v>-0.0131320640795132</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.000353439115425535</v>
+        <v>-0.000456472646170808</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0448808190584647</v>
+        <v>0.0434596763779567</v>
       </c>
     </row>
     <row r="50">
@@ -2117,22 +2117,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0343284735599828</v>
+        <v>0.0188662103102394</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0201512088396257</v>
+        <v>0.00205232490166902</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.0355708915885148</v>
+        <v>-0.00122797095919687</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00827457460412494</v>
+        <v>-0.0215283834153053</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0291487682026544</v>
+        <v>0.0065304532423594</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.040748564464416</v>
+        <v>-0.0387536693911957</v>
       </c>
     </row>
     <row r="51">
@@ -2140,22 +2140,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.0389667546450955</v>
+        <v>-0.158894763418372</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0976804150732539</v>
+        <v>-0.0894465508732977</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0455174374941205</v>
+        <v>0.0482989545468543</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0135775515306906</v>
+        <v>0.165790090032819</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0410564770801283</v>
+        <v>0.147362189834398</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0415134585066785</v>
+        <v>-0.0398760830184937</v>
       </c>
     </row>
     <row r="52">
@@ -2186,22 +2186,22 @@
         <v>58</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0167171255529731</v>
+        <v>0.00885451223390791</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0271085141490038</v>
+        <v>-0.00136969326913887</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.0227414169207274</v>
+        <v>0.000761315475265207</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0139500905731062</v>
+        <v>-0.018777177611455</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0242339318314376</v>
+        <v>0.0143939324301081</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.0890586328964932</v>
+        <v>-0.0827102831506924</v>
       </c>
     </row>
     <row r="54">
@@ -2209,22 +2209,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.0193274305015857</v>
+        <v>-0.010631500581204</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0398345216505583</v>
+        <v>0.00477030847917135</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.0163409239243099</v>
+        <v>0.0067992667140658</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.00963756192084909</v>
+        <v>-0.0205305931191229</v>
       </c>
       <c r="F54" t="n">
-        <v>0.00499308422386937</v>
+        <v>0.0157013645165365</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0902582293570758</v>
+        <v>0.0891068572584674</v>
       </c>
     </row>
     <row r="55">
@@ -2232,22 +2232,22 @@
         <v>60</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.0273497942754557</v>
+        <v>-0.0916724215024141</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0103696832619974</v>
+        <v>0.0847666102656054</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.0457405966867437</v>
+        <v>-0.144207691365061</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.00394910613259132</v>
+        <v>0.0254705746960407</v>
       </c>
       <c r="F55" t="n">
-        <v>0.025205785246921</v>
+        <v>0.0293795557143352</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.0236733304351605</v>
+        <v>-0.0203225297372522</v>
       </c>
     </row>
     <row r="56">
@@ -2255,22 +2255,22 @@
         <v>61</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.00738979985735517</v>
+        <v>-0.00407999480392126</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0269925590778632</v>
+        <v>0.00618581864468831</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.0175734639089428</v>
+        <v>0.00365964709006251</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0029027906081667</v>
+        <v>-0.0161709209462607</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0065487883967555</v>
+        <v>0.00850329639469963</v>
       </c>
       <c r="G56" t="n">
-        <v>0.00132089598527965</v>
+        <v>0.00455245262832601</v>
       </c>
     </row>
     <row r="57">
@@ -2278,22 +2278,22 @@
         <v>62</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.068297515363803</v>
+        <v>-0.147805753517075</v>
       </c>
       <c r="C57" t="n">
-        <v>0.011397148559435</v>
+        <v>-0.0764375575527144</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0136098090335235</v>
+        <v>0.0933768013206292</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0790359250246404</v>
+        <v>0.182780110113618</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0282891408368594</v>
+        <v>0.150159713791361</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0246602282442085</v>
+        <v>-0.0376596668242976</v>
       </c>
     </row>
     <row r="58">
@@ -2301,22 +2301,22 @@
         <v>63</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.00506813365705386</v>
+        <v>-0.00162527030280473</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.00483506278939299</v>
+        <v>-0.00961856194020183</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00276207940911076</v>
+        <v>0.00539823883683468</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0123459404240059</v>
+        <v>-0.00834942761650108</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.0439602998457358</v>
+        <v>-0.00612269286854913</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.042976502888346</v>
+        <v>-0.0405934018180505</v>
       </c>
     </row>
     <row r="59">
@@ -2324,22 +2324,22 @@
         <v>64</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0246106821298752</v>
+        <v>0.0124650045721682</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0282167902703308</v>
+        <v>0.00433837919308441</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.0283379884350242</v>
+        <v>-0.00337202388809567</v>
       </c>
       <c r="E59" t="n">
-        <v>0.00397139121070977</v>
+        <v>-0.02189125136062</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.0111058918571693</v>
+        <v>0.0104463843981883</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.131305779688936</v>
+        <v>-0.128263331602896</v>
       </c>
     </row>
     <row r="60">
@@ -2393,22 +2393,22 @@
         <v>67</v>
       </c>
       <c r="B62" t="n">
-        <v>0.0133418779379515</v>
+        <v>0.00759444806793089</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0159515383725231</v>
+        <v>-0.00522428958661288</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.0138253945993512</v>
+        <v>0.00170067231009769</v>
       </c>
       <c r="E62" t="n">
-        <v>0.000788949087649616</v>
+        <v>-0.0149875508575362</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.0369831574011579</v>
+        <v>0.00421485781061792</v>
       </c>
       <c r="G62" t="n">
-        <v>0.00466507444412459</v>
+        <v>-0.000484072327686797</v>
       </c>
     </row>
     <row r="63">
@@ -2416,22 +2416,22 @@
         <v>68</v>
       </c>
       <c r="B63" t="n">
-        <v>0.126494489702871</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.342014354954646</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.301633340711373</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.113420602646903</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.0346649440248383</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.00325280237827187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2439,22 +2439,22 @@
         <v>69</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.0304344272808897</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.423272254296372</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0.174297756020641</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.117128488932709</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.108285981533543</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0267461215156307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2462,22 +2462,22 @@
         <v>70</v>
       </c>
       <c r="B65" t="n">
-        <v>0.0181752592285761</v>
+        <v>0.0077731648030955</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0256489452555915</v>
+        <v>0.000312596592516023</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.00978660870607837</v>
+        <v>-0.00691571432404485</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0146192142314111</v>
+        <v>-0.0141174887073437</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.00329777382993471</v>
+        <v>0.0147104151413417</v>
       </c>
       <c r="G65" t="n">
-        <v>0.135580074722973</v>
+        <v>0.128986726082139</v>
       </c>
     </row>
     <row r="66">
@@ -2508,22 +2508,22 @@
         <v>72</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.0231752087915032</v>
+        <v>-0.0110954468282406</v>
       </c>
       <c r="C67" t="n">
-        <v>0.00415399221025979</v>
+        <v>-0.000621198678620737</v>
       </c>
       <c r="D67" t="n">
-        <v>0.00375784807766407</v>
+        <v>0.00893493158454546</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.0246540555629402</v>
+        <v>0.00857812958178427</v>
       </c>
       <c r="F67" t="n">
-        <v>0.00880642535804274</v>
+        <v>0.00575071613056645</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0915905691312245</v>
+        <v>-0.0837771753203168</v>
       </c>
     </row>
     <row r="68">
@@ -2531,22 +2531,22 @@
         <v>73</v>
       </c>
       <c r="B68" t="n">
-        <v>0.0197238500847874</v>
+        <v>0.0109714756981104</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.0243550029728403</v>
+        <v>0.00503119278455945</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.0337851737641866</v>
+        <v>0.00163067441829843</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.00730092265340927</v>
+        <v>-0.0184310758424648</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.00974899721733256</v>
+        <v>0.0132170077781776</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.000145733139969747</v>
+        <v>-0.0000489537868759059</v>
       </c>
     </row>
     <row r="69">
@@ -2554,22 +2554,22 @@
         <v>74</v>
       </c>
       <c r="B69" t="n">
-        <v>0.0138840835219039</v>
+        <v>0.00632459936857877</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.0259898965991531</v>
+        <v>0.00182662812521793</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.015524535635877</v>
+        <v>-0.00339389616906396</v>
       </c>
       <c r="E69" t="n">
-        <v>0.000345038313681736</v>
+        <v>-0.0176011744858417</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.00818435298849425</v>
+        <v>0.00949782864065957</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.0459015945615333</v>
+        <v>-0.0392297882347927</v>
       </c>
     </row>
     <row r="70">
@@ -2577,22 +2577,22 @@
         <v>75</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.0273597722103579</v>
+        <v>-0.0275544191275745</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0589003795798018</v>
+        <v>0.175288957396925</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.0165700029837651</v>
+        <v>0.0737028975178986</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0716677100561606</v>
+        <v>-0.0190890196379942</v>
       </c>
       <c r="F70" t="n">
-        <v>0.041219087723614</v>
+        <v>-0.141509039448645</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.00336326010945596</v>
+        <v>-0.0921685658719654</v>
       </c>
     </row>
     <row r="71">
@@ -2600,22 +2600,22 @@
         <v>76</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.00395314945775221</v>
+        <v>-0.000283486945892137</v>
       </c>
       <c r="C71" t="n">
-        <v>0.00433285666929589</v>
+        <v>0.00237520174766455</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.0121751734491371</v>
+        <v>0.00682366737276788</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0122092625753547</v>
+        <v>-0.00159171280455237</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.00653473695086889</v>
+        <v>-0.00534386687994992</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0899787032720376</v>
+        <v>0.0846978337044183</v>
       </c>
     </row>
     <row r="72">
@@ -2623,22 +2623,22 @@
         <v>77</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.0143323591659676</v>
+        <v>0.10347264463982</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0208489228177451</v>
+        <v>-0.0927924711139821</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.0392233280633393</v>
+        <v>0.190094120813746</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0241658279136815</v>
+        <v>-0.0292643115495814</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.0335746960100568</v>
+        <v>-0.0484757798102536</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.110710288565303</v>
+        <v>0.0970671726233446</v>
       </c>
     </row>
     <row r="73">
@@ -2646,22 +2646,22 @@
         <v>78</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.0117854888788379</v>
+        <v>0.0784935524206531</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.0217283140093811</v>
+        <v>0.0950578993103123</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0172263544186515</v>
+        <v>-0.190714111946133</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00145268813296422</v>
+        <v>0.0823363138930326</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0455751799610975</v>
+        <v>0.135372123147328</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.047008415337235</v>
+        <v>-0.00860569302385728</v>
       </c>
     </row>
     <row r="74">
@@ -2669,22 +2669,22 @@
         <v>79</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0366292526611145</v>
+        <v>0.0151180732378473</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.027491103273396</v>
+        <v>-0.00355603681040717</v>
       </c>
       <c r="D74" t="n">
-        <v>0.00322057839161492</v>
+        <v>-0.0188004222961917</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.032132910099214</v>
+        <v>-0.0113261710898952</v>
       </c>
       <c r="F74" t="n">
-        <v>0.00039683025897738</v>
+        <v>0.0218937006344417</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.0866036070558792</v>
+        <v>-0.082340088371969</v>
       </c>
     </row>
     <row r="75">
@@ -2692,22 +2692,22 @@
         <v>80</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0346232802471047</v>
+        <v>0.0129706134719171</v>
       </c>
       <c r="C75" t="n">
-        <v>0.00361916133494962</v>
+        <v>0.00167666851081647</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0256070068349589</v>
+        <v>-0.0270580578703777</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.0137209807312149</v>
+        <v>0.00973037045600286</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0404741330939015</v>
+        <v>0.00685332937554971</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.133656931141269</v>
+        <v>-0.129614104183731</v>
       </c>
     </row>
     <row r="76">
@@ -2715,22 +2715,22 @@
         <v>81</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0788511531167245</v>
+        <v>-0.128113825526988</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.0378127982130221</v>
+        <v>0.326672352948662</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.0486790330023498</v>
+        <v>0.235296981399933</v>
       </c>
       <c r="E76" t="n">
-        <v>0.00315129786512548</v>
+        <v>-0.231459625362739</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.00765274016529189</v>
+        <v>0.219782760621122</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.0863444104377484</v>
+        <v>-0.0652364225951746</v>
       </c>
     </row>
     <row r="77">
@@ -2738,22 +2738,22 @@
         <v>82</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.00487760105624871</v>
+        <v>-0.00862829705444715</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.0360732532159251</v>
+        <v>0.000289090385247539</v>
       </c>
       <c r="D77" t="n">
-        <v>0.028457440436534</v>
+        <v>-0.0178012983259406</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.0211283136082273</v>
+        <v>-0.00842337269396299</v>
       </c>
       <c r="F77" t="n">
-        <v>0.036312302017858</v>
+        <v>0.0183376109135017</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.0913009907852153</v>
+        <v>-0.0867629465543025</v>
       </c>
     </row>
     <row r="78">
@@ -2807,22 +2807,22 @@
         <v>85</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0172705859301595</v>
+        <v>0.0079693818567021</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.0286923619359003</v>
+        <v>-0.00096888100585854</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.0138959895229747</v>
+        <v>-0.00449114465652411</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0100257501550315</v>
+        <v>-0.0219075902615796</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.0220726110340775</v>
+        <v>0.00626256874797174</v>
       </c>
       <c r="G80" t="n">
-        <v>0.136898463337386</v>
+        <v>0.129619628605769</v>
       </c>
     </row>
     <row r="81">
@@ -2830,22 +2830,22 @@
         <v>86</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.00223867338422318</v>
+        <v>0.162478315397588</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.0223442915034916</v>
+        <v>-0.156076224877825</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.0120515239010618</v>
+        <v>0.263159887763645</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.0413242563459515</v>
+        <v>-0.054691867160574</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.0213004082185207</v>
+        <v>-0.031962437975156</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0924982924372281</v>
+        <v>-0.0515488188597323</v>
       </c>
     </row>
     <row r="82">
@@ -2853,22 +2853,22 @@
         <v>87</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0198806732003108</v>
+        <v>0.0122243124307775</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.0151339287876037</v>
+        <v>-0.00154157452152493</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.0302786730377277</v>
+        <v>0.00512886245349394</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.0052085994035326</v>
+        <v>-0.0159612939152729</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.035199955001898</v>
+        <v>0.00776375604840119</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.0842635023653809</v>
+        <v>-0.0842273694096278</v>
       </c>
     </row>
     <row r="83">
@@ -2876,22 +2876,22 @@
         <v>88</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0372565045104934</v>
+        <v>0.0533208123880299</v>
       </c>
       <c r="C83" t="n">
-        <v>0.105767965956893</v>
+        <v>-0.083423019958814</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.116544275069037</v>
+        <v>0.0896639730150972</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.0829602052973178</v>
+        <v>0.238010412805361</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.215747861235874</v>
+        <v>0.240276967687418</v>
       </c>
       <c r="G83" t="n">
-        <v>0.00412419328288507</v>
+        <v>0.0607142477747561</v>
       </c>
     </row>
     <row r="84">
@@ -2899,22 +2899,22 @@
         <v>89</v>
       </c>
       <c r="B84" t="n">
-        <v>0.0248300138388304</v>
+        <v>0.012008738759101</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.0277979783323756</v>
+        <v>-0.0014916016201045</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.017659160390724</v>
+        <v>-0.00513617402147931</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.0106880855707229</v>
+        <v>-0.0189953017699905</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.0203074398929993</v>
+        <v>0.013973001283299</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.0437577209575399</v>
+        <v>-0.0410625410269797</v>
       </c>
     </row>
     <row r="85">
@@ -2945,22 +2945,22 @@
         <v>91</v>
       </c>
       <c r="B86" t="n">
-        <v>0.00768947867952487</v>
+        <v>0.169442723218595</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0194776223110358</v>
+        <v>0.201250046229249</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.00206583249295196</v>
+        <v>0.0800948743504659</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.0383145170700204</v>
+        <v>0.00694713802401791</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.000971623869874352</v>
+        <v>-0.0468069198443033</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.0651505430976553</v>
+        <v>-0.0917918970581054</v>
       </c>
     </row>
     <row r="87">
@@ -2968,22 +2968,22 @@
         <v>92</v>
       </c>
       <c r="B87" t="n">
-        <v>0.0206804259461649</v>
+        <v>0.01226335348722</v>
       </c>
       <c r="C87" t="n">
-        <v>0.00354369260503934</v>
+        <v>0.00268511793281063</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.0215699618324649</v>
+        <v>0.00111185253761677</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.00293461448079394</v>
+        <v>-0.00239110949863645</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.00798493433834989</v>
+        <v>0.00241203773417837</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0470344237469123</v>
+        <v>0.042161039799477</v>
       </c>
     </row>
     <row r="88">
@@ -2991,22 +2991,22 @@
         <v>93</v>
       </c>
       <c r="B88" t="n">
-        <v>0.0456438862606309</v>
+        <v>0.14615597382841</v>
       </c>
       <c r="C88" t="n">
-        <v>0.00573801747415641</v>
+        <v>-0.113782497015259</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.0338348870177088</v>
+        <v>0.189485588506423</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.0482767970831123</v>
+        <v>-0.0325299821210414</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.0269609465227367</v>
+        <v>-0.0198114833753393</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0498368155442937</v>
+        <v>-0.040116974385191</v>
       </c>
     </row>
     <row r="89">
@@ -3014,22 +3014,22 @@
         <v>94</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0144118901280012</v>
+        <v>0.00666164690760525</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.0228798570176672</v>
+        <v>-0.00473552906014537</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.0074000186042987</v>
+        <v>-0.00321410387049721</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.00929785456864268</v>
+        <v>-0.015142106673506</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.0248667857801995</v>
+        <v>0.010201260756998</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0916300422932872</v>
+        <v>0.0857201961825667</v>
       </c>
     </row>
     <row r="90">
@@ -3037,22 +3037,22 @@
         <v>95</v>
       </c>
       <c r="B90" t="n">
-        <v>0.0280975160556019</v>
+        <v>0.0144346886860706</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.00783782050269054</v>
+        <v>-0.0002958098924499</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.014804882569001</v>
+        <v>-0.00529251469530358</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.0140481745701567</v>
+        <v>-0.00652347158892</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.0100675514677194</v>
+        <v>0.00963928405585478</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0911890471651078</v>
+        <v>0.0857254499395239</v>
       </c>
     </row>
     <row r="91">
@@ -3060,22 +3060,22 @@
         <v>96</v>
       </c>
       <c r="B91" t="n">
-        <v>0.00656532754817305</v>
+        <v>0.0983365291149461</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0696013691066277</v>
+        <v>0.114297084488796</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.0622503062191574</v>
+        <v>0.0694770998813331</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0467909007629623</v>
+        <v>0.224803450092526</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.0329277643623355</v>
+        <v>-0.13508524951852</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.0425228386699796</v>
+        <v>0.0107488659961953</v>
       </c>
     </row>
     <row r="92">
@@ -3083,22 +3083,22 @@
         <v>97</v>
       </c>
       <c r="B92" t="n">
-        <v>-0.0132515275169445</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0.336721734860029</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.18623943126285</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0.166718188381516</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.0326620185868539</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.00202343509710424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -3152,22 +3152,22 @@
         <v>100</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.00830942562108276</v>
+        <v>0.0931629273228348</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.00350704433661308</v>
+        <v>0.0978380738784278</v>
       </c>
       <c r="D95" t="n">
-        <v>0.0191335975974929</v>
+        <v>-0.207369607382984</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.0324505445272487</v>
+        <v>0.105950404099338</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0250755349299831</v>
+        <v>0.155964066071411</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.0444053161746636</v>
+        <v>0.031037150273772</v>
       </c>
     </row>
     <row r="96">
@@ -3175,22 +3175,22 @@
         <v>101</v>
       </c>
       <c r="B96" t="n">
-        <v>0.00129868759429332</v>
+        <v>0.113579274199724</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.0264395676724851</v>
+        <v>-0.107369396118741</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.000140892161335468</v>
+        <v>0.17680978733846</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.0276420338935352</v>
+        <v>-0.0415993635359358</v>
       </c>
       <c r="F96" t="n">
-        <v>0.00378792449807149</v>
+        <v>-0.0188586836844397</v>
       </c>
       <c r="G96" t="n">
-        <v>0.00037763539978702</v>
+        <v>-0.021597022041896</v>
       </c>
     </row>
     <row r="97">
@@ -3198,22 +3198,22 @@
         <v>102</v>
       </c>
       <c r="B97" t="n">
-        <v>0.0110738055452453</v>
+        <v>0.00463867476003313</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.0194912886317988</v>
+        <v>-0.000786745694647757</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.00579006119516481</v>
+        <v>-0.00445552637052238</v>
       </c>
       <c r="E97" t="n">
-        <v>0.00218188481954045</v>
+        <v>-0.0131743980363874</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.0102043064709931</v>
+        <v>0.00583519218644623</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.0887779305952718</v>
+        <v>-0.0854133489529017</v>
       </c>
     </row>
     <row r="98">
@@ -3221,22 +3221,22 @@
         <v>103</v>
       </c>
       <c r="B98" t="n">
-        <v>0.00397872317913428</v>
+        <v>-0.00941057516165098</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.0275489395726656</v>
+        <v>0.00544083617145272</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0672622630413475</v>
+        <v>-0.042131288422425</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.0113784034920152</v>
+        <v>0.0054036048970279</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0957075456321249</v>
+        <v>0.014103354078922</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0342223061794475</v>
+        <v>0.0407289224579133</v>
       </c>
     </row>
     <row r="99">
@@ -3244,22 +3244,22 @@
         <v>104</v>
       </c>
       <c r="B99" t="n">
-        <v>0.204107966576081</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0923266036137357</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.0446463255108671</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.205111295540567</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0714911381364169</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.045540768310658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -3267,22 +3267,22 @@
         <v>105</v>
       </c>
       <c r="B100" t="n">
-        <v>0.281727317691547</v>
+        <v>0.0690653131788354</v>
       </c>
       <c r="C100" t="n">
-        <v>0.149564490665699</v>
+        <v>0.0144019261823572</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.166342937730652</v>
+        <v>-0.0719912927211502</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.213504840056701</v>
+        <v>0.0570726879545941</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.1113117209935</v>
+        <v>-0.231504510954185</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.0655566066654908</v>
+        <v>-0.0503454784611294</v>
       </c>
     </row>
     <row r="101">
@@ -3290,22 +3290,22 @@
         <v>106</v>
       </c>
       <c r="B101" t="n">
-        <v>0.0439345394576783</v>
+        <v>0.146617512200371</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.0510093870875176</v>
+        <v>-0.123198752334349</v>
       </c>
       <c r="D101" t="n">
-        <v>0.0101015254455375</v>
+        <v>0.176136817007687</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.0395085236569034</v>
+        <v>-0.0571027591215536</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0156047289864664</v>
+        <v>-0.0092372770846348</v>
       </c>
       <c r="G101" t="n">
-        <v>0.00348089254676056</v>
+        <v>-0.0483536678539823</v>
       </c>
     </row>
     <row r="102">
@@ -3313,22 +3313,22 @@
         <v>107</v>
       </c>
       <c r="B102" t="n">
-        <v>0.00824757881119759</v>
+        <v>0.00440587666453762</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.0158924495114562</v>
+        <v>-0.000621223500699063</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.0126102154052459</v>
+        <v>0.000538664304381457</v>
       </c>
       <c r="E102" t="n">
-        <v>0.00230131602105449</v>
+        <v>-0.0126590298821159</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.0165223712653624</v>
+        <v>0.00455330469931952</v>
       </c>
       <c r="G102" t="n">
-        <v>0.09176614875499</v>
+        <v>0.0863451745878031</v>
       </c>
     </row>
     <row r="103">
@@ -3336,22 +3336,22 @@
         <v>108</v>
       </c>
       <c r="B103" t="n">
-        <v>0.00100428700194261</v>
+        <v>0.207779171049996</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.0320451969592129</v>
+        <v>-0.0218619100844488</v>
       </c>
       <c r="D103" t="n">
-        <v>0.0169795750129315</v>
+        <v>-0.0082421303030639</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.00222263319693046</v>
+        <v>0.042139758550775</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0126895573808783</v>
+        <v>0.103466115643602</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.0894530581053949</v>
+        <v>0.0460431128144281</v>
       </c>
     </row>
     <row r="104">
@@ -3359,22 +3359,22 @@
         <v>109</v>
       </c>
       <c r="B104" t="n">
-        <v>0.202275119365921</v>
+        <v>0.0619748709560854</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0559083822990537</v>
+        <v>0.0129233833249912</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.0100658412403664</v>
+        <v>-0.0646004610853237</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.194154816383981</v>
+        <v>0.0512134428746326</v>
       </c>
       <c r="F104" t="n">
-        <v>0.267991167228072</v>
+        <v>-0.207737596946624</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0346427005478229</v>
+        <v>-0.0100200739180379</v>
       </c>
     </row>
     <row r="105">
@@ -3382,22 +3382,22 @@
         <v>110</v>
       </c>
       <c r="B105" t="n">
-        <v>0.109187046865428</v>
+        <v>0.0955098103272781</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0116075504744826</v>
+        <v>0.108173012161509</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.0209654109664058</v>
+        <v>0.0622750514158867</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.0584655049484297</v>
+        <v>0.21399713908239</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0901616077627789</v>
+        <v>-0.137089718838115</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.0671457866933146</v>
+        <v>-0.0128216193110209</v>
       </c>
     </row>
     <row r="106">
@@ -3405,22 +3405,22 @@
         <v>111</v>
       </c>
       <c r="B106" t="n">
-        <v>0.039928358607264</v>
+        <v>0.216758115955857</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.0208119992448072</v>
+        <v>-0.0223542500814519</v>
       </c>
       <c r="D106" t="n">
-        <v>0.0173497427945694</v>
+        <v>-0.0120602369866817</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.0127797759001378</v>
+        <v>0.0438926531813392</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0465829442138955</v>
+        <v>0.09755455803364</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.000138363346590765</v>
+        <v>0.0089260372136464</v>
       </c>
     </row>
     <row r="107">
@@ -3428,22 +3428,22 @@
         <v>112</v>
       </c>
       <c r="B107" t="n">
-        <v>-0.0321896379959616</v>
+        <v>-0.0216910027158766</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0191422860305271</v>
+        <v>0.251569690442843</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0138937082889285</v>
+        <v>-0.0159585906984353</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.0183225640827699</v>
+        <v>-0.010616501495115</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.00139010832855707</v>
+        <v>0.213630250999655</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0203277996605591</v>
+        <v>-0.0213526778853232</v>
       </c>
     </row>
     <row r="108">
@@ -3451,22 +3451,22 @@
         <v>113</v>
       </c>
       <c r="B108" t="n">
-        <v>0.102112263485813</v>
+        <v>0.0529217814583625</v>
       </c>
       <c r="C108" t="n">
-        <v>0.178794583784247</v>
+        <v>0.0110355771214506</v>
       </c>
       <c r="D108" t="n">
-        <v>0.0669838144096066</v>
+        <v>-0.055163833839839</v>
       </c>
       <c r="E108" t="n">
-        <v>0.365371521792395</v>
+        <v>0.0437323481231954</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.00217462071176539</v>
+        <v>-0.177391958009638</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0238353581025469</v>
+        <v>-0.010605559292029</v>
       </c>
     </row>
     <row r="109">
@@ -3474,22 +3474,22 @@
         <v>114</v>
       </c>
       <c r="B109" t="n">
-        <v>0.118046775221005</v>
+        <v>0.162533587839162</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0207150813409663</v>
+        <v>0.183856172928122</v>
       </c>
       <c r="D109" t="n">
-        <v>0.0317082661521877</v>
+        <v>0.0605100151391801</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.0621753806464647</v>
+        <v>-0.0030959531301365</v>
       </c>
       <c r="F109" t="n">
-        <v>0.188434674336212</v>
+        <v>-0.0659226343707343</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.0333397981056795</v>
+        <v>0.00442576095780489</v>
       </c>
     </row>
     <row r="110">
@@ -3497,22 +3497,22 @@
         <v>115</v>
       </c>
       <c r="B110" t="n">
-        <v>0.011809992050328</v>
+        <v>0.00465455908839999</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.0218071018459441</v>
+        <v>-0.00286262586205472</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.00221192414393415</v>
+        <v>-0.00567439889625549</v>
       </c>
       <c r="E110" t="n">
-        <v>0.000375479326064364</v>
+        <v>-0.0142015640524306</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.0149856350553797</v>
+        <v>0.00665593497996421</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0905921423198863</v>
+        <v>0.0883691957259457</v>
       </c>
     </row>
     <row r="111">
@@ -3520,22 +3520,22 @@
         <v>116</v>
       </c>
       <c r="B111" t="n">
-        <v>0.00476069909626213</v>
+        <v>0.00241454689790139</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.0220721706942494</v>
+        <v>-0.00205463121649567</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.0122270365082954</v>
+        <v>0.0017046314614328</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.0092900998365682</v>
+        <v>-0.0142006125867433</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.0186419734758128</v>
+        <v>0.00999992504495582</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0463993934844458</v>
+        <v>0.0439315775764718</v>
       </c>
     </row>
     <row r="112">
@@ -3543,22 +3543,22 @@
         <v>117</v>
       </c>
       <c r="B112" t="n">
-        <v>0.0965376163651931</v>
+        <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.261017303343067</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.230199463999935</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>0.0865599335746182</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.0264554691311173</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0184882675174324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3566,22 +3566,22 @@
         <v>118</v>
       </c>
       <c r="B113" t="n">
-        <v>0.0222733162321837</v>
+        <v>0.0983431634932607</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0214875176853009</v>
+        <v>0.0854717330113679</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.0144790670807686</v>
+        <v>-0.170758641663904</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.0134282135463501</v>
+        <v>0.0930185077749976</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.00261155786870762</v>
+        <v>0.12294756510716</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0893224830216871</v>
+        <v>-0.0429141061523367</v>
       </c>
     </row>
     <row r="114">
@@ -3589,22 +3589,22 @@
         <v>119</v>
       </c>
       <c r="B114" t="n">
-        <v>0.0243547771728981</v>
+        <v>0.00913936440034367</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.03150573223893</v>
+        <v>-0.00519352534560136</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00533829201957185</v>
+        <v>-0.0146427675240177</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.0145606881946141</v>
+        <v>-0.0164669340060114</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.0117127960253572</v>
+        <v>0.0153262306823988</v>
       </c>
       <c r="G114" t="n">
-        <v>0.094433037230671</v>
+        <v>0.0874414610913162</v>
       </c>
     </row>
     <row r="115">
@@ -3612,22 +3612,22 @@
         <v>120</v>
       </c>
       <c r="B115" t="n">
-        <v>-0.00281590895334617</v>
+        <v>-0.000771712319715831</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.0178197742238294</v>
+        <v>-0.00378751419471354</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.0110055692444259</v>
+        <v>0.00596652436195192</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.0152392502180126</v>
+        <v>-0.0109160818518857</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.0230843983494457</v>
+        <v>0.00979116732821159</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0904948018378706</v>
+        <v>0.087688760082343</v>
       </c>
     </row>
     <row r="116">
@@ -3635,22 +3635,22 @@
         <v>121</v>
       </c>
       <c r="B116" t="n">
-        <v>0.00852118779704109</v>
+        <v>0.00427451044212488</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.022359076417885</v>
+        <v>-0.00412412840175225</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.0110247204264064</v>
+        <v>0.000759381565796883</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.0143262737563715</v>
+        <v>-0.0142223659589028</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.0244193586574639</v>
+        <v>0.0116163339645214</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0463414221184031</v>
+        <v>0.0429729412005636</v>
       </c>
     </row>
     <row r="117">
@@ -3658,22 +3658,22 @@
         <v>122</v>
       </c>
       <c r="B117" t="n">
-        <v>0.0186864802532223</v>
+        <v>0.00735684219782732</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.0237554663482267</v>
+        <v>-0.00257873943895695</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.000130874954076214</v>
+        <v>-0.00988629969448517</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.0137521065678475</v>
+        <v>-0.0122927979246217</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.00624037043541169</v>
+        <v>0.0129881941174982</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.0448114459698023</v>
+        <v>-0.04092764431354</v>
       </c>
     </row>
     <row r="118">
@@ -3704,22 +3704,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="n">
-        <v>0.00437371785159518</v>
+        <v>0.000237496153500978</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.0225902532313866</v>
+        <v>-0.00154136209721116</v>
       </c>
       <c r="D119" t="n">
-        <v>0.00249407757036373</v>
+        <v>-0.00567714858217817</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.0157217262923958</v>
+        <v>-0.00954257500206671</v>
       </c>
       <c r="F119" t="n">
-        <v>0.000895720509625823</v>
+        <v>0.012542997269449</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.044363018973753</v>
+        <v>-0.0424381320647815</v>
       </c>
     </row>
     <row r="120">
@@ -3727,22 +3727,22 @@
         <v>125</v>
       </c>
       <c r="B120" t="n">
-        <v>0.0304961359630437</v>
+        <v>-0.0279019867543447</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.0604695115560925</v>
+        <v>-0.147453098622535</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.000650686986294585</v>
+        <v>-0.223684385220838</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.018405850623779</v>
+        <v>-0.269922268733227</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.0190717132582681</v>
+        <v>-0.121997865697709</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0899260121506821</v>
+        <v>-0.0028635999571273</v>
       </c>
     </row>
     <row r="121">
@@ -3750,22 +3750,22 @@
         <v>126</v>
       </c>
       <c r="B121" t="n">
-        <v>0.00949897952855844</v>
+        <v>0.00398933746926226</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.0186777082904124</v>
+        <v>0.00162860976327089</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.00890958566006731</v>
+        <v>-0.00351999858584925</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.000436878326329391</v>
+        <v>-0.0118256201373089</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.00199203742021849</v>
+        <v>0.00711669527582424</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.0888783508285495</v>
+        <v>-0.082782522146948</v>
       </c>
     </row>
     <row r="122">
@@ -3773,22 +3773,22 @@
         <v>127</v>
       </c>
       <c r="B122" t="n">
-        <v>-0.0116832562513509</v>
+        <v>-0.00590139353400529</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.0193913163288249</v>
+        <v>0.00183284220408217</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.0100796930213195</v>
+        <v>0.00556353268933783</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.0039451430065742</v>
+        <v>-0.0107499180768635</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.00226787560494046</v>
+        <v>0.00707175135274497</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0902257710905345</v>
+        <v>0.0857591087987099</v>
       </c>
     </row>
     <row r="123">
@@ -3796,22 +3796,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="n">
-        <v>0.0420444127228009</v>
+        <v>0.0181912762443635</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.0354082084124411</v>
+        <v>-0.00120346271458516</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.00796990046096838</v>
+        <v>-0.0182469566657982</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.0256439129387366</v>
+        <v>-0.0186699663287584</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.0030945516940245</v>
+        <v>0.0230916321986965</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0466706044676657</v>
+        <v>0.0461927366183071</v>
       </c>
     </row>
     <row r="124">
@@ -3819,22 +3819,22 @@
         <v>129</v>
       </c>
       <c r="B124" t="n">
-        <v>0.214509476937469</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>0.169949706522856</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.0986900598217087</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.0914008266838585</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.0683879583768455</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>-0.00672647672479234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3842,22 +3842,22 @@
         <v>130</v>
       </c>
       <c r="B125" t="n">
-        <v>0.0162325684935257</v>
+        <v>0.00562021591678684</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.0150534475190431</v>
+        <v>-0.00364173229038207</v>
       </c>
       <c r="D125" t="n">
-        <v>0.0113617341823124</v>
+        <v>-0.0125891092186781</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.000449901553248007</v>
+        <v>-0.00774466833943145</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.00372098339390614</v>
+        <v>0.00493080642851767</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.0450115581503963</v>
+        <v>-0.0440963726417288</v>
       </c>
     </row>
     <row r="126">
@@ -3865,22 +3865,22 @@
         <v>131</v>
       </c>
       <c r="B126" t="n">
-        <v>0.0111430659700834</v>
+        <v>0.00610357475822569</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.0179441122518211</v>
+        <v>0.00119487577169756</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.0186601092883804</v>
+        <v>0.000945879926245298</v>
       </c>
       <c r="E126" t="n">
-        <v>0.000265083979337304</v>
+        <v>-0.0141359040698365</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.0139729795998599</v>
+        <v>0.00668644436875768</v>
       </c>
       <c r="G126" t="n">
-        <v>0.137145478603422</v>
+        <v>0.126639107358889</v>
       </c>
     </row>
     <row r="127">
@@ -3888,22 +3888,22 @@
         <v>132</v>
       </c>
       <c r="B127" t="n">
-        <v>-0.010741922669771</v>
+        <v>-0.0051581268402467</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.00786290563955333</v>
+        <v>0.00111286013540073</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.00366024631782151</v>
+        <v>0.00407247157134736</v>
       </c>
       <c r="E127" t="n">
-        <v>0.0260054036229405</v>
+        <v>-0.00901584952846828</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.00910867969887503</v>
+        <v>-0.00753523191172577</v>
       </c>
       <c r="G127" t="n">
-        <v>0.090326113640403</v>
+        <v>0.0842608436184606</v>
       </c>
     </row>
     <row r="128">
@@ -3911,22 +3911,22 @@
         <v>133</v>
       </c>
       <c r="B128" t="n">
-        <v>0.131481738008626</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0.106163932687775</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0.271126731888413</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.0842559256894294</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.273243057178281</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.00668424852547456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3934,22 +3934,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="n">
-        <v>0.0108140611444156</v>
+        <v>0.00489312513113306</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.0322413778444468</v>
+        <v>-0.000045635946710761</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.0177226768573701</v>
+        <v>-0.000867239664407625</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.0142776366806685</v>
+        <v>-0.0194357489258649</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.0137446492311143</v>
+        <v>0.0159905852602478</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0868436862334136</v>
+        <v>-0.0832857135811692</v>
       </c>
     </row>
     <row r="130">
@@ -3957,22 +3957,22 @@
         <v>135</v>
       </c>
       <c r="B130" t="n">
-        <v>0.0144635615092941</v>
+        <v>0.00561482159213791</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.0262740442653458</v>
+        <v>0.00267963439142147</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.00904825040094726</v>
+        <v>-0.0073069661310748</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.00420256093180313</v>
+        <v>-0.0150130535351663</v>
       </c>
       <c r="F130" t="n">
-        <v>0.00379896578787164</v>
+        <v>0.0114931932949195</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0924898222144486</v>
+        <v>0.0845532144163965</v>
       </c>
     </row>
     <row r="131">
@@ -3980,22 +3980,22 @@
         <v>136</v>
       </c>
       <c r="B131" t="n">
-        <v>0.0290468866011963</v>
+        <v>0.0135740937491899</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.000775207108102059</v>
+        <v>-0.00102321189577379</v>
       </c>
       <c r="D131" t="n">
-        <v>0.00165286839185729</v>
+        <v>-0.0123906266343266</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0113428594888185</v>
+        <v>-0.00397416297801674</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.0052142683942725</v>
+        <v>-0.00198802005191114</v>
       </c>
       <c r="G131" t="n">
-        <v>0.135341549223006</v>
+        <v>0.125363865611847</v>
       </c>
     </row>
     <row r="132">
@@ -4003,22 +4003,22 @@
         <v>137</v>
       </c>
       <c r="B132" t="n">
-        <v>0.00251771681973988</v>
+        <v>0.0981523999726944</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.0395014003938543</v>
+        <v>0.0960473315199927</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.0115262332304485</v>
+        <v>-0.199632141744517</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.00446122289397388</v>
+        <v>0.0718668639783643</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.0181230053340054</v>
+        <v>0.155502108750509</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.132936556880731</v>
+        <v>-0.0164355130433886</v>
       </c>
     </row>
     <row r="133">
@@ -4026,22 +4026,22 @@
         <v>138</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.000707331909900875</v>
+        <v>-0.000682472721836959</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.0163837456400542</v>
+        <v>-0.00742508525369083</v>
       </c>
       <c r="D133" t="n">
-        <v>0.00140592151005861</v>
+        <v>0.00130359832821118</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.00942976164485681</v>
+        <v>-0.0100266112894262</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.0281597220717033</v>
+        <v>0.00630675857412337</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.0436677396825602</v>
+        <v>-0.0393682355847545</v>
       </c>
     </row>
     <row r="134">
@@ -4049,22 +4049,22 @@
         <v>139</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.00402022943406505</v>
+        <v>-0.00234865802329089</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.0021720604488526</v>
+        <v>-0.0033915037019674</v>
       </c>
       <c r="D134" t="n">
-        <v>0.00578485473186406</v>
+        <v>0.000520697559276403</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.0114269888282955</v>
+        <v>0.00101808816904254</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.00507351656361396</v>
+        <v>0.00353652755803408</v>
       </c>
       <c r="G134" t="n">
-        <v>0.090111504531493</v>
+        <v>0.084778169291793</v>
       </c>
     </row>
     <row r="135">
@@ -4072,22 +4072,22 @@
         <v>140</v>
       </c>
       <c r="B135" t="n">
-        <v>0.00630567365043033</v>
+        <v>0.0019982569205158</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.0271916287943555</v>
+        <v>0.00175995727761081</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.0114633126796665</v>
+        <v>-0.00215389020670077</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.0318278728344858</v>
+        <v>-0.0109048893103006</v>
       </c>
       <c r="F135" t="n">
-        <v>0.00673209393624788</v>
+        <v>0.0209667085213112</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0478680868965315</v>
+        <v>0.0445132879612684</v>
       </c>
     </row>
     <row r="136">
@@ -4095,22 +4095,22 @@
         <v>141</v>
       </c>
       <c r="B136" t="n">
-        <v>0.0091515233444982</v>
+        <v>0.00151327889112393</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.0346822009174581</v>
+        <v>-0.00787011885682969</v>
       </c>
       <c r="D136" t="n">
-        <v>0.0102159231494646</v>
+        <v>-0.0096964144059843</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.0208081615583702</v>
+        <v>-0.0163421580109105</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.0171267454475928</v>
+        <v>0.0166445148668838</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0917417876768983</v>
+        <v>0.088068834739345</v>
       </c>
     </row>
     <row r="137">
@@ -4118,22 +4118,22 @@
         <v>142</v>
       </c>
       <c r="B137" t="n">
-        <v>0.0112538267646298</v>
+        <v>0.000430200011720803</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.0235772301910244</v>
+        <v>0.00153561062729504</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0225251032948556</v>
+        <v>-0.0202496469329572</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.0172242632876573</v>
+        <v>-0.0040041036476172</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0356519947646334</v>
+        <v>0.0146832649698847</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.134734287456648</v>
+        <v>-0.123915168324698</v>
       </c>
     </row>
     <row r="138">
@@ -4141,22 +4141,22 @@
         <v>143</v>
       </c>
       <c r="B138" t="n">
-        <v>0.00539392881840961</v>
+        <v>0.000288431706266048</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.0290105251357674</v>
+        <v>-0.00728340144971953</v>
       </c>
       <c r="D138" t="n">
-        <v>0.0100501667305141</v>
+        <v>-0.0077645955911067</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0126072903997971</v>
+        <v>-0.0191779799104344</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.0267247106427512</v>
+        <v>0.0026196294763216</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0908153969432733</v>
+        <v>0.0871728534183084</v>
       </c>
     </row>
     <row r="139">
@@ -4164,22 +4164,22 @@
         <v>144</v>
       </c>
       <c r="B139" t="n">
-        <v>0.00117193934077849</v>
+        <v>0.0000710991708298249</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.034119468087123</v>
+        <v>-0.00300445576516616</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.0126648634652915</v>
+        <v>0.0019548885373677</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.00590892721676485</v>
+        <v>-0.0217063585414255</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.0250800063105067</v>
+        <v>0.0119297664494688</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.0880124922395717</v>
+        <v>-0.0830145143470084</v>
       </c>
     </row>
     <row r="140">
@@ -4187,22 +4187,22 @@
         <v>145</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.0768668572464956</v>
+        <v>0.0642903947859444</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.0801353303277584</v>
+        <v>0.127538643741976</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.0241616688201888</v>
+        <v>0.108713545250162</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.176583962180606</v>
+        <v>-0.0454551778020649</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.118437358294827</v>
+        <v>0.14622214196541</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.00668287888591436</v>
+        <v>0.0361571220599572</v>
       </c>
     </row>
     <row r="141">
@@ -4210,22 +4210,22 @@
         <v>146</v>
       </c>
       <c r="B141" t="n">
-        <v>0.313856763331517</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0288033064478646</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.151019241840547</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>0.00697757587062522</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.166352097971467</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.039233682223544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -4233,22 +4233,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="n">
-        <v>0.0123286847584207</v>
+        <v>0.00552666002469074</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.0349276982796806</v>
+        <v>0.00736383917185837</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.0247938095553362</v>
+        <v>-0.00316823487229469</v>
       </c>
       <c r="E142" t="n">
-        <v>0.0364733716579921</v>
+        <v>-0.0288802931623972</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.00689905669570953</v>
+        <v>0.000579683267846792</v>
       </c>
       <c r="G142" t="n">
-        <v>0.00152442136626006</v>
+        <v>-0.000808952133053042</v>
       </c>
     </row>
     <row r="143">
@@ -4256,22 +4256,22 @@
         <v>148</v>
       </c>
       <c r="B143" t="n">
-        <v>0.04095289526286</v>
+        <v>0.219963596131201</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.0145368468356082</v>
+        <v>-0.0162855417439155</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.00988947313524216</v>
+        <v>-0.0040980735493725</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.0361506491302771</v>
+        <v>0.0482072108053491</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0446283954238428</v>
+        <v>0.107176507323956</v>
       </c>
       <c r="G143" t="n">
-        <v>0.110506827519375</v>
+        <v>-0.00696710983001448</v>
       </c>
     </row>
     <row r="144">
@@ -4279,22 +4279,22 @@
         <v>149</v>
       </c>
       <c r="B144" t="n">
-        <v>0.239843595158932</v>
+        <v>0.0722387174376161</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0230257412724803</v>
+        <v>-0.114569441125373</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.0213481112316045</v>
+        <v>-0.0656781707601697</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.152980167029774</v>
+        <v>-0.156727521804759</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0900904769824454</v>
+        <v>0.19083076574627</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.017715265611388</v>
+        <v>0.00918240089688057</v>
       </c>
     </row>
     <row r="145">
@@ -4302,22 +4302,22 @@
         <v>150</v>
       </c>
       <c r="B145" t="n">
-        <v>0.00769012493213039</v>
+        <v>0.00300610816446699</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.0256962683773861</v>
+        <v>-0.00336377397247927</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.00660448741682842</v>
+        <v>-0.00208572046765627</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.00974522854986658</v>
+        <v>-0.0154653298389081</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.0184029807305374</v>
+        <v>0.0111027740077475</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0896878599438543</v>
+        <v>-0.080943836686363</v>
       </c>
     </row>
     <row r="146">
@@ -4325,22 +4325,22 @@
         <v>151</v>
       </c>
       <c r="B146" t="n">
-        <v>0.0113824040029047</v>
+        <v>0.00409120253513048</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.039748293937046</v>
+        <v>0.00055906992482723</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.0139742254474733</v>
+        <v>-0.00455453222065454</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.00889057423421992</v>
+        <v>-0.0233763151466203</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.00945366289324713</v>
+        <v>0.0165291299300553</v>
       </c>
       <c r="G146" t="n">
-        <v>0.00375028430585353</v>
+        <v>0.00119941727476114</v>
       </c>
     </row>
     <row r="147">
@@ -4394,22 +4394,22 @@
         <v>154</v>
       </c>
       <c r="B149" t="n">
-        <v>0.0716727641892187</v>
+        <v>0.192563342503957</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.063301906073406</v>
+        <v>-0.0216300023794778</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.0065978169011253</v>
+        <v>-0.0147002365833531</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.0433476019505738</v>
+        <v>0.00728818429271977</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0349096270301796</v>
+        <v>0.104096878254648</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0231163887022238</v>
+        <v>-0.0123297019994375</v>
       </c>
     </row>
     <row r="150">
@@ -4417,22 +4417,22 @@
         <v>155</v>
       </c>
       <c r="B150" t="n">
-        <v>0.0323462625721955</v>
+        <v>0.1280691600202</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.0223677646956597</v>
+        <v>-0.099687694246069</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.0237926721639066</v>
+        <v>0.168696180109174</v>
       </c>
       <c r="E150" t="n">
-        <v>0.00360138306846486</v>
+        <v>-0.0492641862213483</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.00742150933800261</v>
+        <v>-0.0266801269810652</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.130769486204934</v>
+        <v>-0.0239136815279013</v>
       </c>
     </row>
     <row r="151">
@@ -4440,22 +4440,22 @@
         <v>156</v>
       </c>
       <c r="B151" t="n">
-        <v>0.010569973277645</v>
+        <v>0.00470699841040271</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.0251548764698937</v>
+        <v>-0.000032934091305751</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.0127116663882189</v>
+        <v>-0.0021451556106213</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.00602850375012164</v>
+        <v>-0.0159614412070182</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.0112833328019576</v>
+        <v>0.0107719944033984</v>
       </c>
       <c r="G151" t="n">
-        <v>0.000586649691871163</v>
+        <v>0.00509504666621332</v>
       </c>
     </row>
     <row r="152">
@@ -4463,22 +4463,22 @@
         <v>157</v>
       </c>
       <c r="B152" t="n">
-        <v>0.275730656573302</v>
+        <v>0.170279063824519</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.0258152712970385</v>
+        <v>-0.119864965364157</v>
       </c>
       <c r="D152" t="n">
-        <v>0.0118119446927091</v>
+        <v>-0.161220684719129</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.178246442077461</v>
+        <v>-0.147386749725546</v>
       </c>
       <c r="F152" t="n">
-        <v>0.284963744790194</v>
+        <v>-0.0157235992904741</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.038010481133059</v>
+        <v>-0.0191672773366942</v>
       </c>
     </row>
     <row r="153">
@@ -4486,22 +4486,22 @@
         <v>158</v>
       </c>
       <c r="B153" t="n">
-        <v>0.03630314984074</v>
+        <v>0.0999010888519516</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.0285378657044345</v>
+        <v>0.0762160422767331</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.0147695612479632</v>
+        <v>-0.175665842572325</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.0144150257050714</v>
+        <v>0.0600353009959894</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.0334105842595635</v>
+        <v>0.134295659930661</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.0181160016597424</v>
+        <v>-0.0501432886846296</v>
       </c>
     </row>
     <row r="154">
@@ -4509,22 +4509,22 @@
         <v>159</v>
       </c>
       <c r="B154" t="n">
-        <v>0.0252057332452632</v>
+        <v>0.0140018751615711</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.0219190550367118</v>
+        <v>0.00121391501637242</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.0325599497885203</v>
+        <v>0.00153771896278626</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.0265162941470842</v>
+        <v>-0.0151658253847681</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.0178362898394223</v>
+        <v>0.018796645899399</v>
       </c>
       <c r="G154" t="n">
-        <v>-0.0401979143482668</v>
+        <v>-0.0420761947529749</v>
       </c>
     </row>
     <row r="155">
@@ -4532,22 +4532,22 @@
         <v>160</v>
       </c>
       <c r="B155" t="n">
-        <v>0.00131445719758808</v>
+        <v>0.000274422745921897</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.024854222947092</v>
+        <v>-0.00777526350258392</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.0034284326475756</v>
+        <v>0.00171764090145588</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.0158177176411496</v>
+        <v>-0.0147910231159678</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.0325270698855993</v>
+        <v>0.0113111973166867</v>
       </c>
       <c r="G155" t="n">
-        <v>0.047031508146476</v>
+        <v>0.042229688621679</v>
       </c>
     </row>
     <row r="156">
@@ -4555,22 +4555,22 @@
         <v>161</v>
       </c>
       <c r="B156" t="n">
-        <v>0.134289331038609</v>
+        <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>0.141126104150319</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0.228191303736618</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>0.0601418932465719</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.207801658878756</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0102436628066197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -4578,22 +4578,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="n">
-        <v>-0.0140076311595171</v>
+        <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.0185973187773954</v>
+        <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>0.207227079200689</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.272568120973264</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.450438765905678</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.00069804515976577</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -4601,22 +4601,22 @@
         <v>163</v>
       </c>
       <c r="B158" t="n">
-        <v>0.0135455556933377</v>
+        <v>0.00534716633673498</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.0242448586669253</v>
+        <v>-0.00479114567644085</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.0000511175888186211</v>
+        <v>-0.00680247469159078</v>
       </c>
       <c r="E158" t="n">
-        <v>0.00903254121541002</v>
+        <v>-0.0175819923237618</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.0242711726894863</v>
+        <v>0.00382906628238757</v>
       </c>
       <c r="G158" t="n">
-        <v>0.000487539656902435</v>
+        <v>0.002046143396637</v>
       </c>
     </row>
     <row r="159">
@@ -4624,22 +4624,22 @@
         <v>164</v>
       </c>
       <c r="B159" t="n">
-        <v>0.0756023172089219</v>
+        <v>0.210032271786546</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.0279033355593058</v>
+        <v>-0.0251173832019417</v>
       </c>
       <c r="D159" t="n">
-        <v>0.00324609401393094</v>
+        <v>-0.0139843529449832</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.0514019953908408</v>
+        <v>0.0328442081488694</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0394286576591415</v>
+        <v>0.10209882782383</v>
       </c>
       <c r="G159" t="n">
-        <v>0.109468647067364</v>
+        <v>0.0119439841783297</v>
       </c>
     </row>
     <row r="160">
@@ -4647,22 +4647,22 @@
         <v>165</v>
       </c>
       <c r="B160" t="n">
-        <v>0.00804547293343398</v>
+        <v>0.0023911913986537</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.0261185571826339</v>
+        <v>-0.00324989357050495</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.000860285832822755</v>
+        <v>-0.00516118099732806</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.0121553858588616</v>
+        <v>-0.0138475789051479</v>
       </c>
       <c r="F160" t="n">
-        <v>-0.0111705848740072</v>
+        <v>0.0121404267998257</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.133584017269234</v>
+        <v>-0.12457936486414</v>
       </c>
     </row>
     <row r="161">
@@ -4670,22 +4670,22 @@
         <v>166</v>
       </c>
       <c r="B161" t="n">
-        <v>0.05921219389588</v>
+        <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>0.103678238060376</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>0.0388421377737683</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>0.211869256971371</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.00126100488657701</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>-0.00938885395942997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -4693,22 +4693,22 @@
         <v>167</v>
       </c>
       <c r="B162" t="n">
-        <v>0.0119802055364456</v>
+        <v>0.0013722134917145</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.00719967758988814</v>
+        <v>-0.0295193038986194</v>
       </c>
       <c r="D162" t="n">
-        <v>0.0617692393189657</v>
+        <v>-0.0190204637539225</v>
       </c>
       <c r="E162" t="n">
-        <v>-0.0352848548327605</v>
+        <v>0.00360362615342846</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.0524072667938247</v>
+        <v>0.00732596300078276</v>
       </c>
       <c r="G162" t="n">
-        <v>0.045087396443126</v>
+        <v>0.045233340114455</v>
       </c>
     </row>
     <row r="163">
@@ -4716,22 +4716,22 @@
         <v>168</v>
       </c>
       <c r="B163" t="n">
-        <v>0.0228971976097806</v>
+        <v>0.001692939318381</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.0759280161201655</v>
+        <v>-0.00695428292215036</v>
       </c>
       <c r="D163" t="n">
-        <v>0.0359089161231808</v>
+        <v>-0.0352842673600772</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.00909077141617366</v>
+        <v>-0.0349886805862225</v>
       </c>
       <c r="F163" t="n">
-        <v>0.00818659323652816</v>
+        <v>0.0262136155637684</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0201157436286898</v>
+        <v>0.0162160995450509</v>
       </c>
     </row>
     <row r="164">
@@ -4739,22 +4739,22 @@
         <v>169</v>
       </c>
       <c r="B164" t="n">
-        <v>0.194572083055346</v>
+        <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>0.127486529625524</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.12008712775504</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.180890457054034</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0557591658429752</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0496565070502339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -4762,22 +4762,22 @@
         <v>170</v>
       </c>
       <c r="B165" t="n">
-        <v>-0.00318934750908519</v>
+        <v>-0.00173599587875068</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.0143178273458585</v>
+        <v>0.00215785559525962</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.00838839475980648</v>
+        <v>0.00177129929193106</v>
       </c>
       <c r="E165" t="n">
-        <v>0.00883409368038521</v>
+        <v>-0.0102678841727596</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.00303871323102027</v>
+        <v>0.00158850189369932</v>
       </c>
       <c r="G165" t="n">
-        <v>0.134966746486175</v>
+        <v>0.127293513343487</v>
       </c>
     </row>
     <row r="166">
@@ -4785,22 +4785,22 @@
         <v>171</v>
       </c>
       <c r="B166" t="n">
-        <v>0.00535810106262242</v>
+        <v>0.000679193565959966</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.0206305835598782</v>
+        <v>-0.0037986401521973</v>
       </c>
       <c r="D166" t="n">
-        <v>0.00606923941626352</v>
+        <v>-0.00615809053084277</v>
       </c>
       <c r="E166" t="n">
-        <v>-0.0220376154566832</v>
+        <v>-0.00750380267564219</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.00289270388505604</v>
+        <v>0.0136605101185963</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0884932236683335</v>
+        <v>0.0863272547806411</v>
       </c>
     </row>
     <row r="167">
@@ -4808,22 +4808,22 @@
         <v>172</v>
       </c>
       <c r="B167" t="n">
-        <v>-0.0204461246144318</v>
+        <v>-0.146678615615069</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.0265654865241478</v>
+        <v>0.103835167488591</v>
       </c>
       <c r="D167" t="n">
-        <v>0.0246342797510027</v>
+        <v>0.132688531436518</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.0514343796538591</v>
+        <v>0.103556442362155</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.0162842389271702</v>
+        <v>0.015787634087283</v>
       </c>
       <c r="G167" t="n">
-        <v>-0.0678586414003098</v>
+        <v>0.0150475469391659</v>
       </c>
     </row>
     <row r="168">
@@ -4831,22 +4831,22 @@
         <v>173</v>
       </c>
       <c r="B168" t="n">
-        <v>0.108094922544286</v>
+        <v>0.0361295533781049</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.0339966605457714</v>
+        <v>-0.199144892775621</v>
       </c>
       <c r="D168" t="n">
-        <v>0.00914318971006151</v>
+        <v>0.0318906842556929</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.05165760557987</v>
+        <v>-0.260083736886309</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0123566251507213</v>
+        <v>0.161476823346145</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0500412371366979</v>
+        <v>0.0596102123811484</v>
       </c>
     </row>
     <row r="169">
@@ -4854,22 +4854,22 @@
         <v>174</v>
       </c>
       <c r="B169" t="n">
-        <v>0.00270270443583085</v>
+        <v>0.0035007310154449</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.0154034305309216</v>
+        <v>-0.0019988438511542</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.0248867632936474</v>
+        <v>0.00982487026368794</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.011239409351952</v>
+        <v>-0.0131017384802903</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.0305063270807039</v>
+        <v>0.00858492694623437</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0469565904123897</v>
+        <v>0.0456158176566385</v>
       </c>
     </row>
     <row r="170">
@@ -4877,22 +4877,22 @@
         <v>175</v>
       </c>
       <c r="B170" t="n">
-        <v>-0.0120893882551543</v>
+        <v>0.0263984562120878</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.0274594215641991</v>
+        <v>-0.220143979456439</v>
       </c>
       <c r="D170" t="n">
-        <v>0.0224354703790115</v>
+        <v>-0.0794717502656586</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.038064376653763</v>
+        <v>0.0610332614945429</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.123458533861636</v>
+        <v>0.141998966084677</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.0128942362094502</v>
+        <v>0.0317934483676582</v>
       </c>
     </row>
     <row r="171">
@@ -4900,22 +4900,22 @@
         <v>176</v>
       </c>
       <c r="B171" t="n">
-        <v>0.0101674981543915</v>
+        <v>0.00647386155235838</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.0165023705725229</v>
+        <v>-0.00167460194134018</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.0212626244363961</v>
+        <v>0.00453533813520346</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.00214803253489618</v>
+        <v>-0.014754576953735</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.0282672412381016</v>
+        <v>0.00625149416434362</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.0395642038249428</v>
+        <v>-0.0420709387389597</v>
       </c>
     </row>
     <row r="172">
@@ -4923,22 +4923,22 @@
         <v>177</v>
       </c>
       <c r="B172" t="n">
-        <v>0.0132434389748127</v>
+        <v>0.00524602962531251</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.0255879456924688</v>
+        <v>-0.00222927528377321</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.00486212513919511</v>
+        <v>-0.00587409598782059</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.00831799814247122</v>
+        <v>-0.0150152655922694</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.0118745097488933</v>
+        <v>0.0112821669676265</v>
       </c>
       <c r="G172" t="n">
-        <v>-0.0866382461306559</v>
+        <v>-0.0858416518090477</v>
       </c>
     </row>
     <row r="173">
@@ -4946,22 +4946,22 @@
         <v>178</v>
       </c>
       <c r="B173" t="n">
-        <v>0.00047612890357712</v>
+        <v>-0.00561630944043675</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.0662851729592737</v>
+        <v>-0.0168339789005277</v>
       </c>
       <c r="D173" t="n">
-        <v>0.0251550271692152</v>
+        <v>-0.0131426739505809</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.0532095769294253</v>
+        <v>-0.0273799768646239</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.0309362742573712</v>
+        <v>0.034881735216791</v>
       </c>
       <c r="G173" t="n">
-        <v>0.00281209161834143</v>
+        <v>0.00945358765376211</v>
       </c>
     </row>
     <row r="174">
@@ -4969,22 +4969,22 @@
         <v>179</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.00138845445336114</v>
+        <v>-0.00184942670403457</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.0257203388089959</v>
+        <v>-0.00962370054729871</v>
       </c>
       <c r="D174" t="n">
-        <v>0.00539311586116518</v>
+        <v>-0.000638237048413302</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.00722531991160824</v>
+        <v>-0.0154942582641064</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.0348312614104276</v>
+        <v>0.00767866696878579</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0911850693108336</v>
+        <v>0.0868115849988765</v>
       </c>
     </row>
     <row r="175">
@@ -4992,22 +4992,22 @@
         <v>180</v>
       </c>
       <c r="B175" t="n">
-        <v>0.00724228565063526</v>
+        <v>-0.00241482364655071</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.0506810917010356</v>
+        <v>-0.0132560702277984</v>
       </c>
       <c r="D175" t="n">
-        <v>0.0301868055361633</v>
+        <v>-0.017983660830321</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.045493109980518</v>
+        <v>-0.0179319620911765</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.0120271506266185</v>
+        <v>0.0287793298121077</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0497284598303042</v>
+        <v>0.0497364134535756</v>
       </c>
     </row>
     <row r="176">
@@ -5015,22 +5015,22 @@
         <v>181</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0334465438449992</v>
+        <v>0.0156296335373794</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.0505794164392866</v>
+        <v>0.000961959987618712</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.0301924200972623</v>
+        <v>-0.00766976104748562</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.0102033933027758</v>
+        <v>-0.0336576891554109</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.0229377456615612</v>
+        <v>0.0221980143916785</v>
       </c>
       <c r="G176" t="n">
-        <v>0.00390723096747295</v>
+        <v>0.00704306367132081</v>
       </c>
     </row>
     <row r="177">
@@ -5038,22 +5038,22 @@
         <v>182</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0109826905254251</v>
+        <v>0.0031512077124695</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.0485714521013111</v>
+        <v>-0.00610094310441529</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.0053684856578767</v>
+        <v>-0.00621229747323436</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.00692304912568427</v>
+        <v>-0.0294379912756791</v>
       </c>
       <c r="F177" t="n">
-        <v>-0.030719149555556</v>
+        <v>0.0165688964967107</v>
       </c>
       <c r="G177" t="n">
-        <v>-0.0875292326936379</v>
+        <v>-0.0859582683126255</v>
       </c>
     </row>
     <row r="178">
@@ -5153,22 +5153,22 @@
         <v>187</v>
       </c>
       <c r="B182" t="n">
-        <v>0.0331684492498082</v>
+        <v>0.015824382987037</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.0275495664939364</v>
+        <v>0.00678083668181395</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.025040733605349</v>
+        <v>-0.00989939522168111</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0145058676571732</v>
+        <v>-0.0220432824233872</v>
       </c>
       <c r="F182" t="n">
-        <v>-0.000365938723268601</v>
+        <v>0.00772760655775881</v>
       </c>
       <c r="G182" t="n">
-        <v>0.136110681511947</v>
+        <v>0.13346227330804</v>
       </c>
     </row>
     <row r="183">
@@ -5199,22 +5199,22 @@
         <v>189</v>
       </c>
       <c r="B184" t="n">
-        <v>0.181926261039064</v>
+        <v>-0.0853868130721877</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.197565826621037</v>
+        <v>0.0789545054760186</v>
       </c>
       <c r="D184" t="n">
-        <v>0.351430454773742</v>
+        <v>-0.134319951238945</v>
       </c>
       <c r="E184" t="n">
-        <v>0.061008650316839</v>
+        <v>0.0237241600556472</v>
       </c>
       <c r="F184" t="n">
-        <v>0.165207852638457</v>
+        <v>0.0273651180017951</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.00147991661918554</v>
+        <v>-0.0201138460583616</v>
       </c>
     </row>
     <row r="185">
@@ -5222,22 +5222,22 @@
         <v>190</v>
       </c>
       <c r="B185" t="n">
-        <v>0.0602003340719986</v>
+        <v>0.16616622600442</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.00333963573339389</v>
+        <v>0.196518050907383</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.0519661749653653</v>
+        <v>0.0736837752536366</v>
       </c>
       <c r="E185" t="n">
-        <v>-0.0638021723951743</v>
+        <v>-0.0215237699458484</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.0532852784078828</v>
+        <v>-0.035271295506929</v>
       </c>
       <c r="G185" t="n">
-        <v>-0.0217704371466962</v>
+        <v>0.0126582109057899</v>
       </c>
     </row>
     <row r="186">
@@ -5291,22 +5291,22 @@
         <v>193</v>
       </c>
       <c r="B188" t="n">
-        <v>-0.00203514569817034</v>
+        <v>0.000102544498781813</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.00615492910645531</v>
+        <v>-0.00632042598912509</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.00452373359101052</v>
+        <v>0.00566147713257327</v>
       </c>
       <c r="E188" t="n">
-        <v>0.00504771330302489</v>
+        <v>-0.00807533294709273</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.0342979613175415</v>
+        <v>-0.00186367592233866</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0450165425486919</v>
+        <v>0.0411876435135206</v>
       </c>
     </row>
     <row r="189">
@@ -5314,22 +5314,22 @@
         <v>194</v>
       </c>
       <c r="B189" t="n">
-        <v>-0.00485838695151525</v>
+        <v>-0.0257065969195537</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.0176177866150858</v>
+        <v>-0.174536382947788</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.00171497434194402</v>
+        <v>0.229300787271432</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.0521907585493003</v>
+        <v>0.14772459970164</v>
       </c>
       <c r="F189" t="n">
-        <v>0.0109606908309654</v>
+        <v>0.121868143599989</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.0213804289522527</v>
+        <v>0.0466104415939941</v>
       </c>
     </row>
     <row r="190">
@@ -5337,22 +5337,22 @@
         <v>195</v>
       </c>
       <c r="B190" t="n">
-        <v>-0.0376203582811347</v>
+        <v>-0.0546828262848597</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.0177241351364623</v>
+        <v>-0.261890697914285</v>
       </c>
       <c r="D190" t="n">
-        <v>0.0491925916066678</v>
+        <v>0.0887470039155848</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.0254284032292113</v>
+        <v>-0.0237061096039123</v>
       </c>
       <c r="F190" t="n">
-        <v>0.0662604430547759</v>
+        <v>0.00842405038233143</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.071382484274527</v>
+        <v>0.0258788985842077</v>
       </c>
     </row>
     <row r="191">
@@ -5360,22 +5360,22 @@
         <v>196</v>
       </c>
       <c r="B191" t="n">
-        <v>0.00333869125641026</v>
+        <v>0.00100226986140123</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.0310978952100145</v>
+        <v>-0.00459322715991572</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.00950350401865012</v>
+        <v>0.0011203107151089</v>
       </c>
       <c r="E191" t="n">
-        <v>-0.0293537592177329</v>
+        <v>-0.0157199165040054</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.0201341562441764</v>
+        <v>0.019237622931284</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.0883553405295857</v>
+        <v>-0.0801998523821433</v>
       </c>
     </row>
     <row r="192">
@@ -5383,22 +5383,22 @@
         <v>197</v>
       </c>
       <c r="B192" t="n">
-        <v>0.0861464650590501</v>
+        <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.232921827251147</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.205421169785922</v>
+        <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>0.0772427637429022</v>
+        <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.0236078456557613</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.0104582188567969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -5452,22 +5452,22 @@
         <v>200</v>
       </c>
       <c r="B195" t="n">
-        <v>0.00390364114465595</v>
+        <v>-0.000306152639484338</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.0319283292473076</v>
+        <v>-0.0103700895385006</v>
       </c>
       <c r="D195" t="n">
-        <v>0.00846929714750262</v>
+        <v>-0.00459310330933866</v>
       </c>
       <c r="E195" t="n">
-        <v>-0.0441736720971653</v>
+        <v>-0.011737392308563</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.021621880088475</v>
+        <v>0.0232111503049924</v>
       </c>
       <c r="G195" t="n">
-        <v>0.000763183225105008</v>
+        <v>0.00496672962681783</v>
       </c>
     </row>
     <row r="196">
@@ -5475,22 +5475,22 @@
         <v>201</v>
       </c>
       <c r="B196" t="n">
-        <v>0.0176056889003543</v>
+        <v>0.00884853686525674</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.0123815949380486</v>
+        <v>-0.00149181311436069</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.0107688608537126</v>
+        <v>-0.00300123087968164</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.0141929365141025</v>
+        <v>-0.00804351645372274</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.011862491784286</v>
+        <v>0.00993453160391071</v>
       </c>
       <c r="G196" t="n">
-        <v>-0.0873264911460706</v>
+        <v>-0.0852496838640714</v>
       </c>
     </row>
     <row r="197">
@@ -5498,22 +5498,22 @@
         <v>202</v>
       </c>
       <c r="B197" t="n">
-        <v>-0.00870073843305969</v>
+        <v>-0.0724943907237012</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.0510439015239408</v>
+        <v>-0.0869745208380237</v>
       </c>
       <c r="D197" t="n">
-        <v>0.0316629948948649</v>
+        <v>-0.00862864975221186</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.0475979359034207</v>
+        <v>0.232873682537695</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.0132890654163082</v>
+        <v>-0.0669391426708415</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.0701590586818464</v>
+        <v>-0.000831175838832046</v>
       </c>
     </row>
     <row r="198">
@@ -5521,22 +5521,22 @@
         <v>203</v>
       </c>
       <c r="B198" t="n">
-        <v>-0.00640303897805457</v>
+        <v>-0.0041923302990138</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.0313012640456741</v>
+        <v>-0.00361430259577544</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.00474935060073387</v>
+        <v>0.00201438334013711</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.00719271921703221</v>
+        <v>-0.0179921030640934</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.0195174460380881</v>
+        <v>0.0107466819340295</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0423377638580738</v>
+        <v>-0.0363522047412825</v>
       </c>
     </row>
     <row r="199">
@@ -5544,22 +5544,22 @@
         <v>204</v>
       </c>
       <c r="B199" t="n">
-        <v>-0.00107163900483453</v>
+        <v>-0.000663251980458538</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.0217792000279665</v>
+        <v>-0.00133742475812806</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.0109448855072378</v>
+        <v>0.00325444028003097</v>
       </c>
       <c r="E199" t="n">
-        <v>-0.0266356169245854</v>
+        <v>-0.0098787154770654</v>
       </c>
       <c r="F199" t="n">
-        <v>-0.00831144604062003</v>
+        <v>0.0159790943722114</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0498670386775258</v>
+        <v>0.0427026578315062</v>
       </c>
     </row>
     <row r="200">
@@ -5567,22 +5567,22 @@
         <v>205</v>
       </c>
       <c r="B200" t="n">
-        <v>-0.0157465445103613</v>
+        <v>-0.08069205978282</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.0401503251227725</v>
+        <v>-0.0208646802077071</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.0152622515779279</v>
+        <v>0.0868923585329041</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.00106653384693081</v>
+        <v>-0.0872937856516172</v>
       </c>
       <c r="F200" t="n">
-        <v>-0.0420289806758276</v>
+        <v>0.255104018507899</v>
       </c>
       <c r="G200" t="n">
-        <v>-0.0869047169750142</v>
+        <v>0.0111184126268038</v>
       </c>
     </row>
     <row r="201">
@@ -5590,22 +5590,22 @@
         <v>206</v>
       </c>
       <c r="B201" t="n">
-        <v>-0.0115599417038178</v>
+        <v>-0.0011265589071592</v>
       </c>
       <c r="C201" t="n">
-        <v>0.0190729901965494</v>
+        <v>-0.00145208966067017</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.0210964703345467</v>
+        <v>0.0189467408090165</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0109209268489965</v>
+        <v>0.00314812907721237</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.0317507954808862</v>
+        <v>-0.0110123222675611</v>
       </c>
       <c r="G201" t="n">
-        <v>0.000391379757051251</v>
+        <v>0.00234304304187126</v>
       </c>
     </row>
     <row r="202">
@@ -5613,22 +5613,22 @@
         <v>207</v>
       </c>
       <c r="B202" t="n">
-        <v>0.0222169794718591</v>
+        <v>0.010085697411692</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.046865541845208</v>
+        <v>-0.00351026654543121</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.0206795327343297</v>
+        <v>-0.00453634221024205</v>
       </c>
       <c r="E202" t="n">
-        <v>-0.00859891260017697</v>
+        <v>-0.0311829856944479</v>
       </c>
       <c r="F202" t="n">
-        <v>-0.0337758262152668</v>
+        <v>0.0183135444270866</v>
       </c>
       <c r="G202" t="n">
-        <v>0.00481038816814823</v>
+        <v>0.00911911098586148</v>
       </c>
     </row>
     <row r="203">
@@ -5636,22 +5636,22 @@
         <v>208</v>
       </c>
       <c r="B203" t="n">
-        <v>0.0195815087423474</v>
+        <v>0.0102205392393282</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.0129874861144194</v>
+        <v>-0.00505531484900226</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.0106638825123517</v>
+        <v>-0.00189334865916381</v>
       </c>
       <c r="E203" t="n">
-        <v>-0.0156341486874851</v>
+        <v>-0.00975914934556588</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.0266692726048657</v>
+        <v>0.00978865344488592</v>
       </c>
       <c r="G203" t="n">
-        <v>0.00116854720069754</v>
+        <v>0.00192520583914056</v>
       </c>
     </row>
     <row r="204">
@@ -5659,22 +5659,22 @@
         <v>209</v>
       </c>
       <c r="B204" t="n">
-        <v>-0.0133509041912366</v>
+        <v>-0.00498625790430875</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.000312377866283413</v>
+        <v>-0.0095686876507707</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.000113855478896636</v>
+        <v>0.0111508796374048</v>
       </c>
       <c r="E204" t="n">
-        <v>-0.0149014421800251</v>
+        <v>-0.001043584361075</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.037219716984718</v>
+        <v>0.00180950797859521</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.0442897273503462</v>
+        <v>-0.0391993387798132</v>
       </c>
     </row>
     <row r="205">
@@ -5682,22 +5682,22 @@
         <v>210</v>
       </c>
       <c r="B205" t="n">
-        <v>-0.0169323211322007</v>
+        <v>-0.00770469019420048</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.0332534750486684</v>
+        <v>-0.00277685864649165</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.0181484061334641</v>
+        <v>0.0121018875574311</v>
       </c>
       <c r="E205" t="n">
-        <v>-0.00612161707280465</v>
+        <v>-0.021550405888741</v>
       </c>
       <c r="F205" t="n">
-        <v>-0.0306094349475299</v>
+        <v>0.0104612534128656</v>
       </c>
       <c r="G205" t="n">
-        <v>-0.0414312663064985</v>
+        <v>-0.0391314829253269</v>
       </c>
     </row>
     <row r="206">
@@ -5705,22 +5705,22 @@
         <v>211</v>
       </c>
       <c r="B206" t="n">
-        <v>0.025883678675822</v>
+        <v>0.009076606192552</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.0669833615570625</v>
+        <v>0.0172104365283873</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.0344711444490173</v>
+        <v>-0.0144751225211092</v>
       </c>
       <c r="E206" t="n">
-        <v>-0.0154997690162444</v>
+        <v>-0.0349165539261203</v>
       </c>
       <c r="F206" t="n">
-        <v>0.044333352170312</v>
+        <v>0.0331965292586965</v>
       </c>
       <c r="G206" t="n">
-        <v>0.00187186046841901</v>
+        <v>-0.00204558193863894</v>
       </c>
     </row>
     <row r="207">
@@ -5728,22 +5728,22 @@
         <v>212</v>
       </c>
       <c r="B207" t="n">
-        <v>0.00444773335667908</v>
+        <v>0.00180765871419316</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.0430650023446195</v>
+        <v>0.0037554863503821</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.0258620384500507</v>
+        <v>0.00148192624074482</v>
       </c>
       <c r="E207" t="n">
-        <v>0.0216295407010995</v>
+        <v>-0.0319771122485979</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.0191288440718004</v>
+        <v>0.00687185570742577</v>
       </c>
       <c r="G207" t="n">
-        <v>-0.0432318465716932</v>
+        <v>-0.039470298674935</v>
       </c>
     </row>
     <row r="208">
@@ -5751,22 +5751,22 @@
         <v>213</v>
       </c>
       <c r="B208" t="n">
-        <v>0.00131701408300262</v>
+        <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.145294440180627</v>
+        <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.143429520159449</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>0.100163813175065</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>-0.136655064922698</v>
+        <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.00612050472243574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -5774,22 +5774,22 @@
         <v>214</v>
       </c>
       <c r="B209" t="n">
-        <v>-0.034761092949346</v>
+        <v>-0.093016598206756</v>
       </c>
       <c r="C209" t="n">
-        <v>0.00751495229779699</v>
+        <v>-0.0162162602737457</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.00655592837665806</v>
+        <v>0.100167362239411</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.0282906367159568</v>
+        <v>-0.0549092744409295</v>
       </c>
       <c r="F209" t="n">
-        <v>0.00187521159657097</v>
+        <v>0.266549724218414</v>
       </c>
       <c r="G209" t="n">
-        <v>-0.0901508753566557</v>
+        <v>0.0260620213302077</v>
       </c>
     </row>
   </sheetData>

--- a/example6-rppa/results/pca/pca_norm_WT_7d_MC_CO_over_CO_CO.xlsx
+++ b/example6-rppa/results/pca/pca_norm_WT_7d_MC_CO_over_CO_CO.xlsx
@@ -1013,22 +1013,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.00657774885519052</v>
+        <v>-0.0208760018062579</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00370605445645347</v>
+        <v>0.0337581227193334</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0167261147420646</v>
+        <v>-0.00993849099034437</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0165410753830493</v>
+        <v>0.0104687272453228</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0146614305786302</v>
+        <v>0.00228108650218073</v>
       </c>
       <c r="G2" t="n">
-        <v>0.189876964358538</v>
+        <v>-0.159798540011719</v>
       </c>
     </row>
     <row r="3">
@@ -1036,22 +1036,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0111993878323746</v>
+        <v>0.0183623798439114</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.00110459178225864</v>
+        <v>-0.00798492783346628</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00448673832883429</v>
+        <v>-0.0253810112585595</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.00568123485609609</v>
+        <v>-0.0317151457062741</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0152030868174614</v>
+        <v>-0.018618837081751</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.285408702948272</v>
+        <v>-0.279329478605353</v>
       </c>
     </row>
     <row r="4">
@@ -1059,22 +1059,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>0.131585263880326</v>
+        <v>0.0378152670040101</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.104869148920813</v>
+        <v>-0.00680598251254102</v>
       </c>
       <c r="D4" t="n">
-        <v>0.160629356290015</v>
+        <v>0.00618982363404213</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0366567736211506</v>
+        <v>0.00759972778886281</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0343039671958202</v>
+        <v>0.0131942563358099</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.170984880667016</v>
+        <v>-0.150398646007047</v>
       </c>
     </row>
     <row r="5">
@@ -1082,22 +1082,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.168274484071331</v>
+        <v>0.0592089763780664</v>
       </c>
       <c r="C5" t="n">
-        <v>0.195583454198719</v>
+        <v>0.0125389443928777</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0707218961459099</v>
+        <v>-0.0378737657638692</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.00758660196897218</v>
+        <v>0.00231636351444557</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.051728871657057</v>
+        <v>0.113541394602017</v>
       </c>
       <c r="G5" t="n">
-        <v>0.420886150127981</v>
+        <v>0.0203998088284591</v>
       </c>
     </row>
     <row r="6">
@@ -1105,22 +1105,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0530319953177806</v>
+        <v>0.0000348650802898668</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0622055977641104</v>
+        <v>-0.00285396385120015</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.000476919765206761</v>
+        <v>0.00738257832077002</v>
       </c>
       <c r="E6" t="n">
-        <v>0.211306572359001</v>
+        <v>-0.0201250360373871</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0714621275566927</v>
+        <v>0.00880676158660602</v>
       </c>
       <c r="G6" t="n">
-        <v>0.147890056405921</v>
+        <v>-0.0835948080007354</v>
       </c>
     </row>
     <row r="7">
@@ -1128,22 +1128,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0106465585381168</v>
+        <v>0.0207274587143088</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.00130606909557878</v>
+        <v>-0.00862068204093552</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.00359281451632229</v>
+        <v>-0.0112398320812323</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.00715238596678082</v>
+        <v>-0.00906222879016039</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00720325759563435</v>
+        <v>-0.0130596795873948</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.123550443651407</v>
+        <v>-0.132169048367387</v>
       </c>
     </row>
     <row r="8">
@@ -1151,22 +1151,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>0.00710512249498674</v>
+        <v>0.0197998722809281</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0108022135612484</v>
+        <v>-0.0347557282016192</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0109961184456208</v>
+        <v>0.00774327797229524</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0145495605855044</v>
+        <v>-0.0432139030217731</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0248156578540873</v>
+        <v>-0.023790748357529</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0178564390827558</v>
+        <v>-0.021594442971646</v>
       </c>
     </row>
     <row r="9">
@@ -1174,22 +1174,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0103067710575789</v>
+        <v>0.00862712659422254</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0302081734917859</v>
+        <v>0.0129320741799678</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0183875408204871</v>
+        <v>-0.0763050966577092</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.000380916119395531</v>
+        <v>0.0129374353085661</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000877796850332532</v>
+        <v>0.0499468720497478</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0872177270176596</v>
+        <v>-0.0858828560181907</v>
       </c>
     </row>
     <row r="10">
@@ -1197,22 +1197,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>0.192350764521899</v>
+        <v>0.0532438609161521</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.127603367719778</v>
+        <v>-0.0109356359487019</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.181268856916493</v>
+        <v>-0.0315420247401537</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.162117858467681</v>
+        <v>0.00885968478520868</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0329331346215974</v>
+        <v>0.0410243519140937</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0481904651096822</v>
+        <v>0.137713154159151</v>
       </c>
     </row>
     <row r="11">
@@ -1220,22 +1220,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.00679380366429692</v>
+        <v>-0.00914764024069908</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0076332556508067</v>
+        <v>-0.0355255107969785</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.00226289731981281</v>
+        <v>-0.0086978540472488</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0195515950824219</v>
+        <v>0.0113794593134902</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00826819945537845</v>
+        <v>0.0184709334730005</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0821597908462685</v>
+        <v>-0.0876496372464789</v>
       </c>
     </row>
     <row r="12">
@@ -1243,22 +1243,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>0.224720825240488</v>
+        <v>0.0609066509539654</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0182360097899855</v>
+        <v>0.0123261948437374</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.00134702010969072</v>
+        <v>-0.0436746074015156</v>
       </c>
       <c r="E12" t="n">
-        <v>0.057901203702853</v>
+        <v>-0.0725646823408849</v>
       </c>
       <c r="F12" t="n">
-        <v>0.113354869003016</v>
+        <v>-0.028146334043713</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0475618369468471</v>
+        <v>-0.0402445858620036</v>
       </c>
     </row>
     <row r="13">
@@ -1266,22 +1266,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.131430572616782</v>
+        <v>-0.0395780660138576</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0789153731648802</v>
+        <v>-0.0313112969185558</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.00708083832705991</v>
+        <v>0.0362263718454081</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.255973960721631</v>
+        <v>-0.0289605332070667</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.00147709840723312</v>
+        <v>0.026709470407761</v>
       </c>
       <c r="G13" t="n">
-        <v>0.066528227562322</v>
+        <v>-0.0470521767459831</v>
       </c>
     </row>
     <row r="14">
@@ -1289,22 +1289,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.0146604487335742</v>
+        <v>-0.0232797218588173</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.00460952228696862</v>
+        <v>-0.0320766177394105</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.000428862423159943</v>
+        <v>0.0155785364783304</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0104314461289598</v>
+        <v>-0.0222424653344163</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0148035028228782</v>
+        <v>0.0013217030487767</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.12251153883591</v>
+        <v>-0.136115408043986</v>
       </c>
     </row>
     <row r="15">
@@ -1312,22 +1312,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>0.00166560067539766</v>
+        <v>0.00764539068208881</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.000578590961831163</v>
+        <v>-0.036239283532378</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.00630168467867034</v>
+        <v>-0.00490988454399399</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0212786983802691</v>
+        <v>-0.000374656178286835</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0117023164888762</v>
+        <v>-0.00828614431847065</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0396625501370886</v>
+        <v>-0.0428417039053138</v>
       </c>
     </row>
     <row r="16">
@@ -1335,22 +1335,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>0.174686601771993</v>
+        <v>0.0982028263249054</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.00238313585522848</v>
+        <v>0.0535975863546412</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0101131460122575</v>
+        <v>-0.0596745667179995</v>
       </c>
       <c r="E16" t="n">
-        <v>0.043411700831149</v>
+        <v>0.0145823009843295</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0429631179974598</v>
+        <v>-0.0354036828307205</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0494794247611967</v>
+        <v>0.00388346930171762</v>
       </c>
     </row>
     <row r="17">
@@ -1358,22 +1358,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.145908357188229</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0.0162812402875757</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.0396840053748678</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.019614763744093</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.116561053744713</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.0253885256442759</v>
       </c>
     </row>
     <row r="18">
@@ -1381,22 +1381,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0168086038974482</v>
+        <v>0.0995929344366299</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.140171566146239</v>
+        <v>0.0751329969170609</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.050601791275988</v>
+        <v>0.308743659926286</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0388615117789122</v>
+        <v>-0.0671344134746096</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0904145437744045</v>
+        <v>0.124675440266002</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.00283767160681313</v>
+        <v>0.00755533716435296</v>
       </c>
     </row>
     <row r="19">
@@ -1404,22 +1404,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>0.262708074435779</v>
+        <v>0.036524947838877</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0161473391690528</v>
+        <v>-0.00285002809802077</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.00475526056614301</v>
+        <v>-0.0339224436996225</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0593818613272467</v>
+        <v>-0.013609327855764</v>
       </c>
       <c r="F19" t="n">
-        <v>0.121001343309183</v>
+        <v>-0.0190987732284178</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0541187765942675</v>
+        <v>0.0478830706997344</v>
       </c>
     </row>
     <row r="20">
@@ -1427,22 +1427,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0165542060272025</v>
+        <v>0.0337494518288142</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00189257863785026</v>
+        <v>-0.0265716198820313</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.00786557601237592</v>
+        <v>-0.0233055413130218</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0201701503241638</v>
+        <v>-0.00219278299858002</v>
       </c>
       <c r="F20" t="n">
-        <v>0.012162531077054</v>
+        <v>-0.0138300412100887</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00456132567410455</v>
+        <v>0.00418798648651778</v>
       </c>
     </row>
     <row r="21">
@@ -1450,22 +1450,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>0.00247208750972928</v>
+        <v>0.00720700689038557</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.000546090418553896</v>
+        <v>-0.0301729783039426</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.00293504209026304</v>
+        <v>-0.0094579626495031</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0192952135840445</v>
+        <v>0.0009707693809969</v>
       </c>
       <c r="F21" t="n">
-        <v>0.00934863922762578</v>
+        <v>-0.0130768440180301</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.125129822968629</v>
+        <v>-0.133495086647652</v>
       </c>
     </row>
     <row r="22">
@@ -1473,22 +1473,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>0.166316092569204</v>
+        <v>0.0398598507031057</v>
       </c>
       <c r="C22" t="n">
-        <v>0.190704917691835</v>
+        <v>0.0137664129787803</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0656883632840718</v>
+        <v>-0.0169296301361152</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.00690976637103252</v>
+        <v>0.0222986992410101</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0586154352370619</v>
+        <v>0.0504720958214279</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.05322373727689</v>
+        <v>0.0646872003396233</v>
       </c>
     </row>
     <row r="23">
@@ -1496,22 +1496,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.000479640358444295</v>
+        <v>0.000414851094351515</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00331960050104943</v>
+        <v>-0.0331654912253849</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000753191815285147</v>
+        <v>-0.0170039734570512</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0225312559631312</v>
+        <v>0.0109490469346584</v>
       </c>
       <c r="F23" t="n">
-        <v>0.00724854338846906</v>
+        <v>-0.00801907206677721</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0401363235062948</v>
+        <v>-0.045163739656341</v>
       </c>
     </row>
     <row r="24">
@@ -1519,22 +1519,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0176764865509219</v>
+        <v>0.0389159369831637</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00261294934177921</v>
+        <v>-0.013351823393849</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0166099879782999</v>
+        <v>-0.00622781482589078</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.00859587932573367</v>
+        <v>-0.00387256554228681</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00922549226456954</v>
+        <v>0.00812864990453763</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.00253888269392504</v>
+        <v>0.00211344117200596</v>
       </c>
     </row>
     <row r="25">
@@ -1542,22 +1542,22 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0156424262657541</v>
+        <v>-0.0239802218276091</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.00358958607139374</v>
+        <v>-0.0453063572476477</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0013478297324489</v>
+        <v>0.0123250142051059</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0191750242720625</v>
+        <v>-0.0152532314111111</v>
       </c>
       <c r="F25" t="n">
-        <v>0.016571508586764</v>
+        <v>-0.000585826288109109</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.124417101897312</v>
+        <v>-0.137963025144238</v>
       </c>
     </row>
     <row r="26">
@@ -1565,22 +1565,22 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0404191974073602</v>
+        <v>-0.0104560085710144</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.108943680332563</v>
+        <v>-0.0373063401192525</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.172942941867122</v>
+        <v>0.0213363194145413</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.203026281880101</v>
+        <v>0.0254974937121781</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.113540574948056</v>
+        <v>0.0171827832771937</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0656145500556664</v>
+        <v>-0.0479909923683475</v>
       </c>
     </row>
     <row r="27">
@@ -1588,22 +1588,22 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.00614142256134952</v>
+        <v>-0.00924291062807264</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00207172148999273</v>
+        <v>-0.0233385669182958</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.000162693894510673</v>
+        <v>-0.00191504160818083</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.00962188543080886</v>
+        <v>-0.0110434512906988</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0110795992645127</v>
+        <v>0.0096518535602105</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0435868958889249</v>
+        <v>0.0438564238981407</v>
       </c>
     </row>
     <row r="28">
@@ -1611,22 +1611,22 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0062081649500036</v>
+        <v>0.00850339413836153</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00444921075175249</v>
+        <v>-0.00396669904747828</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00477403688388701</v>
+        <v>-0.0238791373813971</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0109849330401714</v>
+        <v>0.0254346071978451</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.00602362579021961</v>
+        <v>-0.0137929423390177</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0436505347843935</v>
+        <v>0.0487322294211356</v>
       </c>
     </row>
     <row r="29">
@@ -1634,22 +1634,22 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0844026942043349</v>
+        <v>0.0281924769209193</v>
       </c>
       <c r="C29" t="n">
-        <v>0.110046761170866</v>
+        <v>0.015845054065128</v>
       </c>
       <c r="D29" t="n">
-        <v>0.22066251842626</v>
+        <v>-0.0519159227307621</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0861353848151989</v>
+        <v>0.0224492191722621</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.161066968643631</v>
+        <v>-0.0611252599689017</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0222767541664046</v>
+        <v>-0.0367382411729115</v>
       </c>
     </row>
     <row r="30">
@@ -1657,22 +1657,22 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>0.00352645636887335</v>
+        <v>0.00468248314322546</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00508829046071775</v>
+        <v>-0.0175422248773149</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0042908088094301</v>
+        <v>-0.0250541512129345</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0192977873831874</v>
+        <v>0.031619990941571</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00421100877175312</v>
+        <v>-0.0151375353943257</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00173126158796083</v>
+        <v>0.00276121267115479</v>
       </c>
     </row>
     <row r="31">
@@ -1680,22 +1680,22 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0116095009049641</v>
+        <v>0.0222663899264268</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.000204917379695878</v>
+        <v>-0.00669882357446265</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.00405643462840812</v>
+        <v>-0.0125356332633961</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.00919970493856317</v>
+        <v>0.0079173707148955</v>
       </c>
       <c r="F31" t="n">
-        <v>0.000865357515087276</v>
+        <v>-0.0155161965228446</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0411010956982273</v>
+        <v>-0.0436190372454803</v>
       </c>
     </row>
     <row r="32">
@@ -1703,22 +1703,22 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.00736447449969111</v>
+        <v>-0.0146848648857464</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00271223771627867</v>
+        <v>-0.0113317973403466</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00615634362751514</v>
+        <v>-0.00682291379482242</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.00172133298935798</v>
+        <v>-0.0218430940924219</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0111180950600121</v>
+        <v>0.0114273423790247</v>
       </c>
       <c r="G32" t="n">
-        <v>0.00184562514700102</v>
+        <v>-0.000345126388697046</v>
       </c>
     </row>
     <row r="33">
@@ -1726,22 +1726,22 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.00622665725505998</v>
+        <v>-0.00443250415163518</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.00240067287976043</v>
+        <v>-0.0232706194505161</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0114891906059392</v>
+        <v>0.0222995637640038</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.00780150929275081</v>
+        <v>-0.00194300447017244</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00672756519211591</v>
+        <v>0.0119213100050439</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0438135077160107</v>
+        <v>0.0421301182777997</v>
       </c>
     </row>
     <row r="34">
@@ -1749,22 +1749,22 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.000266033478025134</v>
+        <v>0.000170435153799856</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00303092989074408</v>
+        <v>-0.0130209987866863</v>
       </c>
       <c r="D34" t="n">
-        <v>0.000610477217549847</v>
+        <v>-0.00899040473143104</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.00452835728868123</v>
+        <v>-0.0174178221485046</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0112517038473228</v>
+        <v>0.00979635292545297</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0414442773927009</v>
+        <v>-0.043954894830194</v>
       </c>
     </row>
     <row r="35">
@@ -1772,22 +1772,22 @@
         <v>40</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0193584218415648</v>
+        <v>0.0338551019767733</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00557245946987646</v>
+        <v>-0.0338355923931311</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00313567169633356</v>
+        <v>-0.0528776817399225</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0325539447962579</v>
+        <v>0.0143236793268724</v>
       </c>
       <c r="F35" t="n">
-        <v>0.00957290139536295</v>
+        <v>-0.0341889595902302</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.037821025097964</v>
+        <v>-0.044552539872446</v>
       </c>
     </row>
     <row r="36">
@@ -1795,22 +1795,22 @@
         <v>41</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.0799081202259413</v>
+        <v>-0.326304145235387</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0794117094458199</v>
+        <v>0.104880919309591</v>
       </c>
       <c r="D36" t="n">
-        <v>0.16174022883417</v>
+        <v>-0.130637622772714</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.0780376051562371</v>
+        <v>-0.11437496648446</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.115513477146699</v>
+        <v>0.32899444797695</v>
       </c>
       <c r="G36" t="n">
-        <v>0.00626332975952604</v>
+        <v>0.0151624129748573</v>
       </c>
     </row>
     <row r="37">
@@ -1818,22 +1818,22 @@
         <v>42</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.00359428982497921</v>
+        <v>-0.00924872981034794</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00932168887289476</v>
+        <v>-0.00855410553257872</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00730198737937364</v>
+        <v>-0.0211096445469344</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.00657894917629883</v>
+        <v>0.00831704403821472</v>
       </c>
       <c r="F37" t="n">
-        <v>0.00163322763332296</v>
+        <v>0.0152194947953313</v>
       </c>
       <c r="G37" t="n">
-        <v>0.127635371361677</v>
+        <v>0.134467048287846</v>
       </c>
     </row>
     <row r="38">
@@ -1841,22 +1841,22 @@
         <v>43</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.0933719782251433</v>
+        <v>0.0381805211349343</v>
       </c>
       <c r="C38" t="n">
-        <v>0.219548655278297</v>
+        <v>-0.0554768556997334</v>
       </c>
       <c r="D38" t="n">
-        <v>0.163547103909963</v>
+        <v>-0.0331089848954672</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.174971561391915</v>
+        <v>0.00574079442324913</v>
       </c>
       <c r="F38" t="n">
-        <v>0.143604963375859</v>
+        <v>-0.0358323622482244</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0412665859007406</v>
+        <v>-0.045433338755999</v>
       </c>
     </row>
     <row r="39">
@@ -1864,22 +1864,22 @@
         <v>44</v>
       </c>
       <c r="B39" t="n">
-        <v>0.00666683838231932</v>
+        <v>0.0148530766365049</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.000602153383255047</v>
+        <v>-0.0420164115408248</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.00191906832049472</v>
+        <v>-0.0216105602907027</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0266446578306458</v>
+        <v>-0.0112340656777645</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0180517262563977</v>
+        <v>-0.0213575034592113</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0460434166160068</v>
+        <v>0.0479861022806746</v>
       </c>
     </row>
     <row r="40">
@@ -1887,22 +1887,22 @@
         <v>45</v>
       </c>
       <c r="B40" t="n">
-        <v>0.00190205716873722</v>
+        <v>0.0054276980397218</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.00175972444526776</v>
+        <v>-0.0347145673592191</v>
       </c>
       <c r="D40" t="n">
-        <v>0.000556094254019341</v>
+        <v>-0.0145203839790536</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.0162801484263586</v>
+        <v>-0.0368322885452774</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0240535033415824</v>
+        <v>-0.0102502781410397</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0825292995612421</v>
+        <v>-0.089492803570622</v>
       </c>
     </row>
     <row r="41">
@@ -1933,22 +1933,22 @@
         <v>47</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.145010268487172</v>
+        <v>-0.0220032035925264</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.0563557205096884</v>
+        <v>-0.0045574019564066</v>
       </c>
       <c r="D42" t="n">
-        <v>0.096702507857404</v>
+        <v>-0.057556660082655</v>
       </c>
       <c r="E42" t="n">
-        <v>0.191612001543392</v>
+        <v>0.012228405169911</v>
       </c>
       <c r="F42" t="n">
-        <v>0.153408761640394</v>
+        <v>0.080966939673849</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0247687668866498</v>
+        <v>-0.111885955074824</v>
       </c>
     </row>
     <row r="43">
@@ -1979,22 +1979,22 @@
         <v>49</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>-0.160250105715374</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>-0.174929315701639</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>-0.161356414643375</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-0.263456319685706</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>0.0694714923255936</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.0559022642785683</v>
       </c>
     </row>
     <row r="45">
@@ -2002,22 +2002,22 @@
         <v>50</v>
       </c>
       <c r="B45" t="n">
-        <v>0.00483636875561595</v>
+        <v>0.0067602361102734</v>
       </c>
       <c r="C45" t="n">
-        <v>0.00684051401526164</v>
+        <v>-0.00947763901270588</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00402224680173007</v>
+        <v>-0.0254861775342521</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.012690733977421</v>
+        <v>0.0227776044731429</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.00281358639257651</v>
+        <v>-0.00436639998047882</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.12917089594127</v>
+        <v>-0.134007695500133</v>
       </c>
     </row>
     <row r="46">
@@ -2025,22 +2025,22 @@
         <v>51</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.0722743026583251</v>
+        <v>-0.00792532073603069</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0762042145823877</v>
+        <v>-0.0092910340171052</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0209185249242056</v>
+        <v>-0.0407272216285741</v>
       </c>
       <c r="E46" t="n">
-        <v>0.27794214996162</v>
+        <v>-0.00783224237859152</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.101954294480286</v>
+        <v>-0.00528448060501928</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0210286702380389</v>
+        <v>-0.0420789807821445</v>
       </c>
     </row>
     <row r="47">
@@ -2048,22 +2048,22 @@
         <v>52</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.0775046145761626</v>
+        <v>-0.242415343724695</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0716660839747811</v>
+        <v>0.0917594841653168</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.12192065350726</v>
+        <v>0.0566379319470165</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0215341434479072</v>
+        <v>-0.419241037994789</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0248389985203836</v>
+        <v>0.0325111339542581</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.0122813089031575</v>
+        <v>-0.0266729523933783</v>
       </c>
     </row>
     <row r="48">
@@ -2071,22 +2071,22 @@
         <v>53</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>-0.18842868530257</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.1977229714498</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>-0.322152855130307</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-0.185995869036626</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>-0.152195672531132</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.0319956582748591</v>
       </c>
     </row>
     <row r="49">
@@ -2094,22 +2094,22 @@
         <v>54</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.0010220613893048</v>
+        <v>-0.0028812733339007</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0055696178087581</v>
+        <v>-0.015386840453191</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00364439715112544</v>
+        <v>-0.0170065370072654</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0131320640795132</v>
+        <v>0.0181791186864575</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.000456472646170808</v>
+        <v>-0.000353439115425535</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0434596763779567</v>
+        <v>0.0448808190584647</v>
       </c>
     </row>
     <row r="50">
@@ -2117,22 +2117,22 @@
         <v>55</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0188662103102394</v>
+        <v>0.0343284735599828</v>
       </c>
       <c r="C50" t="n">
-        <v>0.00205232490166902</v>
+        <v>-0.0201512088396257</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.00122797095919687</v>
+        <v>-0.0355708915885148</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0215283834153053</v>
+        <v>0.00827457460412494</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0065304532423594</v>
+        <v>-0.0291487682026544</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.0387536693911957</v>
+        <v>-0.040748564464416</v>
       </c>
     </row>
     <row r="51">
@@ -2140,22 +2140,22 @@
         <v>56</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.158894763418372</v>
+        <v>-0.0389667546450955</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0894465508732977</v>
+        <v>-0.0976804150732539</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0482989545468543</v>
+        <v>0.0455174374941205</v>
       </c>
       <c r="E51" t="n">
-        <v>0.165790090032819</v>
+        <v>-0.0135775515306906</v>
       </c>
       <c r="F51" t="n">
-        <v>0.147362189834398</v>
+        <v>0.0410564770801283</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.0398760830184937</v>
+        <v>0.0415134585066785</v>
       </c>
     </row>
     <row r="52">
@@ -2186,22 +2186,22 @@
         <v>58</v>
       </c>
       <c r="B53" t="n">
-        <v>0.00885451223390791</v>
+        <v>0.0167171255529731</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.00136969326913887</v>
+        <v>-0.0271085141490038</v>
       </c>
       <c r="D53" t="n">
-        <v>0.000761315475265207</v>
+        <v>-0.0227414169207274</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.018777177611455</v>
+        <v>-0.0139500905731062</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0143939324301081</v>
+        <v>-0.0242339318314376</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.0827102831506924</v>
+        <v>-0.0890586328964932</v>
       </c>
     </row>
     <row r="54">
@@ -2209,22 +2209,22 @@
         <v>59</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.010631500581204</v>
+        <v>-0.0193274305015857</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00477030847917135</v>
+        <v>-0.0398345216505583</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0067992667140658</v>
+        <v>-0.0163409239243099</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0205305931191229</v>
+        <v>-0.00963756192084909</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0157013645165365</v>
+        <v>0.00499308422386937</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0891068572584674</v>
+        <v>0.0902582293570758</v>
       </c>
     </row>
     <row r="55">
@@ -2232,22 +2232,22 @@
         <v>60</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.0916724215024141</v>
+        <v>-0.0273497942754557</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0847666102656054</v>
+        <v>0.0103696832619974</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.144207691365061</v>
+        <v>-0.0457405966867437</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0254705746960407</v>
+        <v>-0.00394910613259132</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0293795557143352</v>
+        <v>0.025205785246921</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.0203225297372522</v>
+        <v>-0.0236733304351605</v>
       </c>
     </row>
     <row r="56">
@@ -2255,22 +2255,22 @@
         <v>61</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.00407999480392126</v>
+        <v>-0.00738979985735517</v>
       </c>
       <c r="C56" t="n">
-        <v>0.00618581864468831</v>
+        <v>-0.0269925590778632</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00365964709006251</v>
+        <v>-0.0175734639089428</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0161709209462607</v>
+        <v>0.0029027906081667</v>
       </c>
       <c r="F56" t="n">
-        <v>0.00850329639469963</v>
+        <v>0.0065487883967555</v>
       </c>
       <c r="G56" t="n">
-        <v>0.00455245262832601</v>
+        <v>0.00132089598527965</v>
       </c>
     </row>
     <row r="57">
@@ -2278,22 +2278,22 @@
         <v>62</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.147805753517075</v>
+        <v>-0.068297515363803</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0764375575527144</v>
+        <v>0.011397148559435</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0933768013206292</v>
+        <v>0.0136098090335235</v>
       </c>
       <c r="E57" t="n">
-        <v>0.182780110113618</v>
+        <v>-0.0790359250246404</v>
       </c>
       <c r="F57" t="n">
-        <v>0.150159713791361</v>
+        <v>0.0282891408368594</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.0376596668242976</v>
+        <v>0.0246602282442085</v>
       </c>
     </row>
     <row r="58">
@@ -2301,22 +2301,22 @@
         <v>63</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.00162527030280473</v>
+        <v>-0.00506813365705386</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.00961856194020183</v>
+        <v>-0.00483506278939299</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00539823883683468</v>
+        <v>0.00276207940911076</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.00834942761650108</v>
+        <v>0.0123459404240059</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.00612269286854913</v>
+        <v>-0.0439602998457358</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.0405934018180505</v>
+        <v>-0.042976502888346</v>
       </c>
     </row>
     <row r="59">
@@ -2324,22 +2324,22 @@
         <v>64</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0124650045721682</v>
+        <v>0.0246106821298752</v>
       </c>
       <c r="C59" t="n">
-        <v>0.00433837919308441</v>
+        <v>-0.0282167902703308</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.00337202388809567</v>
+        <v>-0.0283379884350242</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.02189125136062</v>
+        <v>0.00397139121070977</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0104463843981883</v>
+        <v>-0.0111058918571693</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.128263331602896</v>
+        <v>-0.131305779688936</v>
       </c>
     </row>
     <row r="60">
@@ -2393,22 +2393,22 @@
         <v>67</v>
       </c>
       <c r="B62" t="n">
-        <v>0.00759444806793089</v>
+        <v>0.0133418779379515</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.00522428958661288</v>
+        <v>-0.0159515383725231</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00170067231009769</v>
+        <v>-0.0138253945993512</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0149875508575362</v>
+        <v>0.000788949087649616</v>
       </c>
       <c r="F62" t="n">
-        <v>0.00421485781061792</v>
+        <v>-0.0369831574011579</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.000484072327686797</v>
+        <v>0.00466507444412459</v>
       </c>
     </row>
     <row r="63">
@@ -2416,22 +2416,22 @@
         <v>68</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>0.126494489702871</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>-0.342014354954646</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>-0.301633340711373</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>0.113420602646903</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>-0.0346649440248383</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>-0.00325280237827187</v>
       </c>
     </row>
     <row r="64">
@@ -2439,22 +2439,22 @@
         <v>69</v>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>-0.0304344272808897</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>-0.423272254296372</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>0.174297756020641</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>-0.117128488932709</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>-0.108285981533543</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>0.0267461215156307</v>
       </c>
     </row>
     <row r="65">
@@ -2462,22 +2462,22 @@
         <v>70</v>
       </c>
       <c r="B65" t="n">
-        <v>0.0077731648030955</v>
+        <v>0.0181752592285761</v>
       </c>
       <c r="C65" t="n">
-        <v>0.000312596592516023</v>
+        <v>-0.0256489452555915</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.00691571432404485</v>
+        <v>-0.00978660870607837</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0141174887073437</v>
+        <v>-0.0146192142314111</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0147104151413417</v>
+        <v>-0.00329777382993471</v>
       </c>
       <c r="G65" t="n">
-        <v>0.128986726082139</v>
+        <v>0.135580074722973</v>
       </c>
     </row>
     <row r="66">
@@ -2508,22 +2508,22 @@
         <v>72</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.0110954468282406</v>
+        <v>-0.0231752087915032</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.000621198678620737</v>
+        <v>0.00415399221025979</v>
       </c>
       <c r="D67" t="n">
-        <v>0.00893493158454546</v>
+        <v>0.00375784807766407</v>
       </c>
       <c r="E67" t="n">
-        <v>0.00857812958178427</v>
+        <v>-0.0246540555629402</v>
       </c>
       <c r="F67" t="n">
-        <v>0.00575071613056645</v>
+        <v>0.00880642535804274</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.0837771753203168</v>
+        <v>-0.0915905691312245</v>
       </c>
     </row>
     <row r="68">
@@ -2531,22 +2531,22 @@
         <v>73</v>
       </c>
       <c r="B68" t="n">
-        <v>0.0109714756981104</v>
+        <v>0.0197238500847874</v>
       </c>
       <c r="C68" t="n">
-        <v>0.00503119278455945</v>
+        <v>-0.0243550029728403</v>
       </c>
       <c r="D68" t="n">
-        <v>0.00163067441829843</v>
+        <v>-0.0337851737641866</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.0184310758424648</v>
+        <v>-0.00730092265340927</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0132170077781776</v>
+        <v>-0.00974899721733256</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.0000489537868759059</v>
+        <v>-0.000145733139969747</v>
       </c>
     </row>
     <row r="69">
@@ -2554,22 +2554,22 @@
         <v>74</v>
       </c>
       <c r="B69" t="n">
-        <v>0.00632459936857877</v>
+        <v>0.0138840835219039</v>
       </c>
       <c r="C69" t="n">
-        <v>0.00182662812521793</v>
+        <v>-0.0259898965991531</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.00339389616906396</v>
+        <v>-0.015524535635877</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.0176011744858417</v>
+        <v>0.000345038313681736</v>
       </c>
       <c r="F69" t="n">
-        <v>0.00949782864065957</v>
+        <v>-0.00818435298849425</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.0392297882347927</v>
+        <v>-0.0459015945615333</v>
       </c>
     </row>
     <row r="70">
@@ -2577,22 +2577,22 @@
         <v>75</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.0275544191275745</v>
+        <v>-0.0273597722103579</v>
       </c>
       <c r="C70" t="n">
-        <v>0.175288957396925</v>
+        <v>0.0589003795798018</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0737028975178986</v>
+        <v>-0.0165700029837651</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.0190890196379942</v>
+        <v>0.0716677100561606</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.141509039448645</v>
+        <v>0.041219087723614</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.0921685658719654</v>
+        <v>-0.00336326010945596</v>
       </c>
     </row>
     <row r="71">
@@ -2600,22 +2600,22 @@
         <v>76</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.000283486945892137</v>
+        <v>-0.00395314945775221</v>
       </c>
       <c r="C71" t="n">
-        <v>0.00237520174766455</v>
+        <v>0.00433285666929589</v>
       </c>
       <c r="D71" t="n">
-        <v>0.00682366737276788</v>
+        <v>-0.0121751734491371</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.00159171280455237</v>
+        <v>0.0122092625753547</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.00534386687994992</v>
+        <v>-0.00653473695086889</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0846978337044183</v>
+        <v>0.0899787032720376</v>
       </c>
     </row>
     <row r="72">
@@ -2623,22 +2623,22 @@
         <v>77</v>
       </c>
       <c r="B72" t="n">
-        <v>0.10347264463982</v>
+        <v>-0.0143323591659676</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.0927924711139821</v>
+        <v>0.0208489228177451</v>
       </c>
       <c r="D72" t="n">
-        <v>0.190094120813746</v>
+        <v>-0.0392233280633393</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.0292643115495814</v>
+        <v>0.0241658279136815</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.0484757798102536</v>
+        <v>-0.0335746960100568</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0970671726233446</v>
+        <v>-0.110710288565303</v>
       </c>
     </row>
     <row r="73">
@@ -2646,22 +2646,22 @@
         <v>78</v>
       </c>
       <c r="B73" t="n">
-        <v>0.0784935524206531</v>
+        <v>-0.0117854888788379</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0950578993103123</v>
+        <v>-0.0217283140093811</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.190714111946133</v>
+        <v>0.0172263544186515</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0823363138930326</v>
+        <v>0.00145268813296422</v>
       </c>
       <c r="F73" t="n">
-        <v>0.135372123147328</v>
+        <v>0.0455751799610975</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.00860569302385728</v>
+        <v>-0.047008415337235</v>
       </c>
     </row>
     <row r="74">
@@ -2669,22 +2669,22 @@
         <v>79</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0151180732378473</v>
+        <v>0.0366292526611145</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.00355603681040717</v>
+        <v>-0.027491103273396</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.0188004222961917</v>
+        <v>0.00322057839161492</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.0113261710898952</v>
+        <v>-0.032132910099214</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0218937006344417</v>
+        <v>0.00039683025897738</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.082340088371969</v>
+        <v>-0.0866036070558792</v>
       </c>
     </row>
     <row r="75">
@@ -2692,22 +2692,22 @@
         <v>80</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0129706134719171</v>
+        <v>0.0346232802471047</v>
       </c>
       <c r="C75" t="n">
-        <v>0.00167666851081647</v>
+        <v>0.00361916133494962</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.0270580578703777</v>
+        <v>0.0256070068349589</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00973037045600286</v>
+        <v>-0.0137209807312149</v>
       </c>
       <c r="F75" t="n">
-        <v>0.00685332937554971</v>
+        <v>0.0404741330939015</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.129614104183731</v>
+        <v>-0.133656931141269</v>
       </c>
     </row>
     <row r="76">
@@ -2715,22 +2715,22 @@
         <v>81</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.128113825526988</v>
+        <v>0.0788511531167245</v>
       </c>
       <c r="C76" t="n">
-        <v>0.326672352948662</v>
+        <v>-0.0378127982130221</v>
       </c>
       <c r="D76" t="n">
-        <v>0.235296981399933</v>
+        <v>-0.0486790330023498</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.231459625362739</v>
+        <v>0.00315129786512548</v>
       </c>
       <c r="F76" t="n">
-        <v>0.219782760621122</v>
+        <v>-0.00765274016529189</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.0652364225951746</v>
+        <v>-0.0863444104377484</v>
       </c>
     </row>
     <row r="77">
@@ -2738,22 +2738,22 @@
         <v>82</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.00862829705444715</v>
+        <v>-0.00487760105624871</v>
       </c>
       <c r="C77" t="n">
-        <v>0.000289090385247539</v>
+        <v>-0.0360732532159251</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.0178012983259406</v>
+        <v>0.028457440436534</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.00842337269396299</v>
+        <v>-0.0211283136082273</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0183376109135017</v>
+        <v>0.036312302017858</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.0867629465543025</v>
+        <v>-0.0913009907852153</v>
       </c>
     </row>
     <row r="78">
@@ -2807,22 +2807,22 @@
         <v>85</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0079693818567021</v>
+        <v>0.0172705859301595</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.00096888100585854</v>
+        <v>-0.0286923619359003</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.00449114465652411</v>
+        <v>-0.0138959895229747</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.0219075902615796</v>
+        <v>0.0100257501550315</v>
       </c>
       <c r="F80" t="n">
-        <v>0.00626256874797174</v>
+        <v>-0.0220726110340775</v>
       </c>
       <c r="G80" t="n">
-        <v>0.129619628605769</v>
+        <v>0.136898463337386</v>
       </c>
     </row>
     <row r="81">
@@ -2830,22 +2830,22 @@
         <v>86</v>
       </c>
       <c r="B81" t="n">
-        <v>0.162478315397588</v>
+        <v>-0.00223867338422318</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.156076224877825</v>
+        <v>-0.0223442915034916</v>
       </c>
       <c r="D81" t="n">
-        <v>0.263159887763645</v>
+        <v>-0.0120515239010618</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.054691867160574</v>
+        <v>-0.0413242563459515</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.031962437975156</v>
+        <v>-0.0213004082185207</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.0515488188597323</v>
+        <v>0.0924982924372281</v>
       </c>
     </row>
     <row r="82">
@@ -2853,22 +2853,22 @@
         <v>87</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0122243124307775</v>
+        <v>0.0198806732003108</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.00154157452152493</v>
+        <v>-0.0151339287876037</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00512886245349394</v>
+        <v>-0.0302786730377277</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.0159612939152729</v>
+        <v>-0.0052085994035326</v>
       </c>
       <c r="F82" t="n">
-        <v>0.00776375604840119</v>
+        <v>-0.035199955001898</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.0842273694096278</v>
+        <v>-0.0842635023653809</v>
       </c>
     </row>
     <row r="83">
@@ -2876,22 +2876,22 @@
         <v>88</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0533208123880299</v>
+        <v>0.0372565045104934</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.083423019958814</v>
+        <v>0.105767965956893</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0896639730150972</v>
+        <v>-0.116544275069037</v>
       </c>
       <c r="E83" t="n">
-        <v>0.238010412805361</v>
+        <v>-0.0829602052973178</v>
       </c>
       <c r="F83" t="n">
-        <v>0.240276967687418</v>
+        <v>-0.215747861235874</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0607142477747561</v>
+        <v>0.00412419328288507</v>
       </c>
     </row>
     <row r="84">
@@ -2899,22 +2899,22 @@
         <v>89</v>
       </c>
       <c r="B84" t="n">
-        <v>0.012008738759101</v>
+        <v>0.0248300138388304</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.0014916016201045</v>
+        <v>-0.0277979783323756</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.00513617402147931</v>
+        <v>-0.017659160390724</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.0189953017699905</v>
+        <v>-0.0106880855707229</v>
       </c>
       <c r="F84" t="n">
-        <v>0.013973001283299</v>
+        <v>-0.0203074398929993</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.0410625410269797</v>
+        <v>-0.0437577209575399</v>
       </c>
     </row>
     <row r="85">
@@ -2945,22 +2945,22 @@
         <v>91</v>
       </c>
       <c r="B86" t="n">
-        <v>0.169442723218595</v>
+        <v>0.00768947867952487</v>
       </c>
       <c r="C86" t="n">
-        <v>0.201250046229249</v>
+        <v>0.0194776223110358</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0800948743504659</v>
+        <v>-0.00206583249295196</v>
       </c>
       <c r="E86" t="n">
-        <v>0.00694713802401791</v>
+        <v>-0.0383145170700204</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.0468069198443033</v>
+        <v>-0.000971623869874352</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.0917918970581054</v>
+        <v>-0.0651505430976553</v>
       </c>
     </row>
     <row r="87">
@@ -2968,22 +2968,22 @@
         <v>92</v>
       </c>
       <c r="B87" t="n">
-        <v>0.01226335348722</v>
+        <v>0.0206804259461649</v>
       </c>
       <c r="C87" t="n">
-        <v>0.00268511793281063</v>
+        <v>0.00354369260503934</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00111185253761677</v>
+        <v>-0.0215699618324649</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.00239110949863645</v>
+        <v>-0.00293461448079394</v>
       </c>
       <c r="F87" t="n">
-        <v>0.00241203773417837</v>
+        <v>-0.00798493433834989</v>
       </c>
       <c r="G87" t="n">
-        <v>0.042161039799477</v>
+        <v>0.0470344237469123</v>
       </c>
     </row>
     <row r="88">
@@ -2991,22 +2991,22 @@
         <v>93</v>
       </c>
       <c r="B88" t="n">
-        <v>0.14615597382841</v>
+        <v>0.0456438862606309</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.113782497015259</v>
+        <v>0.00573801747415641</v>
       </c>
       <c r="D88" t="n">
-        <v>0.189485588506423</v>
+        <v>-0.0338348870177088</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.0325299821210414</v>
+        <v>-0.0482767970831123</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.0198114833753393</v>
+        <v>-0.0269609465227367</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.040116974385191</v>
+        <v>0.0498368155442937</v>
       </c>
     </row>
     <row r="89">
@@ -3014,22 +3014,22 @@
         <v>94</v>
       </c>
       <c r="B89" t="n">
-        <v>0.00666164690760525</v>
+        <v>0.0144118901280012</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.00473552906014537</v>
+        <v>-0.0228798570176672</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.00321410387049721</v>
+        <v>-0.0074000186042987</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.015142106673506</v>
+        <v>-0.00929785456864268</v>
       </c>
       <c r="F89" t="n">
-        <v>0.010201260756998</v>
+        <v>-0.0248667857801995</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0857201961825667</v>
+        <v>0.0916300422932872</v>
       </c>
     </row>
     <row r="90">
@@ -3037,22 +3037,22 @@
         <v>95</v>
       </c>
       <c r="B90" t="n">
-        <v>0.0144346886860706</v>
+        <v>0.0280975160556019</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.0002958098924499</v>
+        <v>-0.00783782050269054</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.00529251469530358</v>
+        <v>-0.014804882569001</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.00652347158892</v>
+        <v>-0.0140481745701567</v>
       </c>
       <c r="F90" t="n">
-        <v>0.00963928405585478</v>
+        <v>-0.0100675514677194</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0857254499395239</v>
+        <v>0.0911890471651078</v>
       </c>
     </row>
     <row r="91">
@@ -3060,22 +3060,22 @@
         <v>96</v>
       </c>
       <c r="B91" t="n">
-        <v>0.0983365291149461</v>
+        <v>0.00656532754817305</v>
       </c>
       <c r="C91" t="n">
-        <v>0.114297084488796</v>
+        <v>0.0696013691066277</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0694770998813331</v>
+        <v>-0.0622503062191574</v>
       </c>
       <c r="E91" t="n">
-        <v>0.224803450092526</v>
+        <v>0.0467909007629623</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.13508524951852</v>
+        <v>-0.0329277643623355</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0107488659961953</v>
+        <v>-0.0425228386699796</v>
       </c>
     </row>
     <row r="92">
@@ -3083,22 +3083,22 @@
         <v>97</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>-0.0132515275169445</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.336721734860029</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>-0.18623943126285</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>0.166718188381516</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>-0.0326620185868539</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>0.00202343509710424</v>
       </c>
     </row>
     <row r="93">
@@ -3152,22 +3152,22 @@
         <v>100</v>
       </c>
       <c r="B95" t="n">
-        <v>0.0931629273228348</v>
+        <v>-0.00830942562108276</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0978380738784278</v>
+        <v>-0.00350704433661308</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.207369607382984</v>
+        <v>0.0191335975974929</v>
       </c>
       <c r="E95" t="n">
-        <v>0.105950404099338</v>
+        <v>-0.0324505445272487</v>
       </c>
       <c r="F95" t="n">
-        <v>0.155964066071411</v>
+        <v>0.0250755349299831</v>
       </c>
       <c r="G95" t="n">
-        <v>0.031037150273772</v>
+        <v>-0.0444053161746636</v>
       </c>
     </row>
     <row r="96">
@@ -3175,22 +3175,22 @@
         <v>101</v>
       </c>
       <c r="B96" t="n">
-        <v>0.113579274199724</v>
+        <v>0.00129868759429332</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.107369396118741</v>
+        <v>-0.0264395676724851</v>
       </c>
       <c r="D96" t="n">
-        <v>0.17680978733846</v>
+        <v>-0.000140892161335468</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.0415993635359358</v>
+        <v>-0.0276420338935352</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.0188586836844397</v>
+        <v>0.00378792449807149</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.021597022041896</v>
+        <v>0.00037763539978702</v>
       </c>
     </row>
     <row r="97">
@@ -3198,22 +3198,22 @@
         <v>102</v>
       </c>
       <c r="B97" t="n">
-        <v>0.00463867476003313</v>
+        <v>0.0110738055452453</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.000786745694647757</v>
+        <v>-0.0194912886317988</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.00445552637052238</v>
+        <v>-0.00579006119516481</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.0131743980363874</v>
+        <v>0.00218188481954045</v>
       </c>
       <c r="F97" t="n">
-        <v>0.00583519218644623</v>
+        <v>-0.0102043064709931</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.0854133489529017</v>
+        <v>-0.0887779305952718</v>
       </c>
     </row>
     <row r="98">
@@ -3221,22 +3221,22 @@
         <v>103</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.00941057516165098</v>
+        <v>0.00397872317913428</v>
       </c>
       <c r="C98" t="n">
-        <v>0.00544083617145272</v>
+        <v>-0.0275489395726656</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.042131288422425</v>
+        <v>0.0672622630413475</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0054036048970279</v>
+        <v>-0.0113784034920152</v>
       </c>
       <c r="F98" t="n">
-        <v>0.014103354078922</v>
+        <v>0.0957075456321249</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0407289224579133</v>
+        <v>0.0342223061794475</v>
       </c>
     </row>
     <row r="99">
@@ -3244,22 +3244,22 @@
         <v>104</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>0.204107966576081</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>0.0923266036137357</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>-0.0446463255108671</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>-0.205111295540567</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>0.0714911381364169</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>0.045540768310658</v>
       </c>
     </row>
     <row r="100">
@@ -3267,22 +3267,22 @@
         <v>105</v>
       </c>
       <c r="B100" t="n">
-        <v>0.0690653131788354</v>
+        <v>0.281727317691547</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0144019261823572</v>
+        <v>0.149564490665699</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.0719912927211502</v>
+        <v>-0.166342937730652</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0570726879545941</v>
+        <v>-0.213504840056701</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.231504510954185</v>
+        <v>-0.1113117209935</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.0503454784611294</v>
+        <v>-0.0655566066654908</v>
       </c>
     </row>
     <row r="101">
@@ -3290,22 +3290,22 @@
         <v>106</v>
       </c>
       <c r="B101" t="n">
-        <v>0.146617512200371</v>
+        <v>0.0439345394576783</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.123198752334349</v>
+        <v>-0.0510093870875176</v>
       </c>
       <c r="D101" t="n">
-        <v>0.176136817007687</v>
+        <v>0.0101015254455375</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.0571027591215536</v>
+        <v>-0.0395085236569034</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.0092372770846348</v>
+        <v>0.0156047289864664</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.0483536678539823</v>
+        <v>0.00348089254676056</v>
       </c>
     </row>
     <row r="102">
@@ -3313,22 +3313,22 @@
         <v>107</v>
       </c>
       <c r="B102" t="n">
-        <v>0.00440587666453762</v>
+        <v>0.00824757881119759</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.000621223500699063</v>
+        <v>-0.0158924495114562</v>
       </c>
       <c r="D102" t="n">
-        <v>0.000538664304381457</v>
+        <v>-0.0126102154052459</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.0126590298821159</v>
+        <v>0.00230131602105449</v>
       </c>
       <c r="F102" t="n">
-        <v>0.00455330469931952</v>
+        <v>-0.0165223712653624</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0863451745878031</v>
+        <v>0.09176614875499</v>
       </c>
     </row>
     <row r="103">
@@ -3336,22 +3336,22 @@
         <v>108</v>
       </c>
       <c r="B103" t="n">
-        <v>0.207779171049996</v>
+        <v>0.00100428700194261</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.0218619100844488</v>
+        <v>-0.0320451969592129</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.0082421303030639</v>
+        <v>0.0169795750129315</v>
       </c>
       <c r="E103" t="n">
-        <v>0.042139758550775</v>
+        <v>-0.00222263319693046</v>
       </c>
       <c r="F103" t="n">
-        <v>0.103466115643602</v>
+        <v>0.0126895573808783</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0460431128144281</v>
+        <v>-0.0894530581053949</v>
       </c>
     </row>
     <row r="104">
@@ -3359,22 +3359,22 @@
         <v>109</v>
       </c>
       <c r="B104" t="n">
-        <v>0.0619748709560854</v>
+        <v>0.202275119365921</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0129233833249912</v>
+        <v>0.0559083822990537</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.0646004610853237</v>
+        <v>-0.0100658412403664</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0512134428746326</v>
+        <v>-0.194154816383981</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.207737596946624</v>
+        <v>0.267991167228072</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.0100200739180379</v>
+        <v>0.0346427005478229</v>
       </c>
     </row>
     <row r="105">
@@ -3382,22 +3382,22 @@
         <v>110</v>
       </c>
       <c r="B105" t="n">
-        <v>0.0955098103272781</v>
+        <v>0.109187046865428</v>
       </c>
       <c r="C105" t="n">
-        <v>0.108173012161509</v>
+        <v>0.0116075504744826</v>
       </c>
       <c r="D105" t="n">
-        <v>0.0622750514158867</v>
+        <v>-0.0209654109664058</v>
       </c>
       <c r="E105" t="n">
-        <v>0.21399713908239</v>
+        <v>-0.0584655049484297</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.137089718838115</v>
+        <v>0.0901616077627789</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.0128216193110209</v>
+        <v>-0.0671457866933146</v>
       </c>
     </row>
     <row r="106">
@@ -3405,22 +3405,22 @@
         <v>111</v>
       </c>
       <c r="B106" t="n">
-        <v>0.216758115955857</v>
+        <v>0.039928358607264</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.0223542500814519</v>
+        <v>-0.0208119992448072</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.0120602369866817</v>
+        <v>0.0173497427945694</v>
       </c>
       <c r="E106" t="n">
-        <v>0.0438926531813392</v>
+        <v>-0.0127797759001378</v>
       </c>
       <c r="F106" t="n">
-        <v>0.09755455803364</v>
+        <v>0.0465829442138955</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0089260372136464</v>
+        <v>-0.000138363346590765</v>
       </c>
     </row>
     <row r="107">
@@ -3428,22 +3428,22 @@
         <v>112</v>
       </c>
       <c r="B107" t="n">
-        <v>-0.0216910027158766</v>
+        <v>-0.0321896379959616</v>
       </c>
       <c r="C107" t="n">
-        <v>0.251569690442843</v>
+        <v>0.0191422860305271</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.0159585906984353</v>
+        <v>0.0138937082889285</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.010616501495115</v>
+        <v>-0.0183225640827699</v>
       </c>
       <c r="F107" t="n">
-        <v>0.213630250999655</v>
+        <v>-0.00139010832855707</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.0213526778853232</v>
+        <v>0.0203277996605591</v>
       </c>
     </row>
     <row r="108">
@@ -3451,22 +3451,22 @@
         <v>113</v>
       </c>
       <c r="B108" t="n">
-        <v>0.0529217814583625</v>
+        <v>0.102112263485813</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0110355771214506</v>
+        <v>0.178794583784247</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.055163833839839</v>
+        <v>0.0669838144096066</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0437323481231954</v>
+        <v>0.365371521792395</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.177391958009638</v>
+        <v>-0.00217462071176539</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.010605559292029</v>
+        <v>-0.0238353581025469</v>
       </c>
     </row>
     <row r="109">
@@ -3474,22 +3474,22 @@
         <v>114</v>
       </c>
       <c r="B109" t="n">
-        <v>0.162533587839162</v>
+        <v>0.118046775221005</v>
       </c>
       <c r="C109" t="n">
-        <v>0.183856172928122</v>
+        <v>0.0207150813409663</v>
       </c>
       <c r="D109" t="n">
-        <v>0.0605100151391801</v>
+        <v>0.0317082661521877</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.0030959531301365</v>
+        <v>-0.0621753806464647</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.0659226343707343</v>
+        <v>0.188434674336212</v>
       </c>
       <c r="G109" t="n">
-        <v>0.00442576095780489</v>
+        <v>-0.0333397981056795</v>
       </c>
     </row>
     <row r="110">
@@ -3497,22 +3497,22 @@
         <v>115</v>
       </c>
       <c r="B110" t="n">
-        <v>0.00465455908839999</v>
+        <v>0.011809992050328</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.00286262586205472</v>
+        <v>-0.0218071018459441</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.00567439889625549</v>
+        <v>-0.00221192414393415</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.0142015640524306</v>
+        <v>0.000375479326064364</v>
       </c>
       <c r="F110" t="n">
-        <v>0.00665593497996421</v>
+        <v>-0.0149856350553797</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0883691957259457</v>
+        <v>0.0905921423198863</v>
       </c>
     </row>
     <row r="111">
@@ -3520,22 +3520,22 @@
         <v>116</v>
       </c>
       <c r="B111" t="n">
-        <v>0.00241454689790139</v>
+        <v>0.00476069909626213</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.00205463121649567</v>
+        <v>-0.0220721706942494</v>
       </c>
       <c r="D111" t="n">
-        <v>0.0017046314614328</v>
+        <v>-0.0122270365082954</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.0142006125867433</v>
+        <v>-0.0092900998365682</v>
       </c>
       <c r="F111" t="n">
-        <v>0.00999992504495582</v>
+        <v>-0.0186419734758128</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0439315775764718</v>
+        <v>0.0463993934844458</v>
       </c>
     </row>
     <row r="112">
@@ -3543,22 +3543,22 @@
         <v>117</v>
       </c>
       <c r="B112" t="n">
-        <v>0</v>
+        <v>0.0965376163651931</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>-0.261017303343067</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>-0.230199463999935</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>0.0865599335746182</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>-0.0264554691311173</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>0.0184882675174324</v>
       </c>
     </row>
     <row r="113">
@@ -3566,22 +3566,22 @@
         <v>118</v>
       </c>
       <c r="B113" t="n">
-        <v>0.0983431634932607</v>
+        <v>0.0222733162321837</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0854717330113679</v>
+        <v>0.0214875176853009</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.170758641663904</v>
+        <v>-0.0144790670807686</v>
       </c>
       <c r="E113" t="n">
-        <v>0.0930185077749976</v>
+        <v>-0.0134282135463501</v>
       </c>
       <c r="F113" t="n">
-        <v>0.12294756510716</v>
+        <v>-0.00261155786870762</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.0429141061523367</v>
+        <v>0.0893224830216871</v>
       </c>
     </row>
     <row r="114">
@@ -3589,22 +3589,22 @@
         <v>119</v>
       </c>
       <c r="B114" t="n">
-        <v>0.00913936440034367</v>
+        <v>0.0243547771728981</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.00519352534560136</v>
+        <v>-0.03150573223893</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.0146427675240177</v>
+        <v>0.00533829201957185</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.0164669340060114</v>
+        <v>-0.0145606881946141</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0153262306823988</v>
+        <v>-0.0117127960253572</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0874414610913162</v>
+        <v>0.094433037230671</v>
       </c>
     </row>
     <row r="115">
@@ -3612,22 +3612,22 @@
         <v>120</v>
       </c>
       <c r="B115" t="n">
-        <v>-0.000771712319715831</v>
+        <v>-0.00281590895334617</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.00378751419471354</v>
+        <v>-0.0178197742238294</v>
       </c>
       <c r="D115" t="n">
-        <v>0.00596652436195192</v>
+        <v>-0.0110055692444259</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.0109160818518857</v>
+        <v>-0.0152392502180126</v>
       </c>
       <c r="F115" t="n">
-        <v>0.00979116732821159</v>
+        <v>-0.0230843983494457</v>
       </c>
       <c r="G115" t="n">
-        <v>0.087688760082343</v>
+        <v>0.0904948018378706</v>
       </c>
     </row>
     <row r="116">
@@ -3635,22 +3635,22 @@
         <v>121</v>
       </c>
       <c r="B116" t="n">
-        <v>0.00427451044212488</v>
+        <v>0.00852118779704109</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.00412412840175225</v>
+        <v>-0.022359076417885</v>
       </c>
       <c r="D116" t="n">
-        <v>0.000759381565796883</v>
+        <v>-0.0110247204264064</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.0142223659589028</v>
+        <v>-0.0143262737563715</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0116163339645214</v>
+        <v>-0.0244193586574639</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0429729412005636</v>
+        <v>0.0463414221184031</v>
       </c>
     </row>
     <row r="117">
@@ -3658,22 +3658,22 @@
         <v>122</v>
       </c>
       <c r="B117" t="n">
-        <v>0.00735684219782732</v>
+        <v>0.0186864802532223</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.00257873943895695</v>
+        <v>-0.0237554663482267</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.00988629969448517</v>
+        <v>-0.000130874954076214</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.0122927979246217</v>
+        <v>-0.0137521065678475</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0129881941174982</v>
+        <v>-0.00624037043541169</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.04092764431354</v>
+        <v>-0.0448114459698023</v>
       </c>
     </row>
     <row r="118">
@@ -3704,22 +3704,22 @@
         <v>124</v>
       </c>
       <c r="B119" t="n">
-        <v>0.000237496153500978</v>
+        <v>0.00437371785159518</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.00154136209721116</v>
+        <v>-0.0225902532313866</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.00567714858217817</v>
+        <v>0.00249407757036373</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.00954257500206671</v>
+        <v>-0.0157217262923958</v>
       </c>
       <c r="F119" t="n">
-        <v>0.012542997269449</v>
+        <v>0.000895720509625823</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0424381320647815</v>
+        <v>-0.044363018973753</v>
       </c>
     </row>
     <row r="120">
@@ -3727,22 +3727,22 @@
         <v>125</v>
       </c>
       <c r="B120" t="n">
-        <v>-0.0279019867543447</v>
+        <v>0.0304961359630437</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.147453098622535</v>
+        <v>-0.0604695115560925</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.223684385220838</v>
+        <v>-0.000650686986294585</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.269922268733227</v>
+        <v>-0.018405850623779</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.121997865697709</v>
+        <v>-0.0190717132582681</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.0028635999571273</v>
+        <v>0.0899260121506821</v>
       </c>
     </row>
     <row r="121">
@@ -3750,22 +3750,22 @@
         <v>126</v>
       </c>
       <c r="B121" t="n">
-        <v>0.00398933746926226</v>
+        <v>0.00949897952855844</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00162860976327089</v>
+        <v>-0.0186777082904124</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.00351999858584925</v>
+        <v>-0.00890958566006731</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.0118256201373089</v>
+        <v>-0.000436878326329391</v>
       </c>
       <c r="F121" t="n">
-        <v>0.00711669527582424</v>
+        <v>-0.00199203742021849</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.082782522146948</v>
+        <v>-0.0888783508285495</v>
       </c>
     </row>
     <row r="122">
@@ -3773,22 +3773,22 @@
         <v>127</v>
       </c>
       <c r="B122" t="n">
-        <v>-0.00590139353400529</v>
+        <v>-0.0116832562513509</v>
       </c>
       <c r="C122" t="n">
-        <v>0.00183284220408217</v>
+        <v>-0.0193913163288249</v>
       </c>
       <c r="D122" t="n">
-        <v>0.00556353268933783</v>
+        <v>-0.0100796930213195</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.0107499180768635</v>
+        <v>-0.0039451430065742</v>
       </c>
       <c r="F122" t="n">
-        <v>0.00707175135274497</v>
+        <v>-0.00226787560494046</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0857591087987099</v>
+        <v>0.0902257710905345</v>
       </c>
     </row>
     <row r="123">
@@ -3796,22 +3796,22 @@
         <v>128</v>
       </c>
       <c r="B123" t="n">
-        <v>0.0181912762443635</v>
+        <v>0.0420444127228009</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.00120346271458516</v>
+        <v>-0.0354082084124411</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.0182469566657982</v>
+        <v>-0.00796990046096838</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.0186699663287584</v>
+        <v>-0.0256439129387366</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0230916321986965</v>
+        <v>-0.0030945516940245</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0461927366183071</v>
+        <v>0.0466706044676657</v>
       </c>
     </row>
     <row r="124">
@@ -3819,22 +3819,22 @@
         <v>129</v>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>0.214509476937469</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>0.169949706522856</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>-0.0986900598217087</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>-0.0914008266838585</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>-0.0683879583768455</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>-0.00672647672479234</v>
       </c>
     </row>
     <row r="125">
@@ -3842,22 +3842,22 @@
         <v>130</v>
       </c>
       <c r="B125" t="n">
-        <v>0.00562021591678684</v>
+        <v>0.0162325684935257</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.00364173229038207</v>
+        <v>-0.0150534475190431</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.0125891092186781</v>
+        <v>0.0113617341823124</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.00774466833943145</v>
+        <v>-0.000449901553248007</v>
       </c>
       <c r="F125" t="n">
-        <v>0.00493080642851767</v>
+        <v>-0.00372098339390614</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.0440963726417288</v>
+        <v>-0.0450115581503963</v>
       </c>
     </row>
     <row r="126">
@@ -3865,22 +3865,22 @@
         <v>131</v>
       </c>
       <c r="B126" t="n">
-        <v>0.00610357475822569</v>
+        <v>0.0111430659700834</v>
       </c>
       <c r="C126" t="n">
-        <v>0.00119487577169756</v>
+        <v>-0.0179441122518211</v>
       </c>
       <c r="D126" t="n">
-        <v>0.000945879926245298</v>
+        <v>-0.0186601092883804</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.0141359040698365</v>
+        <v>0.000265083979337304</v>
       </c>
       <c r="F126" t="n">
-        <v>0.00668644436875768</v>
+        <v>-0.0139729795998599</v>
       </c>
       <c r="G126" t="n">
-        <v>0.126639107358889</v>
+        <v>0.137145478603422</v>
       </c>
     </row>
     <row r="127">
@@ -3888,22 +3888,22 @@
         <v>132</v>
       </c>
       <c r="B127" t="n">
-        <v>-0.0051581268402467</v>
+        <v>-0.010741922669771</v>
       </c>
       <c r="C127" t="n">
-        <v>0.00111286013540073</v>
+        <v>-0.00786290563955333</v>
       </c>
       <c r="D127" t="n">
-        <v>0.00407247157134736</v>
+        <v>-0.00366024631782151</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.00901584952846828</v>
+        <v>0.0260054036229405</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.00753523191172577</v>
+        <v>-0.00910867969887503</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0842608436184606</v>
+        <v>0.090326113640403</v>
       </c>
     </row>
     <row r="128">
@@ -3911,22 +3911,22 @@
         <v>133</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>0.131481738008626</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>0.106163932687775</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>0.271126731888413</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>-0.0842559256894294</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>-0.273243057178281</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>-0.00668424852547456</v>
       </c>
     </row>
     <row r="129">
@@ -3934,22 +3934,22 @@
         <v>134</v>
       </c>
       <c r="B129" t="n">
-        <v>0.00489312513113306</v>
+        <v>0.0108140611444156</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.000045635946710761</v>
+        <v>-0.0322413778444468</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.000867239664407625</v>
+        <v>-0.0177226768573701</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.0194357489258649</v>
+        <v>-0.0142776366806685</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0159905852602478</v>
+        <v>-0.0137446492311143</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0832857135811692</v>
+        <v>-0.0868436862334136</v>
       </c>
     </row>
     <row r="130">
@@ -3957,22 +3957,22 @@
         <v>135</v>
       </c>
       <c r="B130" t="n">
-        <v>0.00561482159213791</v>
+        <v>0.0144635615092941</v>
       </c>
       <c r="C130" t="n">
-        <v>0.00267963439142147</v>
+        <v>-0.0262740442653458</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.0073069661310748</v>
+        <v>-0.00904825040094726</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.0150130535351663</v>
+        <v>-0.00420256093180313</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0114931932949195</v>
+        <v>0.00379896578787164</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0845532144163965</v>
+        <v>0.0924898222144486</v>
       </c>
     </row>
     <row r="131">
@@ -3980,22 +3980,22 @@
         <v>136</v>
       </c>
       <c r="B131" t="n">
-        <v>0.0135740937491899</v>
+        <v>0.0290468866011963</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.00102321189577379</v>
+        <v>-0.000775207108102059</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.0123906266343266</v>
+        <v>0.00165286839185729</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.00397416297801674</v>
+        <v>0.0113428594888185</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.00198802005191114</v>
+        <v>-0.0052142683942725</v>
       </c>
       <c r="G131" t="n">
-        <v>0.125363865611847</v>
+        <v>0.135341549223006</v>
       </c>
     </row>
     <row r="132">
@@ -4003,22 +4003,22 @@
         <v>137</v>
       </c>
       <c r="B132" t="n">
-        <v>0.0981523999726944</v>
+        <v>0.00251771681973988</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0960473315199927</v>
+        <v>-0.0395014003938543</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.199632141744517</v>
+        <v>-0.0115262332304485</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0718668639783643</v>
+        <v>-0.00446122289397388</v>
       </c>
       <c r="F132" t="n">
-        <v>0.155502108750509</v>
+        <v>-0.0181230053340054</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.0164355130433886</v>
+        <v>-0.132936556880731</v>
       </c>
     </row>
     <row r="133">
@@ -4026,22 +4026,22 @@
         <v>138</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.000682472721836959</v>
+        <v>-0.000707331909900875</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.00742508525369083</v>
+        <v>-0.0163837456400542</v>
       </c>
       <c r="D133" t="n">
-        <v>0.00130359832821118</v>
+        <v>0.00140592151005861</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.0100266112894262</v>
+        <v>-0.00942976164485681</v>
       </c>
       <c r="F133" t="n">
-        <v>0.00630675857412337</v>
+        <v>-0.0281597220717033</v>
       </c>
       <c r="G133" t="n">
-        <v>-0.0393682355847545</v>
+        <v>-0.0436677396825602</v>
       </c>
     </row>
     <row r="134">
@@ -4049,22 +4049,22 @@
         <v>139</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.00234865802329089</v>
+        <v>-0.00402022943406505</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.0033915037019674</v>
+        <v>-0.0021720604488526</v>
       </c>
       <c r="D134" t="n">
-        <v>0.000520697559276403</v>
+        <v>0.00578485473186406</v>
       </c>
       <c r="E134" t="n">
-        <v>0.00101808816904254</v>
+        <v>-0.0114269888282955</v>
       </c>
       <c r="F134" t="n">
-        <v>0.00353652755803408</v>
+        <v>-0.00507351656361396</v>
       </c>
       <c r="G134" t="n">
-        <v>0.084778169291793</v>
+        <v>0.090111504531493</v>
       </c>
     </row>
     <row r="135">
@@ -4072,22 +4072,22 @@
         <v>140</v>
       </c>
       <c r="B135" t="n">
-        <v>0.0019982569205158</v>
+        <v>0.00630567365043033</v>
       </c>
       <c r="C135" t="n">
-        <v>0.00175995727761081</v>
+        <v>-0.0271916287943555</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.00215389020670077</v>
+        <v>-0.0114633126796665</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.0109048893103006</v>
+        <v>-0.0318278728344858</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0209667085213112</v>
+        <v>0.00673209393624788</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0445132879612684</v>
+        <v>0.0478680868965315</v>
       </c>
     </row>
     <row r="136">
@@ -4095,22 +4095,22 @@
         <v>141</v>
       </c>
       <c r="B136" t="n">
-        <v>0.00151327889112393</v>
+        <v>0.0091515233444982</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.00787011885682969</v>
+        <v>-0.0346822009174581</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.0096964144059843</v>
+        <v>0.0102159231494646</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.0163421580109105</v>
+        <v>-0.0208081615583702</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0166445148668838</v>
+        <v>-0.0171267454475928</v>
       </c>
       <c r="G136" t="n">
-        <v>0.088068834739345</v>
+        <v>0.0917417876768983</v>
       </c>
     </row>
     <row r="137">
@@ -4118,22 +4118,22 @@
         <v>142</v>
       </c>
       <c r="B137" t="n">
-        <v>0.000430200011720803</v>
+        <v>0.0112538267646298</v>
       </c>
       <c r="C137" t="n">
-        <v>0.00153561062729504</v>
+        <v>-0.0235772301910244</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.0202496469329572</v>
+        <v>0.0225251032948556</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.0040041036476172</v>
+        <v>-0.0172242632876573</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0146832649698847</v>
+        <v>0.0356519947646334</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.123915168324698</v>
+        <v>-0.134734287456648</v>
       </c>
     </row>
     <row r="138">
@@ -4141,22 +4141,22 @@
         <v>143</v>
       </c>
       <c r="B138" t="n">
-        <v>0.000288431706266048</v>
+        <v>0.00539392881840961</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.00728340144971953</v>
+        <v>-0.0290105251357674</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.0077645955911067</v>
+        <v>0.0100501667305141</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.0191779799104344</v>
+        <v>0.0126072903997971</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0026196294763216</v>
+        <v>-0.0267247106427512</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0871728534183084</v>
+        <v>0.0908153969432733</v>
       </c>
     </row>
     <row r="139">
@@ -4164,22 +4164,22 @@
         <v>144</v>
       </c>
       <c r="B139" t="n">
-        <v>0.0000710991708298249</v>
+        <v>0.00117193934077849</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.00300445576516616</v>
+        <v>-0.034119468087123</v>
       </c>
       <c r="D139" t="n">
-        <v>0.0019548885373677</v>
+        <v>-0.0126648634652915</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.0217063585414255</v>
+        <v>-0.00590892721676485</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0119297664494688</v>
+        <v>-0.0250800063105067</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.0830145143470084</v>
+        <v>-0.0880124922395717</v>
       </c>
     </row>
     <row r="140">
@@ -4187,22 +4187,22 @@
         <v>145</v>
       </c>
       <c r="B140" t="n">
-        <v>0.0642903947859444</v>
+        <v>-0.0768668572464956</v>
       </c>
       <c r="C140" t="n">
-        <v>0.127538643741976</v>
+        <v>-0.0801353303277584</v>
       </c>
       <c r="D140" t="n">
-        <v>0.108713545250162</v>
+        <v>-0.0241616688201888</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.0454551778020649</v>
+        <v>-0.176583962180606</v>
       </c>
       <c r="F140" t="n">
-        <v>0.14622214196541</v>
+        <v>-0.118437358294827</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0361571220599572</v>
+        <v>-0.00668287888591436</v>
       </c>
     </row>
     <row r="141">
@@ -4210,22 +4210,22 @@
         <v>146</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>0.313856763331517</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>0.0288033064478646</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>-0.151019241840547</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>0.00697757587062522</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>-0.166352097971467</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>0.039233682223544</v>
       </c>
     </row>
     <row r="142">
@@ -4233,22 +4233,22 @@
         <v>147</v>
       </c>
       <c r="B142" t="n">
-        <v>0.00552666002469074</v>
+        <v>0.0123286847584207</v>
       </c>
       <c r="C142" t="n">
-        <v>0.00736383917185837</v>
+        <v>-0.0349276982796806</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.00316823487229469</v>
+        <v>-0.0247938095553362</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.0288802931623972</v>
+        <v>0.0364733716579921</v>
       </c>
       <c r="F142" t="n">
-        <v>0.000579683267846792</v>
+        <v>-0.00689905669570953</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.000808952133053042</v>
+        <v>0.00152442136626006</v>
       </c>
     </row>
     <row r="143">
@@ -4256,22 +4256,22 @@
         <v>148</v>
       </c>
       <c r="B143" t="n">
-        <v>0.219963596131201</v>
+        <v>0.04095289526286</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.0162855417439155</v>
+        <v>-0.0145368468356082</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.0040980735493725</v>
+        <v>-0.00988947313524216</v>
       </c>
       <c r="E143" t="n">
-        <v>0.0482072108053491</v>
+        <v>-0.0361506491302771</v>
       </c>
       <c r="F143" t="n">
-        <v>0.107176507323956</v>
+        <v>0.0446283954238428</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.00696710983001448</v>
+        <v>0.110506827519375</v>
       </c>
     </row>
     <row r="144">
@@ -4279,22 +4279,22 @@
         <v>149</v>
       </c>
       <c r="B144" t="n">
-        <v>0.0722387174376161</v>
+        <v>0.239843595158932</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.114569441125373</v>
+        <v>0.0230257412724803</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.0656781707601697</v>
+        <v>-0.0213481112316045</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.156727521804759</v>
+        <v>-0.152980167029774</v>
       </c>
       <c r="F144" t="n">
-        <v>0.19083076574627</v>
+        <v>0.0900904769824454</v>
       </c>
       <c r="G144" t="n">
-        <v>0.00918240089688057</v>
+        <v>-0.017715265611388</v>
       </c>
     </row>
     <row r="145">
@@ -4302,22 +4302,22 @@
         <v>150</v>
       </c>
       <c r="B145" t="n">
-        <v>0.00300610816446699</v>
+        <v>0.00769012493213039</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.00336377397247927</v>
+        <v>-0.0256962683773861</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.00208572046765627</v>
+        <v>-0.00660448741682842</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.0154653298389081</v>
+        <v>-0.00974522854986658</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0111027740077475</v>
+        <v>-0.0184029807305374</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.080943836686363</v>
+        <v>-0.0896878599438543</v>
       </c>
     </row>
     <row r="146">
@@ -4325,22 +4325,22 @@
         <v>151</v>
       </c>
       <c r="B146" t="n">
-        <v>0.00409120253513048</v>
+        <v>0.0113824040029047</v>
       </c>
       <c r="C146" t="n">
-        <v>0.00055906992482723</v>
+        <v>-0.039748293937046</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.00455453222065454</v>
+        <v>-0.0139742254474733</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.0233763151466203</v>
+        <v>-0.00889057423421992</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0165291299300553</v>
+        <v>-0.00945366289324713</v>
       </c>
       <c r="G146" t="n">
-        <v>0.00119941727476114</v>
+        <v>0.00375028430585353</v>
       </c>
     </row>
     <row r="147">
@@ -4394,22 +4394,22 @@
         <v>154</v>
       </c>
       <c r="B149" t="n">
-        <v>0.192563342503957</v>
+        <v>0.0716727641892187</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.0216300023794778</v>
+        <v>-0.063301906073406</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.0147002365833531</v>
+        <v>-0.0065978169011253</v>
       </c>
       <c r="E149" t="n">
-        <v>0.00728818429271977</v>
+        <v>-0.0433476019505738</v>
       </c>
       <c r="F149" t="n">
-        <v>0.104096878254648</v>
+        <v>0.0349096270301796</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.0123297019994375</v>
+        <v>0.0231163887022238</v>
       </c>
     </row>
     <row r="150">
@@ -4417,22 +4417,22 @@
         <v>155</v>
       </c>
       <c r="B150" t="n">
-        <v>0.1280691600202</v>
+        <v>0.0323462625721955</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.099687694246069</v>
+        <v>-0.0223677646956597</v>
       </c>
       <c r="D150" t="n">
-        <v>0.168696180109174</v>
+        <v>-0.0237926721639066</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.0492641862213483</v>
+        <v>0.00360138306846486</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.0266801269810652</v>
+        <v>-0.00742150933800261</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.0239136815279013</v>
+        <v>-0.130769486204934</v>
       </c>
     </row>
     <row r="151">
@@ -4440,22 +4440,22 @@
         <v>156</v>
       </c>
       <c r="B151" t="n">
-        <v>0.00470699841040271</v>
+        <v>0.010569973277645</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.000032934091305751</v>
+        <v>-0.0251548764698937</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.0021451556106213</v>
+        <v>-0.0127116663882189</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.0159614412070182</v>
+        <v>-0.00602850375012164</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0107719944033984</v>
+        <v>-0.0112833328019576</v>
       </c>
       <c r="G151" t="n">
-        <v>0.00509504666621332</v>
+        <v>0.000586649691871163</v>
       </c>
     </row>
     <row r="152">
@@ -4463,22 +4463,22 @@
         <v>157</v>
       </c>
       <c r="B152" t="n">
-        <v>0.170279063824519</v>
+        <v>0.275730656573302</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.119864965364157</v>
+        <v>-0.0258152712970385</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.161220684719129</v>
+        <v>0.0118119446927091</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.147386749725546</v>
+        <v>-0.178246442077461</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.0157235992904741</v>
+        <v>0.284963744790194</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.0191672773366942</v>
+        <v>-0.038010481133059</v>
       </c>
     </row>
     <row r="153">
@@ -4486,22 +4486,22 @@
         <v>158</v>
       </c>
       <c r="B153" t="n">
-        <v>0.0999010888519516</v>
+        <v>0.03630314984074</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0762160422767331</v>
+        <v>-0.0285378657044345</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.175665842572325</v>
+        <v>-0.0147695612479632</v>
       </c>
       <c r="E153" t="n">
-        <v>0.0600353009959894</v>
+        <v>-0.0144150257050714</v>
       </c>
       <c r="F153" t="n">
-        <v>0.134295659930661</v>
+        <v>-0.0334105842595635</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.0501432886846296</v>
+        <v>-0.0181160016597424</v>
       </c>
     </row>
     <row r="154">
@@ -4509,22 +4509,22 @@
         <v>159</v>
       </c>
       <c r="B154" t="n">
-        <v>0.0140018751615711</v>
+        <v>0.0252057332452632</v>
       </c>
       <c r="C154" t="n">
-        <v>0.00121391501637242</v>
+        <v>-0.0219190550367118</v>
       </c>
       <c r="D154" t="n">
-        <v>0.00153771896278626</v>
+        <v>-0.0325599497885203</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.0151658253847681</v>
+        <v>-0.0265162941470842</v>
       </c>
       <c r="F154" t="n">
-        <v>0.018796645899399</v>
+        <v>-0.0178362898394223</v>
       </c>
       <c r="G154" t="n">
-        <v>-0.0420761947529749</v>
+        <v>-0.0401979143482668</v>
       </c>
     </row>
     <row r="155">
@@ -4532,22 +4532,22 @@
         <v>160</v>
       </c>
       <c r="B155" t="n">
-        <v>0.000274422745921897</v>
+        <v>0.00131445719758808</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.00777526350258392</v>
+        <v>-0.024854222947092</v>
       </c>
       <c r="D155" t="n">
-        <v>0.00171764090145588</v>
+        <v>-0.0034284326475756</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.0147910231159678</v>
+        <v>-0.0158177176411496</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0113111973166867</v>
+        <v>-0.0325270698855993</v>
       </c>
       <c r="G155" t="n">
-        <v>0.042229688621679</v>
+        <v>0.047031508146476</v>
       </c>
     </row>
     <row r="156">
@@ -4555,22 +4555,22 @@
         <v>161</v>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>0.134289331038609</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>0.141126104150319</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>0.228191303736618</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>0.0601418932465719</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>-0.207801658878756</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>0.0102436628066197</v>
       </c>
     </row>
     <row r="157">
@@ -4578,22 +4578,22 @@
         <v>162</v>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>-0.0140076311595171</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>-0.0185973187773954</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>0.207227079200689</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>-0.272568120973264</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>-0.450438765905678</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>0.00069804515976577</v>
       </c>
     </row>
     <row r="158">
@@ -4601,22 +4601,22 @@
         <v>163</v>
       </c>
       <c r="B158" t="n">
-        <v>0.00534716633673498</v>
+        <v>0.0135455556933377</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.00479114567644085</v>
+        <v>-0.0242448586669253</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.00680247469159078</v>
+        <v>-0.0000511175888186211</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.0175819923237618</v>
+        <v>0.00903254121541002</v>
       </c>
       <c r="F158" t="n">
-        <v>0.00382906628238757</v>
+        <v>-0.0242711726894863</v>
       </c>
       <c r="G158" t="n">
-        <v>0.002046143396637</v>
+        <v>0.000487539656902435</v>
       </c>
     </row>
     <row r="159">
@@ -4624,22 +4624,22 @@
         <v>164</v>
       </c>
       <c r="B159" t="n">
-        <v>0.210032271786546</v>
+        <v>0.0756023172089219</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.0251173832019417</v>
+        <v>-0.0279033355593058</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.0139843529449832</v>
+        <v>0.00324609401393094</v>
       </c>
       <c r="E159" t="n">
-        <v>0.0328442081488694</v>
+        <v>-0.0514019953908408</v>
       </c>
       <c r="F159" t="n">
-        <v>0.10209882782383</v>
+        <v>0.0394286576591415</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0119439841783297</v>
+        <v>0.109468647067364</v>
       </c>
     </row>
     <row r="160">
@@ -4647,22 +4647,22 @@
         <v>165</v>
       </c>
       <c r="B160" t="n">
-        <v>0.0023911913986537</v>
+        <v>0.00804547293343398</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.00324989357050495</v>
+        <v>-0.0261185571826339</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.00516118099732806</v>
+        <v>-0.000860285832822755</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.0138475789051479</v>
+        <v>-0.0121553858588616</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0121404267998257</v>
+        <v>-0.0111705848740072</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.12457936486414</v>
+        <v>-0.133584017269234</v>
       </c>
     </row>
     <row r="161">
@@ -4670,22 +4670,22 @@
         <v>166</v>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>0.05921219389588</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>0.103678238060376</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>0.0388421377737683</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>0.211869256971371</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>-0.00126100488657701</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>-0.00938885395942997</v>
       </c>
     </row>
     <row r="162">
@@ -4693,22 +4693,22 @@
         <v>167</v>
       </c>
       <c r="B162" t="n">
-        <v>0.0013722134917145</v>
+        <v>0.0119802055364456</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.0295193038986194</v>
+        <v>-0.00719967758988814</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.0190204637539225</v>
+        <v>0.0617692393189657</v>
       </c>
       <c r="E162" t="n">
-        <v>0.00360362615342846</v>
+        <v>-0.0352848548327605</v>
       </c>
       <c r="F162" t="n">
-        <v>0.00732596300078276</v>
+        <v>-0.0524072667938247</v>
       </c>
       <c r="G162" t="n">
-        <v>0.045233340114455</v>
+        <v>0.045087396443126</v>
       </c>
     </row>
     <row r="163">
@@ -4716,22 +4716,22 @@
         <v>168</v>
       </c>
       <c r="B163" t="n">
-        <v>0.001692939318381</v>
+        <v>0.0228971976097806</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.00695428292215036</v>
+        <v>-0.0759280161201655</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.0352842673600772</v>
+        <v>0.0359089161231808</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.0349886805862225</v>
+        <v>-0.00909077141617366</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0262136155637684</v>
+        <v>0.00818659323652816</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0162160995450509</v>
+        <v>0.0201157436286898</v>
       </c>
     </row>
     <row r="164">
@@ -4739,22 +4739,22 @@
         <v>169</v>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>0.194572083055346</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>0.127486529625524</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>-0.12008712775504</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>-0.180890457054034</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>0.0557591658429752</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>0.0496565070502339</v>
       </c>
     </row>
     <row r="165">
@@ -4762,22 +4762,22 @@
         <v>170</v>
       </c>
       <c r="B165" t="n">
-        <v>-0.00173599587875068</v>
+        <v>-0.00318934750908519</v>
       </c>
       <c r="C165" t="n">
-        <v>0.00215785559525962</v>
+        <v>-0.0143178273458585</v>
       </c>
       <c r="D165" t="n">
-        <v>0.00177129929193106</v>
+        <v>-0.00838839475980648</v>
       </c>
       <c r="E165" t="n">
-        <v>-0.0102678841727596</v>
+        <v>0.00883409368038521</v>
       </c>
       <c r="F165" t="n">
-        <v>0.00158850189369932</v>
+        <v>-0.00303871323102027</v>
       </c>
       <c r="G165" t="n">
-        <v>0.127293513343487</v>
+        <v>0.134966746486175</v>
       </c>
     </row>
     <row r="166">
@@ -4785,22 +4785,22 @@
         <v>171</v>
       </c>
       <c r="B166" t="n">
-        <v>0.000679193565959966</v>
+        <v>0.00535810106262242</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.0037986401521973</v>
+        <v>-0.0206305835598782</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.00615809053084277</v>
+        <v>0.00606923941626352</v>
       </c>
       <c r="E166" t="n">
-        <v>-0.00750380267564219</v>
+        <v>-0.0220376154566832</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0136605101185963</v>
+        <v>-0.00289270388505604</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0863272547806411</v>
+        <v>0.0884932236683335</v>
       </c>
     </row>
     <row r="167">
@@ -4808,22 +4808,22 @@
         <v>172</v>
       </c>
       <c r="B167" t="n">
-        <v>-0.146678615615069</v>
+        <v>-0.0204461246144318</v>
       </c>
       <c r="C167" t="n">
-        <v>0.103835167488591</v>
+        <v>-0.0265654865241478</v>
       </c>
       <c r="D167" t="n">
-        <v>0.132688531436518</v>
+        <v>0.0246342797510027</v>
       </c>
       <c r="E167" t="n">
-        <v>0.103556442362155</v>
+        <v>-0.0514343796538591</v>
       </c>
       <c r="F167" t="n">
-        <v>0.015787634087283</v>
+        <v>-0.0162842389271702</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0150475469391659</v>
+        <v>-0.0678586414003098</v>
       </c>
     </row>
     <row r="168">
@@ -4831,22 +4831,22 @@
         <v>173</v>
       </c>
       <c r="B168" t="n">
-        <v>0.0361295533781049</v>
+        <v>0.108094922544286</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.199144892775621</v>
+        <v>-0.0339966605457714</v>
       </c>
       <c r="D168" t="n">
-        <v>0.0318906842556929</v>
+        <v>0.00914318971006151</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.260083736886309</v>
+        <v>-0.05165760557987</v>
       </c>
       <c r="F168" t="n">
-        <v>0.161476823346145</v>
+        <v>0.0123566251507213</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0596102123811484</v>
+        <v>0.0500412371366979</v>
       </c>
     </row>
     <row r="169">
@@ -4854,22 +4854,22 @@
         <v>174</v>
       </c>
       <c r="B169" t="n">
-        <v>0.0035007310154449</v>
+        <v>0.00270270443583085</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.0019988438511542</v>
+        <v>-0.0154034305309216</v>
       </c>
       <c r="D169" t="n">
-        <v>0.00982487026368794</v>
+        <v>-0.0248867632936474</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.0131017384802903</v>
+        <v>-0.011239409351952</v>
       </c>
       <c r="F169" t="n">
-        <v>0.00858492694623437</v>
+        <v>-0.0305063270807039</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0456158176566385</v>
+        <v>0.0469565904123897</v>
       </c>
     </row>
     <row r="170">
@@ -4877,22 +4877,22 @@
         <v>175</v>
       </c>
       <c r="B170" t="n">
-        <v>0.0263984562120878</v>
+        <v>-0.0120893882551543</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.220143979456439</v>
+        <v>-0.0274594215641991</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.0794717502656586</v>
+        <v>0.0224354703790115</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0610332614945429</v>
+        <v>-0.038064376653763</v>
       </c>
       <c r="F170" t="n">
-        <v>0.141998966084677</v>
+        <v>-0.123458533861636</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0317934483676582</v>
+        <v>-0.0128942362094502</v>
       </c>
     </row>
     <row r="171">
@@ -4900,22 +4900,22 @@
         <v>176</v>
       </c>
       <c r="B171" t="n">
-        <v>0.00647386155235838</v>
+        <v>0.0101674981543915</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.00167460194134018</v>
+        <v>-0.0165023705725229</v>
       </c>
       <c r="D171" t="n">
-        <v>0.00453533813520346</v>
+        <v>-0.0212626244363961</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.014754576953735</v>
+        <v>-0.00214803253489618</v>
       </c>
       <c r="F171" t="n">
-        <v>0.00625149416434362</v>
+        <v>-0.0282672412381016</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.0420709387389597</v>
+        <v>-0.0395642038249428</v>
       </c>
     </row>
     <row r="172">
@@ -4923,22 +4923,22 @@
         <v>177</v>
       </c>
       <c r="B172" t="n">
-        <v>0.00524602962531251</v>
+        <v>0.0132434389748127</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.00222927528377321</v>
+        <v>-0.0255879456924688</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.00587409598782059</v>
+        <v>-0.00486212513919511</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.0150152655922694</v>
+        <v>-0.00831799814247122</v>
       </c>
       <c r="F172" t="n">
-        <v>0.0112821669676265</v>
+        <v>-0.0118745097488933</v>
       </c>
       <c r="G172" t="n">
-        <v>-0.0858416518090477</v>
+        <v>-0.0866382461306559</v>
       </c>
     </row>
     <row r="173">
@@ -4946,22 +4946,22 @@
         <v>178</v>
       </c>
       <c r="B173" t="n">
-        <v>-0.00561630944043675</v>
+        <v>0.00047612890357712</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.0168339789005277</v>
+        <v>-0.0662851729592737</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.0131426739505809</v>
+        <v>0.0251550271692152</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.0273799768646239</v>
+        <v>-0.0532095769294253</v>
       </c>
       <c r="F173" t="n">
-        <v>0.034881735216791</v>
+        <v>-0.0309362742573712</v>
       </c>
       <c r="G173" t="n">
-        <v>0.00945358765376211</v>
+        <v>0.00281209161834143</v>
       </c>
     </row>
     <row r="174">
@@ -4969,22 +4969,22 @@
         <v>179</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.00184942670403457</v>
+        <v>-0.00138845445336114</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.00962370054729871</v>
+        <v>-0.0257203388089959</v>
       </c>
       <c r="D174" t="n">
-        <v>-0.000638237048413302</v>
+        <v>0.00539311586116518</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.0154942582641064</v>
+        <v>-0.00722531991160824</v>
       </c>
       <c r="F174" t="n">
-        <v>0.00767866696878579</v>
+        <v>-0.0348312614104276</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0868115849988765</v>
+        <v>0.0911850693108336</v>
       </c>
     </row>
     <row r="175">
@@ -4992,22 +4992,22 @@
         <v>180</v>
       </c>
       <c r="B175" t="n">
-        <v>-0.00241482364655071</v>
+        <v>0.00724228565063526</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.0132560702277984</v>
+        <v>-0.0506810917010356</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.017983660830321</v>
+        <v>0.0301868055361633</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.0179319620911765</v>
+        <v>-0.045493109980518</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0287793298121077</v>
+        <v>-0.0120271506266185</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0497364134535756</v>
+        <v>0.0497284598303042</v>
       </c>
     </row>
     <row r="176">
@@ -5015,22 +5015,22 @@
         <v>181</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0156296335373794</v>
+        <v>0.0334465438449992</v>
       </c>
       <c r="C176" t="n">
-        <v>0.000961959987618712</v>
+        <v>-0.0505794164392866</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.00766976104748562</v>
+        <v>-0.0301924200972623</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.0336576891554109</v>
+        <v>-0.0102033933027758</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0221980143916785</v>
+        <v>-0.0229377456615612</v>
       </c>
       <c r="G176" t="n">
-        <v>0.00704306367132081</v>
+        <v>0.00390723096747295</v>
       </c>
     </row>
     <row r="177">
@@ -5038,22 +5038,22 @@
         <v>182</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0031512077124695</v>
+        <v>0.0109826905254251</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.00610094310441529</v>
+        <v>-0.0485714521013111</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.00621229747323436</v>
+        <v>-0.0053684856578767</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.0294379912756791</v>
+        <v>-0.00692304912568427</v>
       </c>
       <c r="F177" t="n">
-        <v>0.0165688964967107</v>
+        <v>-0.030719149555556</v>
       </c>
       <c r="G177" t="n">
-        <v>-0.0859582683126255</v>
+        <v>-0.0875292326936379</v>
       </c>
     </row>
     <row r="178">
@@ -5153,22 +5153,22 @@
         <v>187</v>
       </c>
       <c r="B182" t="n">
-        <v>0.015824382987037</v>
+        <v>0.0331684492498082</v>
       </c>
       <c r="C182" t="n">
-        <v>0.00678083668181395</v>
+        <v>-0.0275495664939364</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.00989939522168111</v>
+        <v>-0.025040733605349</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.0220432824233872</v>
+        <v>0.0145058676571732</v>
       </c>
       <c r="F182" t="n">
-        <v>0.00772760655775881</v>
+        <v>-0.000365938723268601</v>
       </c>
       <c r="G182" t="n">
-        <v>0.13346227330804</v>
+        <v>0.136110681511947</v>
       </c>
     </row>
     <row r="183">
@@ -5199,22 +5199,22 @@
         <v>189</v>
       </c>
       <c r="B184" t="n">
-        <v>-0.0853868130721877</v>
+        <v>0.181926261039064</v>
       </c>
       <c r="C184" t="n">
-        <v>0.0789545054760186</v>
+        <v>-0.197565826621037</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.134319951238945</v>
+        <v>0.351430454773742</v>
       </c>
       <c r="E184" t="n">
-        <v>0.0237241600556472</v>
+        <v>0.061008650316839</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0273651180017951</v>
+        <v>0.165207852638457</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.0201138460583616</v>
+        <v>-0.00147991661918554</v>
       </c>
     </row>
     <row r="185">
@@ -5222,22 +5222,22 @@
         <v>190</v>
       </c>
       <c r="B185" t="n">
-        <v>0.16616622600442</v>
+        <v>0.0602003340719986</v>
       </c>
       <c r="C185" t="n">
-        <v>0.196518050907383</v>
+        <v>-0.00333963573339389</v>
       </c>
       <c r="D185" t="n">
-        <v>0.0736837752536366</v>
+        <v>-0.0519661749653653</v>
       </c>
       <c r="E185" t="n">
-        <v>-0.0215237699458484</v>
+        <v>-0.0638021723951743</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.035271295506929</v>
+        <v>-0.0532852784078828</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0126582109057899</v>
+        <v>-0.0217704371466962</v>
       </c>
     </row>
     <row r="186">
@@ -5291,22 +5291,22 @@
         <v>193</v>
       </c>
       <c r="B188" t="n">
-        <v>0.000102544498781813</v>
+        <v>-0.00203514569817034</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.00632042598912509</v>
+        <v>-0.00615492910645531</v>
       </c>
       <c r="D188" t="n">
-        <v>0.00566147713257327</v>
+        <v>-0.00452373359101052</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.00807533294709273</v>
+        <v>0.00504771330302489</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.00186367592233866</v>
+        <v>-0.0342979613175415</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0411876435135206</v>
+        <v>0.0450165425486919</v>
       </c>
     </row>
     <row r="189">
@@ -5314,22 +5314,22 @@
         <v>194</v>
       </c>
       <c r="B189" t="n">
-        <v>-0.0257065969195537</v>
+        <v>-0.00485838695151525</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.174536382947788</v>
+        <v>-0.0176177866150858</v>
       </c>
       <c r="D189" t="n">
-        <v>0.229300787271432</v>
+        <v>-0.00171497434194402</v>
       </c>
       <c r="E189" t="n">
-        <v>0.14772459970164</v>
+        <v>-0.0521907585493003</v>
       </c>
       <c r="F189" t="n">
-        <v>0.121868143599989</v>
+        <v>0.0109606908309654</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0466104415939941</v>
+        <v>-0.0213804289522527</v>
       </c>
     </row>
     <row r="190">
@@ -5337,22 +5337,22 @@
         <v>195</v>
       </c>
       <c r="B190" t="n">
-        <v>-0.0546828262848597</v>
+        <v>-0.0376203582811347</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.261890697914285</v>
+        <v>-0.0177241351364623</v>
       </c>
       <c r="D190" t="n">
-        <v>0.0887470039155848</v>
+        <v>0.0491925916066678</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.0237061096039123</v>
+        <v>-0.0254284032292113</v>
       </c>
       <c r="F190" t="n">
-        <v>0.00842405038233143</v>
+        <v>0.0662604430547759</v>
       </c>
       <c r="G190" t="n">
-        <v>0.0258788985842077</v>
+        <v>-0.071382484274527</v>
       </c>
     </row>
     <row r="191">
@@ -5360,22 +5360,22 @@
         <v>196</v>
       </c>
       <c r="B191" t="n">
-        <v>0.00100226986140123</v>
+        <v>0.00333869125641026</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.00459322715991572</v>
+        <v>-0.0310978952100145</v>
       </c>
       <c r="D191" t="n">
-        <v>0.0011203107151089</v>
+        <v>-0.00950350401865012</v>
       </c>
       <c r="E191" t="n">
-        <v>-0.0157199165040054</v>
+        <v>-0.0293537592177329</v>
       </c>
       <c r="F191" t="n">
-        <v>0.019237622931284</v>
+        <v>-0.0201341562441764</v>
       </c>
       <c r="G191" t="n">
-        <v>-0.0801998523821433</v>
+        <v>-0.0883553405295857</v>
       </c>
     </row>
     <row r="192">
@@ -5383,22 +5383,22 @@
         <v>197</v>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>0.0861464650590501</v>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>-0.232921827251147</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>-0.205421169785922</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>0.0772427637429022</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>-0.0236078456557613</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>0.0104582188567969</v>
       </c>
     </row>
     <row r="193">
@@ -5452,22 +5452,22 @@
         <v>200</v>
       </c>
       <c r="B195" t="n">
-        <v>-0.000306152639484338</v>
+        <v>0.00390364114465595</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.0103700895385006</v>
+        <v>-0.0319283292473076</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.00459310330933866</v>
+        <v>0.00846929714750262</v>
       </c>
       <c r="E195" t="n">
-        <v>-0.011737392308563</v>
+        <v>-0.0441736720971653</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0232111503049924</v>
+        <v>-0.021621880088475</v>
       </c>
       <c r="G195" t="n">
-        <v>0.00496672962681783</v>
+        <v>0.000763183225105008</v>
       </c>
     </row>
     <row r="196">
@@ -5475,22 +5475,22 @@
         <v>201</v>
       </c>
       <c r="B196" t="n">
-        <v>0.00884853686525674</v>
+        <v>0.0176056889003543</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.00149181311436069</v>
+        <v>-0.0123815949380486</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.00300123087968164</v>
+        <v>-0.0107688608537126</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.00804351645372274</v>
+        <v>-0.0141929365141025</v>
       </c>
       <c r="F196" t="n">
-        <v>0.00993453160391071</v>
+        <v>-0.011862491784286</v>
       </c>
       <c r="G196" t="n">
-        <v>-0.0852496838640714</v>
+        <v>-0.0873264911460706</v>
       </c>
     </row>
     <row r="197">
@@ -5498,22 +5498,22 @@
         <v>202</v>
       </c>
       <c r="B197" t="n">
-        <v>-0.0724943907237012</v>
+        <v>-0.00870073843305969</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.0869745208380237</v>
+        <v>-0.0510439015239408</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.00862864975221186</v>
+        <v>0.0316629948948649</v>
       </c>
       <c r="E197" t="n">
-        <v>0.232873682537695</v>
+        <v>-0.0475979359034207</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.0669391426708415</v>
+        <v>-0.0132890654163082</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.000831175838832046</v>
+        <v>-0.0701590586818464</v>
       </c>
     </row>
     <row r="198">
@@ -5521,22 +5521,22 @@
         <v>203</v>
       </c>
       <c r="B198" t="n">
-        <v>-0.0041923302990138</v>
+        <v>-0.00640303897805457</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.00361430259577544</v>
+        <v>-0.0313012640456741</v>
       </c>
       <c r="D198" t="n">
-        <v>0.00201438334013711</v>
+        <v>-0.00474935060073387</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.0179921030640934</v>
+        <v>-0.00719271921703221</v>
       </c>
       <c r="F198" t="n">
-        <v>0.0107466819340295</v>
+        <v>-0.0195174460380881</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0363522047412825</v>
+        <v>-0.0423377638580738</v>
       </c>
     </row>
     <row r="199">
@@ -5544,22 +5544,22 @@
         <v>204</v>
       </c>
       <c r="B199" t="n">
-        <v>-0.000663251980458538</v>
+        <v>-0.00107163900483453</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.00133742475812806</v>
+        <v>-0.0217792000279665</v>
       </c>
       <c r="D199" t="n">
-        <v>0.00325444028003097</v>
+        <v>-0.0109448855072378</v>
       </c>
       <c r="E199" t="n">
-        <v>-0.0098787154770654</v>
+        <v>-0.0266356169245854</v>
       </c>
       <c r="F199" t="n">
-        <v>0.0159790943722114</v>
+        <v>-0.00831144604062003</v>
       </c>
       <c r="G199" t="n">
-        <v>0.0427026578315062</v>
+        <v>0.0498670386775258</v>
       </c>
     </row>
     <row r="200">
@@ -5567,22 +5567,22 @@
         <v>205</v>
       </c>
       <c r="B200" t="n">
-        <v>-0.08069205978282</v>
+        <v>-0.0157465445103613</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.0208646802077071</v>
+        <v>-0.0401503251227725</v>
       </c>
       <c r="D200" t="n">
-        <v>0.0868923585329041</v>
+        <v>-0.0152622515779279</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.0872937856516172</v>
+        <v>-0.00106653384693081</v>
       </c>
       <c r="F200" t="n">
-        <v>0.255104018507899</v>
+        <v>-0.0420289806758276</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0111184126268038</v>
+        <v>-0.0869047169750142</v>
       </c>
     </row>
     <row r="201">
@@ -5590,22 +5590,22 @@
         <v>206</v>
       </c>
       <c r="B201" t="n">
-        <v>-0.0011265589071592</v>
+        <v>-0.0115599417038178</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.00145208966067017</v>
+        <v>0.0190729901965494</v>
       </c>
       <c r="D201" t="n">
-        <v>0.0189467408090165</v>
+        <v>-0.0210964703345467</v>
       </c>
       <c r="E201" t="n">
-        <v>0.00314812907721237</v>
+        <v>0.0109209268489965</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.0110123222675611</v>
+        <v>-0.0317507954808862</v>
       </c>
       <c r="G201" t="n">
-        <v>0.00234304304187126</v>
+        <v>0.000391379757051251</v>
       </c>
     </row>
     <row r="202">
@@ -5613,22 +5613,22 @@
         <v>207</v>
       </c>
       <c r="B202" t="n">
-        <v>0.010085697411692</v>
+        <v>0.0222169794718591</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.00351026654543121</v>
+        <v>-0.046865541845208</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.00453634221024205</v>
+        <v>-0.0206795327343297</v>
       </c>
       <c r="E202" t="n">
-        <v>-0.0311829856944479</v>
+        <v>-0.00859891260017697</v>
       </c>
       <c r="F202" t="n">
-        <v>0.0183135444270866</v>
+        <v>-0.0337758262152668</v>
       </c>
       <c r="G202" t="n">
-        <v>0.00911911098586148</v>
+        <v>0.00481038816814823</v>
       </c>
     </row>
     <row r="203">
@@ -5636,22 +5636,22 @@
         <v>208</v>
       </c>
       <c r="B203" t="n">
-        <v>0.0102205392393282</v>
+        <v>0.0195815087423474</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.00505531484900226</v>
+        <v>-0.0129874861144194</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.00189334865916381</v>
+        <v>-0.0106638825123517</v>
       </c>
       <c r="E203" t="n">
-        <v>-0.00975914934556588</v>
+        <v>-0.0156341486874851</v>
       </c>
       <c r="F203" t="n">
-        <v>0.00978865344488592</v>
+        <v>-0.0266692726048657</v>
       </c>
       <c r="G203" t="n">
-        <v>0.00192520583914056</v>
+        <v>0.00116854720069754</v>
       </c>
     </row>
     <row r="204">
@@ -5659,22 +5659,22 @@
         <v>209</v>
       </c>
       <c r="B204" t="n">
-        <v>-0.00498625790430875</v>
+        <v>-0.0133509041912366</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.0095686876507707</v>
+        <v>-0.000312377866283413</v>
       </c>
       <c r="D204" t="n">
-        <v>0.0111508796374048</v>
+        <v>-0.000113855478896636</v>
       </c>
       <c r="E204" t="n">
-        <v>-0.001043584361075</v>
+        <v>-0.0149014421800251</v>
       </c>
       <c r="F204" t="n">
-        <v>0.00180950797859521</v>
+        <v>-0.037219716984718</v>
       </c>
       <c r="G204" t="n">
-        <v>-0.0391993387798132</v>
+        <v>-0.0442897273503462</v>
       </c>
     </row>
     <row r="205">
@@ -5682,22 +5682,22 @@
         <v>210</v>
       </c>
       <c r="B205" t="n">
-        <v>-0.00770469019420048</v>
+        <v>-0.0169323211322007</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.00277685864649165</v>
+        <v>-0.0332534750486684</v>
       </c>
       <c r="D205" t="n">
-        <v>0.0121018875574311</v>
+        <v>-0.0181484061334641</v>
       </c>
       <c r="E205" t="n">
-        <v>-0.021550405888741</v>
+        <v>-0.00612161707280465</v>
       </c>
       <c r="F205" t="n">
-        <v>0.0104612534128656</v>
+        <v>-0.0306094349475299</v>
       </c>
       <c r="G205" t="n">
-        <v>-0.0391314829253269</v>
+        <v>-0.0414312663064985</v>
       </c>
     </row>
     <row r="206">
@@ -5705,22 +5705,22 @@
         <v>211</v>
       </c>
       <c r="B206" t="n">
-        <v>0.009076606192552</v>
+        <v>0.025883678675822</v>
       </c>
       <c r="C206" t="n">
-        <v>0.0172104365283873</v>
+        <v>-0.0669833615570625</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.0144751225211092</v>
+        <v>-0.0344711444490173</v>
       </c>
       <c r="E206" t="n">
-        <v>-0.0349165539261203</v>
+        <v>-0.0154997690162444</v>
       </c>
       <c r="F206" t="n">
-        <v>0.0331965292586965</v>
+        <v>0.044333352170312</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.00204558193863894</v>
+        <v>0.00187186046841901</v>
       </c>
     </row>
     <row r="207">
@@ -5728,22 +5728,22 @@
         <v>212</v>
       </c>
       <c r="B207" t="n">
-        <v>0.00180765871419316</v>
+        <v>0.00444773335667908</v>
       </c>
       <c r="C207" t="n">
-        <v>0.0037554863503821</v>
+        <v>-0.0430650023446195</v>
       </c>
       <c r="D207" t="n">
-        <v>0.00148192624074482</v>
+        <v>-0.0258620384500507</v>
       </c>
       <c r="E207" t="n">
-        <v>-0.0319771122485979</v>
+        <v>0.0216295407010995</v>
       </c>
       <c r="F207" t="n">
-        <v>0.00687185570742577</v>
+        <v>-0.0191288440718004</v>
       </c>
       <c r="G207" t="n">
-        <v>-0.039470298674935</v>
+        <v>-0.0432318465716932</v>
       </c>
     </row>
     <row r="208">
@@ -5751,22 +5751,22 @@
         <v>213</v>
       </c>
       <c r="B208" t="n">
-        <v>0</v>
+        <v>0.00131701408300262</v>
       </c>
       <c r="C208" t="n">
-        <v>0</v>
+        <v>-0.145294440180627</v>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>-0.143429520159449</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>0.100163813175065</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>-0.136655064922698</v>
       </c>
       <c r="G208" t="n">
-        <v>0</v>
+        <v>0.00612050472243574</v>
       </c>
     </row>
     <row r="209">
@@ -5774,22 +5774,22 @@
         <v>214</v>
       </c>
       <c r="B209" t="n">
-        <v>-0.093016598206756</v>
+        <v>-0.034761092949346</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.0162162602737457</v>
+        <v>0.00751495229779699</v>
       </c>
       <c r="D209" t="n">
-        <v>0.100167362239411</v>
+        <v>-0.00655592837665806</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.0549092744409295</v>
+        <v>-0.0282906367159568</v>
       </c>
       <c r="F209" t="n">
-        <v>0.266549724218414</v>
+        <v>0.00187521159657097</v>
       </c>
       <c r="G209" t="n">
-        <v>0.0260620213302077</v>
+        <v>-0.0901508753566557</v>
       </c>
     </row>
   </sheetData>
